--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="H9" s="211">
-        <f>IF(AND(ISNUMBER(H7),ISNUMBER(H8)),H7*H8*(1-N(J19)/100),"")</f>
+        <f>IF(AND(ISNUMBER(H7),ISNUMBER(H8),OR(H6="Buy",H6="Sell")),H7*H8*(1+IF(H6="Buy",1,-1)*N(J19)/100),"")</f>
         <v/>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -2620,7 +2620,7 @@
         <v>62000</v>
       </c>
       <c r="H6" s="247" t="n">
-        <v>6187.6</v>
+        <v>6212.4</v>
       </c>
       <c r="I6" s="246" t="n"/>
       <c r="J6" s="183" t="n"/>
@@ -2688,7 +2688,7 @@
         <v>3200</v>
       </c>
       <c r="H8" s="247" t="n">
-        <v>3193.6</v>
+        <v>3206.4</v>
       </c>
       <c r="I8" s="246" t="n"/>
       <c r="J8" s="183" t="n"/>
@@ -2722,7 +2722,7 @@
         <v>3180</v>
       </c>
       <c r="H9" s="241" t="n">
-        <v>3808.368</v>
+        <v>3823.632</v>
       </c>
       <c r="I9" s="240" t="n"/>
       <c r="J9" s="177" t="n"/>
@@ -2756,7 +2756,7 @@
         <v>3250</v>
       </c>
       <c r="H10" s="247" t="n">
-        <v>2594.8</v>
+        <v>2605.2</v>
       </c>
       <c r="I10" s="246" t="n"/>
       <c r="J10" s="183" t="n"/>
@@ -2892,7 +2892,7 @@
         <v>146</v>
       </c>
       <c r="H14" s="247" t="n">
-        <v>3642.7</v>
+        <v>3657.3</v>
       </c>
       <c r="I14" s="246" t="n"/>
       <c r="J14" s="183" t="n"/>

--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -5142,7 +5142,7 @@
         <v>585</v>
       </c>
       <c r="I5" s="241" t="n">
-        <v>1167.66</v>
+        <v>1172.34</v>
       </c>
       <c r="J5" s="240" t="n">
         <v>2</v>
@@ -5194,7 +5194,7 @@
         <v>62200</v>
       </c>
       <c r="I6" s="247" t="n">
-        <v>3103.78</v>
+        <v>3116.22</v>
       </c>
       <c r="J6" s="246" t="n">
         <v>0.05</v>
@@ -5246,7 +5246,7 @@
         <v>3200</v>
       </c>
       <c r="I7" s="241" t="n">
-        <v>3193.6</v>
+        <v>3206.4</v>
       </c>
       <c r="J7" s="240" t="n">
         <v>1</v>
@@ -5298,7 +5298,7 @@
         <v>145</v>
       </c>
       <c r="I8" s="247" t="n">
-        <v>2894.2</v>
+        <v>2905.8</v>
       </c>
       <c r="J8" s="246" t="n">
         <v>20</v>

--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -2586,7 +2586,7 @@
         <v>3</v>
       </c>
       <c r="J5" s="177" t="n">
-        <v>600</v>
+        <v>598.8</v>
       </c>
       <c r="K5" s="241" t="n">
         <v>1796.4</v>
@@ -2617,7 +2617,7 @@
         <v>0.1</v>
       </c>
       <c r="G6" s="183" t="n">
-        <v>62000</v>
+        <v>62124</v>
       </c>
       <c r="H6" s="247" t="n">
         <v>6212.4</v>
@@ -2654,7 +2654,7 @@
         <v>1.5</v>
       </c>
       <c r="J7" s="177" t="n">
-        <v>0.0525</v>
+        <v>0.052395</v>
       </c>
       <c r="K7" s="241" t="n">
         <v>0.0785925</v>
@@ -2685,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="183" t="n">
-        <v>3200</v>
+        <v>3206.4</v>
       </c>
       <c r="H8" s="247" t="n">
         <v>3206.4</v>
@@ -2719,7 +2719,7 @@
         <v>1.2</v>
       </c>
       <c r="G9" s="177" t="n">
-        <v>3180</v>
+        <v>3186.36</v>
       </c>
       <c r="H9" s="241" t="n">
         <v>3823.632</v>
@@ -2753,7 +2753,7 @@
         <v>0.8</v>
       </c>
       <c r="G10" s="183" t="n">
-        <v>3250</v>
+        <v>3256.5</v>
       </c>
       <c r="H10" s="247" t="n">
         <v>2605.2</v>
@@ -2790,7 +2790,7 @@
         <v>1.5</v>
       </c>
       <c r="J11" s="177" t="n">
-        <v>3400</v>
+        <v>3393.2</v>
       </c>
       <c r="K11" s="241" t="n">
         <v>5089.8</v>
@@ -2824,7 +2824,7 @@
         <v>30</v>
       </c>
       <c r="J12" s="183" t="n">
-        <v>150</v>
+        <v>149.7</v>
       </c>
       <c r="K12" s="247" t="n">
         <v>4491</v>
@@ -2858,7 +2858,7 @@
         <v>10</v>
       </c>
       <c r="J13" s="177" t="n">
-        <v>152</v>
+        <v>151.696</v>
       </c>
       <c r="K13" s="241" t="n">
         <v>1516.96</v>
@@ -2889,7 +2889,7 @@
         <v>25</v>
       </c>
       <c r="G14" s="183" t="n">
-        <v>146</v>
+        <v>146.292</v>
       </c>
       <c r="H14" s="247" t="n">
         <v>3657.3</v>
@@ -5139,7 +5139,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="177" t="n">
-        <v>585</v>
+        <v>586.17</v>
       </c>
       <c r="I5" s="241" t="n">
         <v>1172.34</v>
@@ -5148,7 +5148,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="177" t="n">
-        <v>600</v>
+        <v>598.8</v>
       </c>
       <c r="L5" s="241" t="n">
         <v>1197.6</v>
@@ -5191,7 +5191,7 @@
         <v>0.05</v>
       </c>
       <c r="H6" s="183" t="n">
-        <v>62200</v>
+        <v>62324.4</v>
       </c>
       <c r="I6" s="247" t="n">
         <v>3116.22</v>
@@ -5200,7 +5200,7 @@
         <v>0.05</v>
       </c>
       <c r="K6" s="183" t="n">
-        <v>63000</v>
+        <v>62874</v>
       </c>
       <c r="L6" s="247" t="n">
         <v>3143.7</v>
@@ -5243,7 +5243,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="177" t="n">
-        <v>3200</v>
+        <v>3206.4</v>
       </c>
       <c r="I7" s="241" t="n">
         <v>3206.4</v>
@@ -5252,7 +5252,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="177" t="n">
-        <v>3350</v>
+        <v>3343.3</v>
       </c>
       <c r="L7" s="241" t="n">
         <v>3343.3</v>
@@ -5295,7 +5295,7 @@
         <v>20</v>
       </c>
       <c r="H8" s="183" t="n">
-        <v>145</v>
+        <v>145.29</v>
       </c>
       <c r="I8" s="247" t="n">
         <v>2905.8</v>
@@ -5304,7 +5304,7 @@
         <v>20</v>
       </c>
       <c r="K8" s="183" t="n">
-        <v>152</v>
+        <v>151.696</v>
       </c>
       <c r="L8" s="247" t="n">
         <v>3033.92</v>

--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -115,7 +115,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -208,6 +208,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00722F37"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -644,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="271">
+  <cellXfs count="272">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1447,6 +1453,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="18" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2581,18 +2590,28 @@
       </c>
       <c r="F5" s="240" t="n"/>
       <c r="G5" s="177" t="n"/>
-      <c r="H5" s="241" t="n"/>
+      <c r="H5" s="271">
+        <f>IF(AND(ISNUMBER(F5),ISNUMBER(G5)),F5*G5,"")</f>
+        <v/>
+      </c>
       <c r="I5" s="240" t="n">
         <v>3</v>
       </c>
       <c r="J5" s="177" t="n">
         <v>598.8</v>
       </c>
-      <c r="K5" s="241" t="n">
-        <v>1796.4</v>
-      </c>
-      <c r="L5" s="240" t="n"/>
-      <c r="M5" s="177" t="n"/>
+      <c r="K5" s="271">
+        <f>IF(AND(ISNUMBER(I5),ISNUMBER(J5)),I5*J5,"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="240">
+        <f>IF(COUNT(F5,I5)=0,"",N(F5)-N(I5))</f>
+        <v/>
+      </c>
+      <c r="M5" s="177">
+        <f>IF(COUNT(H5,K5)=0,"",N(K5)-N(H5))</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="244" t="inlineStr">
@@ -2619,14 +2638,24 @@
       <c r="G6" s="183" t="n">
         <v>62124</v>
       </c>
-      <c r="H6" s="247" t="n">
-        <v>6212.4</v>
+      <c r="H6" s="271">
+        <f>IF(AND(ISNUMBER(F6),ISNUMBER(G6)),F6*G6,"")</f>
+        <v/>
       </c>
       <c r="I6" s="246" t="n"/>
       <c r="J6" s="183" t="n"/>
-      <c r="K6" s="247" t="n"/>
-      <c r="L6" s="246" t="n"/>
-      <c r="M6" s="183" t="n"/>
+      <c r="K6" s="271">
+        <f>IF(AND(ISNUMBER(I6),ISNUMBER(J6)),I6*J6,"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="246">
+        <f>IF(COUNT(F6,I6)=0,"",N(F6)-N(I6))</f>
+        <v/>
+      </c>
+      <c r="M6" s="183">
+        <f>IF(COUNT(H6,K6)=0,"",N(K6)-N(H6))</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="238" t="inlineStr">
@@ -2649,18 +2678,28 @@
       </c>
       <c r="F7" s="240" t="n"/>
       <c r="G7" s="177" t="n"/>
-      <c r="H7" s="241" t="n"/>
+      <c r="H7" s="271">
+        <f>IF(AND(ISNUMBER(F7),ISNUMBER(G7)),F7*G7,"")</f>
+        <v/>
+      </c>
       <c r="I7" s="240" t="n">
         <v>1.5</v>
       </c>
       <c r="J7" s="177" t="n">
         <v>0.052395</v>
       </c>
-      <c r="K7" s="241" t="n">
-        <v>0.0785925</v>
-      </c>
-      <c r="L7" s="240" t="n"/>
-      <c r="M7" s="177" t="n"/>
+      <c r="K7" s="271">
+        <f>IF(AND(ISNUMBER(I7),ISNUMBER(J7)),I7*J7,"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="240">
+        <f>IF(COUNT(F7,I7)=0,"",N(F7)-N(I7))</f>
+        <v/>
+      </c>
+      <c r="M7" s="177">
+        <f>IF(COUNT(H7,K7)=0,"",N(K7)-N(H7))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="244" t="inlineStr">
@@ -2687,14 +2726,24 @@
       <c r="G8" s="183" t="n">
         <v>3206.4</v>
       </c>
-      <c r="H8" s="247" t="n">
-        <v>3206.4</v>
+      <c r="H8" s="271">
+        <f>IF(AND(ISNUMBER(F8),ISNUMBER(G8)),F8*G8,"")</f>
+        <v/>
       </c>
       <c r="I8" s="246" t="n"/>
       <c r="J8" s="183" t="n"/>
-      <c r="K8" s="247" t="n"/>
-      <c r="L8" s="246" t="n"/>
-      <c r="M8" s="183" t="n"/>
+      <c r="K8" s="271">
+        <f>IF(AND(ISNUMBER(I8),ISNUMBER(J8)),I8*J8,"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="246">
+        <f>IF(COUNT(F8,I8)=0,"",N(F8)-N(I8))</f>
+        <v/>
+      </c>
+      <c r="M8" s="183">
+        <f>IF(COUNT(H8,K8)=0,"",N(K8)-N(H8))</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="238" t="inlineStr">
@@ -2721,14 +2770,24 @@
       <c r="G9" s="177" t="n">
         <v>3186.36</v>
       </c>
-      <c r="H9" s="241" t="n">
-        <v>3823.632</v>
+      <c r="H9" s="271">
+        <f>IF(AND(ISNUMBER(F9),ISNUMBER(G9)),F9*G9,"")</f>
+        <v/>
       </c>
       <c r="I9" s="240" t="n"/>
       <c r="J9" s="177" t="n"/>
-      <c r="K9" s="241" t="n"/>
-      <c r="L9" s="240" t="n"/>
-      <c r="M9" s="177" t="n"/>
+      <c r="K9" s="271">
+        <f>IF(AND(ISNUMBER(I9),ISNUMBER(J9)),I9*J9,"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="240">
+        <f>IF(COUNT(F9,I9)=0,"",N(F9)-N(I9))</f>
+        <v/>
+      </c>
+      <c r="M9" s="177">
+        <f>IF(COUNT(H9,K9)=0,"",N(K9)-N(H9))</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="244" t="inlineStr">
@@ -2755,14 +2814,24 @@
       <c r="G10" s="183" t="n">
         <v>3256.5</v>
       </c>
-      <c r="H10" s="247" t="n">
-        <v>2605.2</v>
+      <c r="H10" s="271">
+        <f>IF(AND(ISNUMBER(F10),ISNUMBER(G10)),F10*G10,"")</f>
+        <v/>
       </c>
       <c r="I10" s="246" t="n"/>
       <c r="J10" s="183" t="n"/>
-      <c r="K10" s="247" t="n"/>
-      <c r="L10" s="246" t="n"/>
-      <c r="M10" s="183" t="n"/>
+      <c r="K10" s="271">
+        <f>IF(AND(ISNUMBER(I10),ISNUMBER(J10)),I10*J10,"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="246">
+        <f>IF(COUNT(F10,I10)=0,"",N(F10)-N(I10))</f>
+        <v/>
+      </c>
+      <c r="M10" s="183">
+        <f>IF(COUNT(H10,K10)=0,"",N(K10)-N(H10))</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="238" t="inlineStr">
@@ -2785,18 +2854,28 @@
       </c>
       <c r="F11" s="240" t="n"/>
       <c r="G11" s="177" t="n"/>
-      <c r="H11" s="241" t="n"/>
+      <c r="H11" s="271">
+        <f>IF(AND(ISNUMBER(F11),ISNUMBER(G11)),F11*G11,"")</f>
+        <v/>
+      </c>
       <c r="I11" s="240" t="n">
         <v>1.5</v>
       </c>
       <c r="J11" s="177" t="n">
         <v>3393.2</v>
       </c>
-      <c r="K11" s="241" t="n">
-        <v>5089.8</v>
-      </c>
-      <c r="L11" s="240" t="n"/>
-      <c r="M11" s="177" t="n"/>
+      <c r="K11" s="271">
+        <f>IF(AND(ISNUMBER(I11),ISNUMBER(J11)),I11*J11,"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="240">
+        <f>IF(COUNT(F11,I11)=0,"",N(F11)-N(I11))</f>
+        <v/>
+      </c>
+      <c r="M11" s="177">
+        <f>IF(COUNT(H11,K11)=0,"",N(K11)-N(H11))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="244" t="inlineStr">
@@ -2819,18 +2898,28 @@
       </c>
       <c r="F12" s="246" t="n"/>
       <c r="G12" s="183" t="n"/>
-      <c r="H12" s="247" t="n"/>
+      <c r="H12" s="271">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER(G12)),F12*G12,"")</f>
+        <v/>
+      </c>
       <c r="I12" s="246" t="n">
         <v>30</v>
       </c>
       <c r="J12" s="183" t="n">
         <v>149.7</v>
       </c>
-      <c r="K12" s="247" t="n">
-        <v>4491</v>
-      </c>
-      <c r="L12" s="246" t="n"/>
-      <c r="M12" s="183" t="n"/>
+      <c r="K12" s="271">
+        <f>IF(AND(ISNUMBER(I12),ISNUMBER(J12)),I12*J12,"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="246">
+        <f>IF(COUNT(F12,I12)=0,"",N(F12)-N(I12))</f>
+        <v/>
+      </c>
+      <c r="M12" s="183">
+        <f>IF(COUNT(H12,K12)=0,"",N(K12)-N(H12))</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="238" t="inlineStr">
@@ -2853,18 +2942,28 @@
       </c>
       <c r="F13" s="240" t="n"/>
       <c r="G13" s="177" t="n"/>
-      <c r="H13" s="241" t="n"/>
+      <c r="H13" s="271">
+        <f>IF(AND(ISNUMBER(F13),ISNUMBER(G13)),F13*G13,"")</f>
+        <v/>
+      </c>
       <c r="I13" s="240" t="n">
         <v>10</v>
       </c>
       <c r="J13" s="177" t="n">
         <v>151.696</v>
       </c>
-      <c r="K13" s="241" t="n">
-        <v>1516.96</v>
-      </c>
-      <c r="L13" s="240" t="n"/>
-      <c r="M13" s="177" t="n"/>
+      <c r="K13" s="271">
+        <f>IF(AND(ISNUMBER(I13),ISNUMBER(J13)),I13*J13,"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="240">
+        <f>IF(COUNT(F13,I13)=0,"",N(F13)-N(I13))</f>
+        <v/>
+      </c>
+      <c r="M13" s="177">
+        <f>IF(COUNT(H13,K13)=0,"",N(K13)-N(H13))</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="B14" s="244" t="inlineStr">
@@ -2891,14 +2990,24 @@
       <c r="G14" s="183" t="n">
         <v>146.292</v>
       </c>
-      <c r="H14" s="247" t="n">
-        <v>3657.3</v>
+      <c r="H14" s="271">
+        <f>IF(AND(ISNUMBER(F14),ISNUMBER(G14)),F14*G14,"")</f>
+        <v/>
       </c>
       <c r="I14" s="246" t="n"/>
       <c r="J14" s="183" t="n"/>
-      <c r="K14" s="247" t="n"/>
-      <c r="L14" s="246" t="n"/>
-      <c r="M14" s="183" t="n"/>
+      <c r="K14" s="271">
+        <f>IF(AND(ISNUMBER(I14),ISNUMBER(J14)),I14*J14,"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="246">
+        <f>IF(COUNT(F14,I14)=0,"",N(F14)-N(I14))</f>
+        <v/>
+      </c>
+      <c r="M14" s="183">
+        <f>IF(COUNT(H14,K14)=0,"",N(K14)-N(H14))</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="238" t="n"/>
@@ -2907,12 +3016,24 @@
       <c r="E15" s="239" t="n"/>
       <c r="F15" s="240" t="n"/>
       <c r="G15" s="177" t="n"/>
-      <c r="H15" s="241" t="n"/>
+      <c r="H15" s="271">
+        <f>IF(AND(ISNUMBER(F15),ISNUMBER(G15)),F15*G15,"")</f>
+        <v/>
+      </c>
       <c r="I15" s="240" t="n"/>
       <c r="J15" s="177" t="n"/>
-      <c r="K15" s="241" t="n"/>
-      <c r="L15" s="240" t="n"/>
-      <c r="M15" s="177" t="n"/>
+      <c r="K15" s="271">
+        <f>IF(AND(ISNUMBER(I15),ISNUMBER(J15)),I15*J15,"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="240">
+        <f>IF(COUNT(F15,I15)=0,"",N(F15)-N(I15))</f>
+        <v/>
+      </c>
+      <c r="M15" s="177">
+        <f>IF(COUNT(H15,K15)=0,"",N(K15)-N(H15))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="B16" s="244" t="n"/>
@@ -2921,12 +3042,24 @@
       <c r="E16" s="245" t="n"/>
       <c r="F16" s="246" t="n"/>
       <c r="G16" s="183" t="n"/>
-      <c r="H16" s="247" t="n"/>
+      <c r="H16" s="271">
+        <f>IF(AND(ISNUMBER(F16),ISNUMBER(G16)),F16*G16,"")</f>
+        <v/>
+      </c>
       <c r="I16" s="246" t="n"/>
       <c r="J16" s="183" t="n"/>
-      <c r="K16" s="247" t="n"/>
-      <c r="L16" s="246" t="n"/>
-      <c r="M16" s="183" t="n"/>
+      <c r="K16" s="271">
+        <f>IF(AND(ISNUMBER(I16),ISNUMBER(J16)),I16*J16,"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="246">
+        <f>IF(COUNT(F16,I16)=0,"",N(F16)-N(I16))</f>
+        <v/>
+      </c>
+      <c r="M16" s="183">
+        <f>IF(COUNT(H16,K16)=0,"",N(K16)-N(H16))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B4:M16"/>

--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -217,7 +217,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="49">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -646,11 +646,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right style="thick">
+        <color rgb="FFFFFFFF"/>
+      </right>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="274">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1454,6 +1470,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="18" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2480,7 +2502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M16"/>
+  <dimension ref="B1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -2496,6 +2518,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
@@ -2563,9 +2586,14 @@
           <t>Дельта 1</t>
         </is>
       </c>
-      <c r="M4" s="107" t="inlineStr">
+      <c r="M4" s="272" t="inlineStr">
         <is>
           <t>Дельта 2</t>
+        </is>
+      </c>
+      <c r="N4" s="273" t="inlineStr">
+        <is>
+          <t>Break even</t>
         </is>
       </c>
     </row>
@@ -2608,8 +2636,12 @@
         <f>IF(COUNT(F5,I5)=0,"",N(F5)-N(I5))</f>
         <v/>
       </c>
-      <c r="M5" s="177">
+      <c r="M5" s="241">
         <f>IF(COUNT(H5,K5)=0,"",N(K5)-N(H5))</f>
+        <v/>
+      </c>
+      <c r="N5" s="240">
+        <f>IF(AND(ISNUMBER(F5),ISNUMBER(G5),F5&gt;0,1-N(Ввод!$J$19)/100&gt;0),G5/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I5),ISNUMBER(J5),I5&gt;0),J5/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
@@ -2652,8 +2684,12 @@
         <f>IF(COUNT(F6,I6)=0,"",N(F6)-N(I6))</f>
         <v/>
       </c>
-      <c r="M6" s="183">
+      <c r="M6" s="247">
         <f>IF(COUNT(H6,K6)=0,"",N(K6)-N(H6))</f>
+        <v/>
+      </c>
+      <c r="N6" s="246">
+        <f>IF(AND(ISNUMBER(F6),ISNUMBER(G6),F6&gt;0,1-N(Ввод!$J$19)/100&gt;0),G6/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I6),ISNUMBER(J6),I6&gt;0),J6/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
@@ -2696,8 +2732,12 @@
         <f>IF(COUNT(F7,I7)=0,"",N(F7)-N(I7))</f>
         <v/>
       </c>
-      <c r="M7" s="177">
+      <c r="M7" s="241">
         <f>IF(COUNT(H7,K7)=0,"",N(K7)-N(H7))</f>
+        <v/>
+      </c>
+      <c r="N7" s="240">
+        <f>IF(AND(ISNUMBER(F7),ISNUMBER(G7),F7&gt;0,1-N(Ввод!$J$19)/100&gt;0),G7/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I7),ISNUMBER(J7),I7&gt;0),J7/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
@@ -2740,8 +2780,12 @@
         <f>IF(COUNT(F8,I8)=0,"",N(F8)-N(I8))</f>
         <v/>
       </c>
-      <c r="M8" s="183">
+      <c r="M8" s="247">
         <f>IF(COUNT(H8,K8)=0,"",N(K8)-N(H8))</f>
+        <v/>
+      </c>
+      <c r="N8" s="246">
+        <f>IF(AND(ISNUMBER(F8),ISNUMBER(G8),F8&gt;0,1-N(Ввод!$J$19)/100&gt;0),G8/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I8),ISNUMBER(J8),I8&gt;0),J8/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
@@ -2784,8 +2828,12 @@
         <f>IF(COUNT(F9,I9)=0,"",N(F9)-N(I9))</f>
         <v/>
       </c>
-      <c r="M9" s="177">
+      <c r="M9" s="241">
         <f>IF(COUNT(H9,K9)=0,"",N(K9)-N(H9))</f>
+        <v/>
+      </c>
+      <c r="N9" s="240">
+        <f>IF(AND(ISNUMBER(F9),ISNUMBER(G9),F9&gt;0,1-N(Ввод!$J$19)/100&gt;0),G9/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I9),ISNUMBER(J9),I9&gt;0),J9/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
@@ -2828,8 +2876,12 @@
         <f>IF(COUNT(F10,I10)=0,"",N(F10)-N(I10))</f>
         <v/>
       </c>
-      <c r="M10" s="183">
+      <c r="M10" s="247">
         <f>IF(COUNT(H10,K10)=0,"",N(K10)-N(H10))</f>
+        <v/>
+      </c>
+      <c r="N10" s="246">
+        <f>IF(AND(ISNUMBER(F10),ISNUMBER(G10),F10&gt;0,1-N(Ввод!$J$19)/100&gt;0),G10/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I10),ISNUMBER(J10),I10&gt;0),J10/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
@@ -2872,8 +2924,12 @@
         <f>IF(COUNT(F11,I11)=0,"",N(F11)-N(I11))</f>
         <v/>
       </c>
-      <c r="M11" s="177">
+      <c r="M11" s="241">
         <f>IF(COUNT(H11,K11)=0,"",N(K11)-N(H11))</f>
+        <v/>
+      </c>
+      <c r="N11" s="240">
+        <f>IF(AND(ISNUMBER(F11),ISNUMBER(G11),F11&gt;0,1-N(Ввод!$J$19)/100&gt;0),G11/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I11),ISNUMBER(J11),I11&gt;0),J11/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
@@ -2916,8 +2972,12 @@
         <f>IF(COUNT(F12,I12)=0,"",N(F12)-N(I12))</f>
         <v/>
       </c>
-      <c r="M12" s="183">
+      <c r="M12" s="247">
         <f>IF(COUNT(H12,K12)=0,"",N(K12)-N(H12))</f>
+        <v/>
+      </c>
+      <c r="N12" s="246">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER(G12),F12&gt;0,1-N(Ввод!$J$19)/100&gt;0),G12/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I12),ISNUMBER(J12),I12&gt;0),J12/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
@@ -2960,8 +3020,12 @@
         <f>IF(COUNT(F13,I13)=0,"",N(F13)-N(I13))</f>
         <v/>
       </c>
-      <c r="M13" s="177">
+      <c r="M13" s="241">
         <f>IF(COUNT(H13,K13)=0,"",N(K13)-N(H13))</f>
+        <v/>
+      </c>
+      <c r="N13" s="240">
+        <f>IF(AND(ISNUMBER(F13),ISNUMBER(G13),F13&gt;0,1-N(Ввод!$J$19)/100&gt;0),G13/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I13),ISNUMBER(J13),I13&gt;0),J13/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
@@ -3004,8 +3068,12 @@
         <f>IF(COUNT(F14,I14)=0,"",N(F14)-N(I14))</f>
         <v/>
       </c>
-      <c r="M14" s="183">
+      <c r="M14" s="247">
         <f>IF(COUNT(H14,K14)=0,"",N(K14)-N(H14))</f>
+        <v/>
+      </c>
+      <c r="N14" s="246">
+        <f>IF(AND(ISNUMBER(F14),ISNUMBER(G14),F14&gt;0,1-N(Ввод!$J$19)/100&gt;0),G14/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I14),ISNUMBER(J14),I14&gt;0),J14/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
@@ -3030,8 +3098,12 @@
         <f>IF(COUNT(F15,I15)=0,"",N(F15)-N(I15))</f>
         <v/>
       </c>
-      <c r="M15" s="177">
+      <c r="M15" s="241">
         <f>IF(COUNT(H15,K15)=0,"",N(K15)-N(H15))</f>
+        <v/>
+      </c>
+      <c r="N15" s="240">
+        <f>IF(AND(ISNUMBER(F15),ISNUMBER(G15),F15&gt;0,1-N(Ввод!$J$19)/100&gt;0),G15/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I15),ISNUMBER(J15),I15&gt;0),J15/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
@@ -3056,17 +3128,21 @@
         <f>IF(COUNT(F16,I16)=0,"",N(F16)-N(I16))</f>
         <v/>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="247">
         <f>IF(COUNT(H16,K16)=0,"",N(K16)-N(H16))</f>
+        <v/>
+      </c>
+      <c r="N16" s="246">
+        <f>IF(AND(ISNUMBER(F16),ISNUMBER(G16),F16&gt;0,1-N(Ввод!$J$19)/100&gt;0),G16/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I16),ISNUMBER(J16),I16&gt;0),J16/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B4:M16"/>
   <mergeCells count="1">
-    <mergeCell ref="B1:M2"/>
+    <mergeCell ref="B1:N2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:M200">
+  <conditionalFormatting sqref="B5:N200">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($B5&lt;&gt;"",COUNTIF(Закрытые!$B$5:$B$200,$B5)&gt;0)</formula>
     </cfRule>

--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -3286,9 +3286,18 @@
         <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B5)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B5)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B5)*100,2))</f>
         <v/>
       </c>
-      <c r="K5" s="240" t="n"/>
-      <c r="L5" s="177" t="n"/>
-      <c r="M5" s="177" t="n"/>
+      <c r="K5" s="240">
+        <f>IF(MIN(N(C5),N(F5))&lt;=0,"",ROUND(MIN(N(C5),N(F5))*(N(G5)-N(D5)),8))</f>
+        <v/>
+      </c>
+      <c r="L5" s="177">
+        <f>IF(MIN(N(C5),N(F5))&lt;=0,"",IF(N(D5)=0,"",ROUND((N(G5)/N(D5)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M5" s="177">
+        <f>IF(OR(ROUND(N(C5)-N(F5),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C5)&gt;N(F5),(N(E5)-N(H5))/((N(C5)-N(F5))*(1-N(Ввод!$J$19)/100)),(N(H5)-N(E5))/((N(F5)-N(C5))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="245" t="inlineStr">
@@ -3328,9 +3337,18 @@
         <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B6)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B6)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B6)*100,2))</f>
         <v/>
       </c>
-      <c r="K6" s="246" t="n"/>
-      <c r="L6" s="183" t="n"/>
-      <c r="M6" s="183" t="n"/>
+      <c r="K6" s="246">
+        <f>IF(MIN(N(C6),N(F6))&lt;=0,"",ROUND(MIN(N(C6),N(F6))*(N(G6)-N(D6)),8))</f>
+        <v/>
+      </c>
+      <c r="L6" s="183">
+        <f>IF(MIN(N(C6),N(F6))&lt;=0,"",IF(N(D6)=0,"",ROUND((N(G6)/N(D6)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M6" s="183">
+        <f>IF(OR(ROUND(N(C6)-N(F6),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C6)&gt;N(F6),(N(E6)-N(H6))/((N(C6)-N(F6))*(1-N(Ввод!$J$19)/100)),(N(H6)-N(E6))/((N(F6)-N(C6))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="239" t="inlineStr">
@@ -3370,9 +3388,18 @@
         <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B7)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B7)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B7)*100,2))</f>
         <v/>
       </c>
-      <c r="K7" s="240" t="n"/>
-      <c r="L7" s="177" t="n"/>
-      <c r="M7" s="177" t="n"/>
+      <c r="K7" s="240">
+        <f>IF(MIN(N(C7),N(F7))&lt;=0,"",ROUND(MIN(N(C7),N(F7))*(N(G7)-N(D7)),8))</f>
+        <v/>
+      </c>
+      <c r="L7" s="177">
+        <f>IF(MIN(N(C7),N(F7))&lt;=0,"",IF(N(D7)=0,"",ROUND((N(G7)/N(D7)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M7" s="177">
+        <f>IF(OR(ROUND(N(C7)-N(F7),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C7)&gt;N(F7),(N(E7)-N(H7))/((N(C7)-N(F7))*(1-N(Ввод!$J$19)/100)),(N(H7)-N(E7))/((N(F7)-N(C7))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="245" t="inlineStr">
@@ -3412,9 +3439,18 @@
         <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B8)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B8)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B8)*100,2))</f>
         <v/>
       </c>
-      <c r="K8" s="246" t="n"/>
-      <c r="L8" s="183" t="n"/>
-      <c r="M8" s="183" t="n"/>
+      <c r="K8" s="246">
+        <f>IF(MIN(N(C8),N(F8))&lt;=0,"",ROUND(MIN(N(C8),N(F8))*(N(G8)-N(D8)),8))</f>
+        <v/>
+      </c>
+      <c r="L8" s="183">
+        <f>IF(MIN(N(C8),N(F8))&lt;=0,"",IF(N(D8)=0,"",ROUND((N(G8)/N(D8)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M8" s="183">
+        <f>IF(OR(ROUND(N(C8)-N(F8),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C8)&gt;N(F8),(N(E8)-N(H8))/((N(C8)-N(F8))*(1-N(Ввод!$J$19)/100)),(N(H8)-N(E8))/((N(F8)-N(C8))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="239" t="inlineStr">
@@ -3454,51 +3490,159 @@
         <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B9)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B9)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B9)*100,2))</f>
         <v/>
       </c>
-      <c r="K9" s="240" t="n"/>
-      <c r="L9" s="177" t="n"/>
-      <c r="M9" s="177" t="n"/>
+      <c r="K9" s="240">
+        <f>IF(MIN(N(C9),N(F9))&lt;=0,"",ROUND(MIN(N(C9),N(F9))*(N(G9)-N(D9)),8))</f>
+        <v/>
+      </c>
+      <c r="L9" s="177">
+        <f>IF(MIN(N(C9),N(F9))&lt;=0,"",IF(N(D9)=0,"",ROUND((N(G9)/N(D9)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M9" s="177">
+        <f>IF(OR(ROUND(N(C9)-N(F9),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C9)&gt;N(F9),(N(E9)-N(H9))/((N(C9)-N(F9))*(1-N(Ввод!$J$19)/100)),(N(H9)-N(E9))/((N(F9)-N(C9))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="245" t="n"/>
-      <c r="C10" s="246" t="n"/>
-      <c r="D10" s="183" t="n"/>
-      <c r="E10" s="247" t="n"/>
-      <c r="F10" s="246" t="n"/>
-      <c r="G10" s="183" t="n"/>
-      <c r="H10" s="247" t="n"/>
-      <c r="I10" s="246" t="n"/>
-      <c r="J10" s="247" t="n"/>
-      <c r="K10" s="246" t="n"/>
-      <c r="L10" s="183" t="n"/>
-      <c r="M10" s="183" t="n"/>
+      <c r="C10" s="246">
+        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B10)=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B10))</f>
+        <v/>
+      </c>
+      <c r="D10" s="183">
+        <f>IF(C10="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B10)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B10)*Закрытые!$G$5:$G$200*Закрытые!$H$5:$H$200))/C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="247">
+        <f>IF(C10="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B10))</f>
+        <v/>
+      </c>
+      <c r="F10" s="246">
+        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B10)=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="183">
+        <f>IF(F10="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B10)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B10)*Закрытые!$J$5:$J$200*Закрытые!$K$5:$K$200))/F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="247">
+        <f>IF(F10="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$F$5:$F$200,$B10))</f>
+        <v/>
+      </c>
+      <c r="I10" s="246">
+        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B10)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B10),8))</f>
+        <v/>
+      </c>
+      <c r="J10" s="247">
+        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B10)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B10)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B10)*100,2))</f>
+        <v/>
+      </c>
+      <c r="K10" s="246">
+        <f>IF(MIN(N(C10),N(F10))&lt;=0,"",ROUND(MIN(N(C10),N(F10))*(N(G10)-N(D10)),8))</f>
+        <v/>
+      </c>
+      <c r="L10" s="183">
+        <f>IF(MIN(N(C10),N(F10))&lt;=0,"",IF(N(D10)=0,"",ROUND((N(G10)/N(D10)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M10" s="183">
+        <f>IF(OR(ROUND(N(C10)-N(F10),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C10)&gt;N(F10),(N(E10)-N(H10))/((N(C10)-N(F10))*(1-N(Ввод!$J$19)/100)),(N(H10)-N(E10))/((N(F10)-N(C10))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="239" t="n"/>
-      <c r="C11" s="240" t="n"/>
-      <c r="D11" s="177" t="n"/>
-      <c r="E11" s="241" t="n"/>
-      <c r="F11" s="240" t="n"/>
-      <c r="G11" s="177" t="n"/>
-      <c r="H11" s="241" t="n"/>
-      <c r="I11" s="240" t="n"/>
-      <c r="J11" s="241" t="n"/>
-      <c r="K11" s="240" t="n"/>
-      <c r="L11" s="177" t="n"/>
-      <c r="M11" s="177" t="n"/>
+      <c r="C11" s="240">
+        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B11)=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B11))</f>
+        <v/>
+      </c>
+      <c r="D11" s="177">
+        <f>IF(C11="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B11)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B11)*Закрытые!$G$5:$G$200*Закрытые!$H$5:$H$200))/C11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="241">
+        <f>IF(C11="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B11))</f>
+        <v/>
+      </c>
+      <c r="F11" s="240">
+        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B11)=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="177">
+        <f>IF(F11="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B11)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B11)*Закрытые!$J$5:$J$200*Закрытые!$K$5:$K$200))/F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="241">
+        <f>IF(F11="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$F$5:$F$200,$B11))</f>
+        <v/>
+      </c>
+      <c r="I11" s="240">
+        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B11)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B11),8))</f>
+        <v/>
+      </c>
+      <c r="J11" s="241">
+        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B11)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B11)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B11)*100,2))</f>
+        <v/>
+      </c>
+      <c r="K11" s="240">
+        <f>IF(MIN(N(C11),N(F11))&lt;=0,"",ROUND(MIN(N(C11),N(F11))*(N(G11)-N(D11)),8))</f>
+        <v/>
+      </c>
+      <c r="L11" s="177">
+        <f>IF(MIN(N(C11),N(F11))&lt;=0,"",IF(N(D11)=0,"",ROUND((N(G11)/N(D11)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M11" s="177">
+        <f>IF(OR(ROUND(N(C11)-N(F11),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C11)&gt;N(F11),(N(E11)-N(H11))/((N(C11)-N(F11))*(1-N(Ввод!$J$19)/100)),(N(H11)-N(E11))/((N(F11)-N(C11))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="245" t="n"/>
-      <c r="C12" s="246" t="n"/>
-      <c r="D12" s="183" t="n"/>
-      <c r="E12" s="247" t="n"/>
-      <c r="F12" s="246" t="n"/>
-      <c r="G12" s="183" t="n"/>
-      <c r="H12" s="247" t="n"/>
-      <c r="I12" s="246" t="n"/>
-      <c r="J12" s="247" t="n"/>
-      <c r="K12" s="246" t="n"/>
-      <c r="L12" s="183" t="n"/>
-      <c r="M12" s="183" t="n"/>
+      <c r="C12" s="246">
+        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B12)=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B12))</f>
+        <v/>
+      </c>
+      <c r="D12" s="183">
+        <f>IF(C12="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B12)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B12)*Закрытые!$G$5:$G$200*Закрытые!$H$5:$H$200))/C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="247">
+        <f>IF(C12="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B12))</f>
+        <v/>
+      </c>
+      <c r="F12" s="246">
+        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B12)=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="183">
+        <f>IF(F12="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B12)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B12)*Закрытые!$J$5:$J$200*Закрытые!$K$5:$K$200))/F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="247">
+        <f>IF(F12="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$F$5:$F$200,$B12))</f>
+        <v/>
+      </c>
+      <c r="I12" s="246">
+        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B12)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B12),8))</f>
+        <v/>
+      </c>
+      <c r="J12" s="247">
+        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B12)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B12)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B12)*100,2))</f>
+        <v/>
+      </c>
+      <c r="K12" s="246">
+        <f>IF(MIN(N(C12),N(F12))&lt;=0,"",ROUND(MIN(N(C12),N(F12))*(N(G12)-N(D12)),8))</f>
+        <v/>
+      </c>
+      <c r="L12" s="183">
+        <f>IF(MIN(N(C12),N(F12))&lt;=0,"",IF(N(D12)=0,"",ROUND((N(G12)/N(D12)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M12" s="183">
+        <f>IF(OR(ROUND(N(C12)-N(F12),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C12)&gt;N(F12),(N(E12)-N(H12))/((N(C12)-N(F12))*(1-N(Ввод!$J$19)/100)),(N(H12)-N(E12))/((N(F12)-N(C12))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B4:M12"/>

--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -26,8 +26,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Торговля'!$A$1:$N$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ИТОГО Торговля'!$B$4:$M$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'ИТОГО Торговля'!$A$1:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Лэндинг'!$B$4:$M$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Лэндинг'!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Лэндинг'!$B$4:$M$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Лэндинг'!$A$1:$N$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ИТОГО Лэндинг'!$B$4:$M$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'ИТОГО Лэндинг'!$A$1:$N$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Пул'!$B$4:$K$12</definedName>
@@ -3661,7 +3661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M12"/>
+  <dimension ref="B1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -3677,6 +3677,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
@@ -3744,9 +3745,14 @@
           <t>Дельта 1</t>
         </is>
       </c>
-      <c r="M4" s="107" t="inlineStr">
+      <c r="M4" s="272" t="inlineStr">
         <is>
           <t>Дельта 2</t>
+        </is>
+      </c>
+      <c r="N4" s="273" t="inlineStr">
+        <is>
+          <t>Break even</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3763,7 @@
         </is>
       </c>
       <c r="C5" s="237" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D5" s="238" t="inlineStr">
         <is>
@@ -3769,37 +3775,39 @@
           <t>BNB/USDT</t>
         </is>
       </c>
-      <c r="F5" s="240" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="177" t="n">
-        <v>590</v>
-      </c>
-      <c r="H5" s="241" t="n">
-        <v>2950</v>
+      <c r="F5" s="240" t="n"/>
+      <c r="G5" s="177" t="n"/>
+      <c r="H5" s="271">
+        <f>IF(AND(ISNUMBER(F5),ISNUMBER(G5)),F5*G5,"")</f>
+        <v/>
       </c>
       <c r="I5" s="240" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" s="177" t="n">
-        <v>575</v>
-      </c>
-      <c r="K5" s="241" t="n">
-        <v>2875</v>
+        <v>598.8</v>
+      </c>
+      <c r="K5" s="271">
+        <f>IF(AND(ISNUMBER(I5),ISNUMBER(J5)),I5*J5,"")</f>
+        <v/>
       </c>
       <c r="L5" s="240">
-        <f>IF(AND(AND(ISNUMBER(F5),ISNUMBER(I5),ISNUMBER(H5),ISNUMBER(K5)),F5&gt;0,I5&gt;0,H5&lt;&gt;0),ROUND(MIN(F5,I5)*(K5/I5-H5/F5),8),"")</f>
-        <v/>
-      </c>
-      <c r="M5" s="177">
-        <f>IF(AND(AND(ISNUMBER(F5),ISNUMBER(I5),ISNUMBER(H5),ISNUMBER(K5)),F5&gt;0,I5&gt;0,H5&lt;&gt;0),ROUND((K5/I5)/(H5/F5)*100-100,2),"")</f>
+        <f>IF(COUNT(F5,I5)=0,"",N(F5)-N(I5))</f>
+        <v/>
+      </c>
+      <c r="M5" s="241">
+        <f>IF(COUNT(H5,K5)=0,"",N(K5)-N(H5))</f>
+        <v/>
+      </c>
+      <c r="N5" s="240">
+        <f>IF(AND(ISNUMBER(F5),ISNUMBER(G5),F5&gt;0,1-N(Ввод!$J$19)/100&gt;0),G5/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I5),ISNUMBER(J5),I5&gt;0),J5/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="244" t="inlineStr">
         <is>
-          <t>L-0002</t>
+          <t>L-0001</t>
         </is>
       </c>
       <c r="C6" s="243" t="n">
@@ -3807,7 +3815,7 @@
       </c>
       <c r="D6" s="244" t="inlineStr">
         <is>
-          <t>Bybit</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="E6" s="245" t="inlineStr">
@@ -3816,121 +3824,127 @@
         </is>
       </c>
       <c r="F6" s="246" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="G6" s="183" t="n">
-        <v>62000</v>
-      </c>
-      <c r="H6" s="247" t="n">
-        <v>15500</v>
-      </c>
-      <c r="I6" s="246" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J6" s="183" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K6" s="247" t="n">
-        <v>16000</v>
+        <v>62124</v>
+      </c>
+      <c r="H6" s="271">
+        <f>IF(AND(ISNUMBER(F6),ISNUMBER(G6)),F6*G6,"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="246" t="n"/>
+      <c r="J6" s="183" t="n"/>
+      <c r="K6" s="271">
+        <f>IF(AND(ISNUMBER(I6),ISNUMBER(J6)),I6*J6,"")</f>
+        <v/>
       </c>
       <c r="L6" s="246">
-        <f>IF(AND(AND(ISNUMBER(F6),ISNUMBER(I6),ISNUMBER(H6),ISNUMBER(K6)),F6&gt;0,I6&gt;0,H6&lt;&gt;0),ROUND(MIN(F6,I6)*(K6/I6-H6/F6),8),"")</f>
-        <v/>
-      </c>
-      <c r="M6" s="183">
-        <f>IF(AND(AND(ISNUMBER(F6),ISNUMBER(I6),ISNUMBER(H6),ISNUMBER(K6)),F6&gt;0,I6&gt;0,H6&lt;&gt;0),ROUND((K6/I6)/(H6/F6)*100-100,2),"")</f>
+        <f>IF(COUNT(F6,I6)=0,"",N(F6)-N(I6))</f>
+        <v/>
+      </c>
+      <c r="M6" s="247">
+        <f>IF(COUNT(H6,K6)=0,"",N(K6)-N(H6))</f>
+        <v/>
+      </c>
+      <c r="N6" s="246">
+        <f>IF(AND(ISNUMBER(F6),ISNUMBER(G6),F6&gt;0,1-N(Ввод!$J$19)/100&gt;0),G6/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I6),ISNUMBER(J6),I6&gt;0),J6/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="238" t="inlineStr">
         <is>
-          <t>L-0006</t>
+          <t>L-0004</t>
         </is>
       </c>
       <c r="C7" s="237" t="n">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="D7" s="238" t="inlineStr">
         <is>
-          <t>OKX</t>
+          <t>Binance</t>
         </is>
       </c>
       <c r="E7" s="239" t="inlineStr">
         <is>
-          <t>BTC/USDT</t>
-        </is>
-      </c>
-      <c r="F7" s="240" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G7" s="177" t="n">
-        <v>62500</v>
-      </c>
-      <c r="H7" s="241" t="n">
-        <v>6250</v>
+          <t>ETH/BTC</t>
+        </is>
+      </c>
+      <c r="F7" s="240" t="n"/>
+      <c r="G7" s="177" t="n"/>
+      <c r="H7" s="271">
+        <f>IF(AND(ISNUMBER(F7),ISNUMBER(G7)),F7*G7,"")</f>
+        <v/>
       </c>
       <c r="I7" s="240" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J7" s="177" t="n">
-        <v>63100</v>
-      </c>
-      <c r="K7" s="241" t="n">
-        <v>6310</v>
+        <v>0.052395</v>
+      </c>
+      <c r="K7" s="271">
+        <f>IF(AND(ISNUMBER(I7),ISNUMBER(J7)),I7*J7,"")</f>
+        <v/>
       </c>
       <c r="L7" s="240">
-        <f>IF(AND(AND(ISNUMBER(F7),ISNUMBER(I7),ISNUMBER(H7),ISNUMBER(K7)),F7&gt;0,I7&gt;0,H7&lt;&gt;0),ROUND(MIN(F7,I7)*(K7/I7-H7/F7),8),"")</f>
-        <v/>
-      </c>
-      <c r="M7" s="177">
-        <f>IF(AND(AND(ISNUMBER(F7),ISNUMBER(I7),ISNUMBER(H7),ISNUMBER(K7)),F7&gt;0,I7&gt;0,H7&lt;&gt;0),ROUND((K7/I7)/(H7/F7)*100-100,2),"")</f>
+        <f>IF(COUNT(F7,I7)=0,"",N(F7)-N(I7))</f>
+        <v/>
+      </c>
+      <c r="M7" s="241">
+        <f>IF(COUNT(H7,K7)=0,"",N(K7)-N(H7))</f>
+        <v/>
+      </c>
+      <c r="N7" s="240">
+        <f>IF(AND(ISNUMBER(F7),ISNUMBER(G7),F7&gt;0,1-N(Ввод!$J$19)/100&gt;0),G7/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I7),ISNUMBER(J7),I7&gt;0),J7/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="244" t="inlineStr">
         <is>
-          <t>L-0001</t>
+          <t>L-0002</t>
         </is>
       </c>
       <c r="C8" s="243" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D8" s="244" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Bybit</t>
         </is>
       </c>
       <c r="E8" s="245" t="inlineStr">
         <is>
-          <t>ETH/BTC</t>
+          <t>ETH/USDT</t>
         </is>
       </c>
       <c r="F8" s="246" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="183" t="n">
-        <v>0.0521</v>
-      </c>
-      <c r="H8" s="247" t="n">
-        <v>0.02605</v>
-      </c>
-      <c r="I8" s="246" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J8" s="183" t="n">
-        <v>0.0534</v>
-      </c>
-      <c r="K8" s="247" t="n">
-        <v>0.0267</v>
+        <v>3206.4</v>
+      </c>
+      <c r="H8" s="271">
+        <f>IF(AND(ISNUMBER(F8),ISNUMBER(G8)),F8*G8,"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="246" t="n"/>
+      <c r="J8" s="183" t="n"/>
+      <c r="K8" s="271">
+        <f>IF(AND(ISNUMBER(I8),ISNUMBER(J8)),I8*J8,"")</f>
+        <v/>
       </c>
       <c r="L8" s="246">
-        <f>IF(AND(AND(ISNUMBER(F8),ISNUMBER(I8),ISNUMBER(H8),ISNUMBER(K8)),F8&gt;0,I8&gt;0,H8&lt;&gt;0),ROUND(MIN(F8,I8)*(K8/I8-H8/F8),8),"")</f>
-        <v/>
-      </c>
-      <c r="M8" s="183">
-        <f>IF(AND(AND(ISNUMBER(F8),ISNUMBER(I8),ISNUMBER(H8),ISNUMBER(K8)),F8&gt;0,I8&gt;0,H8&lt;&gt;0),ROUND((K8/I8)/(H8/F8)*100-100,2),"")</f>
+        <f>IF(COUNT(F8,I8)=0,"",N(F8)-N(I8))</f>
+        <v/>
+      </c>
+      <c r="M8" s="247">
+        <f>IF(COUNT(H8,K8)=0,"",N(K8)-N(H8))</f>
+        <v/>
+      </c>
+      <c r="N8" s="246">
+        <f>IF(AND(ISNUMBER(F8),ISNUMBER(G8),F8&gt;0,1-N(Ввод!$J$19)/100&gt;0),G8/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I8),ISNUMBER(J8),I8&gt;0),J8/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
@@ -3941,7 +3955,7 @@
         </is>
       </c>
       <c r="C9" s="237" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D9" s="238" t="inlineStr">
         <is>
@@ -3950,48 +3964,50 @@
       </c>
       <c r="E9" s="239" t="inlineStr">
         <is>
-          <t>ETH/BTC</t>
+          <t>ETH/USDT</t>
         </is>
       </c>
       <c r="F9" s="240" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G9" s="177" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="H9" s="241" t="n">
-        <v>0.04144</v>
-      </c>
-      <c r="I9" s="240" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J9" s="177" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="K9" s="241" t="n">
-        <v>0.0424</v>
+        <v>3186.36</v>
+      </c>
+      <c r="H9" s="271">
+        <f>IF(AND(ISNUMBER(F9),ISNUMBER(G9)),F9*G9,"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="240" t="n"/>
+      <c r="J9" s="177" t="n"/>
+      <c r="K9" s="271">
+        <f>IF(AND(ISNUMBER(I9),ISNUMBER(J9)),I9*J9,"")</f>
+        <v/>
       </c>
       <c r="L9" s="240">
-        <f>IF(AND(AND(ISNUMBER(F9),ISNUMBER(I9),ISNUMBER(H9),ISNUMBER(K9)),F9&gt;0,I9&gt;0,H9&lt;&gt;0),ROUND(MIN(F9,I9)*(K9/I9-H9/F9),8),"")</f>
-        <v/>
-      </c>
-      <c r="M9" s="177">
-        <f>IF(AND(AND(ISNUMBER(F9),ISNUMBER(I9),ISNUMBER(H9),ISNUMBER(K9)),F9&gt;0,I9&gt;0,H9&lt;&gt;0),ROUND((K9/I9)/(H9/F9)*100-100,2),"")</f>
+        <f>IF(COUNT(F9,I9)=0,"",N(F9)-N(I9))</f>
+        <v/>
+      </c>
+      <c r="M9" s="241">
+        <f>IF(COUNT(H9,K9)=0,"",N(K9)-N(H9))</f>
+        <v/>
+      </c>
+      <c r="N9" s="240">
+        <f>IF(AND(ISNUMBER(F9),ISNUMBER(G9),F9&gt;0,1-N(Ввод!$J$19)/100&gt;0),G9/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I9),ISNUMBER(J9),I9&gt;0),J9/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="244" t="inlineStr">
         <is>
-          <t>L-0004</t>
+          <t>L-0008</t>
         </is>
       </c>
       <c r="C10" s="243" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="D10" s="244" t="inlineStr">
         <is>
-          <t>Binance</t>
+          <t>Bybit</t>
         </is>
       </c>
       <c r="E10" s="245" t="inlineStr">
@@ -4000,40 +4016,42 @@
         </is>
       </c>
       <c r="F10" s="246" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G10" s="183" t="n">
-        <v>3200</v>
-      </c>
-      <c r="H10" s="247" t="n">
-        <v>3840</v>
-      </c>
-      <c r="I10" s="246" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J10" s="183" t="n">
-        <v>3350</v>
-      </c>
-      <c r="K10" s="247" t="n">
-        <v>4020</v>
+        <v>3256.5</v>
+      </c>
+      <c r="H10" s="271">
+        <f>IF(AND(ISNUMBER(F10),ISNUMBER(G10)),F10*G10,"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="246" t="n"/>
+      <c r="J10" s="183" t="n"/>
+      <c r="K10" s="271">
+        <f>IF(AND(ISNUMBER(I10),ISNUMBER(J10)),I10*J10,"")</f>
+        <v/>
       </c>
       <c r="L10" s="246">
-        <f>IF(AND(AND(ISNUMBER(F10),ISNUMBER(I10),ISNUMBER(H10),ISNUMBER(K10)),F10&gt;0,I10&gt;0,H10&lt;&gt;0),ROUND(MIN(F10,I10)*(K10/I10-H10/F10),8),"")</f>
-        <v/>
-      </c>
-      <c r="M10" s="183">
-        <f>IF(AND(AND(ISNUMBER(F10),ISNUMBER(I10),ISNUMBER(H10),ISNUMBER(K10)),F10&gt;0,I10&gt;0,H10&lt;&gt;0),ROUND((K10/I10)/(H10/F10)*100-100,2),"")</f>
+        <f>IF(COUNT(F10,I10)=0,"",N(F10)-N(I10))</f>
+        <v/>
+      </c>
+      <c r="M10" s="247">
+        <f>IF(COUNT(H10,K10)=0,"",N(K10)-N(H10))</f>
+        <v/>
+      </c>
+      <c r="N10" s="246">
+        <f>IF(AND(ISNUMBER(F10),ISNUMBER(G10),F10&gt;0,1-N(Ввод!$J$19)/100&gt;0),G10/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I10),ISNUMBER(J10),I10&gt;0),J10/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="238" t="inlineStr">
         <is>
-          <t>L-0003</t>
+          <t>L-0009</t>
         </is>
       </c>
       <c r="C11" s="237" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
       <c r="D11" s="238" t="inlineStr">
         <is>
@@ -4042,86 +4060,246 @@
       </c>
       <c r="E11" s="239" t="inlineStr">
         <is>
-          <t>SOL/USDT</t>
-        </is>
-      </c>
-      <c r="F11" s="240" t="n">
-        <v>20</v>
-      </c>
-      <c r="G11" s="177" t="n">
-        <v>145</v>
-      </c>
-      <c r="H11" s="241" t="n">
-        <v>2900</v>
+          <t>ETH/USDT</t>
+        </is>
+      </c>
+      <c r="F11" s="240" t="n"/>
+      <c r="G11" s="177" t="n"/>
+      <c r="H11" s="271">
+        <f>IF(AND(ISNUMBER(F11),ISNUMBER(G11)),F11*G11,"")</f>
+        <v/>
       </c>
       <c r="I11" s="240" t="n">
-        <v>20</v>
+        <v>1.5</v>
       </c>
       <c r="J11" s="177" t="n">
-        <v>139</v>
-      </c>
-      <c r="K11" s="241" t="n">
-        <v>2780</v>
+        <v>3393.2</v>
+      </c>
+      <c r="K11" s="271">
+        <f>IF(AND(ISNUMBER(I11),ISNUMBER(J11)),I11*J11,"")</f>
+        <v/>
       </c>
       <c r="L11" s="240">
-        <f>IF(AND(AND(ISNUMBER(F11),ISNUMBER(I11),ISNUMBER(H11),ISNUMBER(K11)),F11&gt;0,I11&gt;0,H11&lt;&gt;0),ROUND(MIN(F11,I11)*(K11/I11-H11/F11),8),"")</f>
-        <v/>
-      </c>
-      <c r="M11" s="177">
-        <f>IF(AND(AND(ISNUMBER(F11),ISNUMBER(I11),ISNUMBER(H11),ISNUMBER(K11)),F11&gt;0,I11&gt;0,H11&lt;&gt;0),ROUND((K11/I11)/(H11/F11)*100-100,2),"")</f>
+        <f>IF(COUNT(F11,I11)=0,"",N(F11)-N(I11))</f>
+        <v/>
+      </c>
+      <c r="M11" s="241">
+        <f>IF(COUNT(H11,K11)=0,"",N(K11)-N(H11))</f>
+        <v/>
+      </c>
+      <c r="N11" s="240">
+        <f>IF(AND(ISNUMBER(F11),ISNUMBER(G11),F11&gt;0,1-N(Ввод!$J$19)/100&gt;0),G11/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I11),ISNUMBER(J11),I11&gt;0),J11/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="244" t="inlineStr">
         <is>
-          <t>L-0008</t>
+          <t>L-0010</t>
         </is>
       </c>
       <c r="C12" s="243" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="D12" s="244" t="inlineStr">
         <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="E12" s="245" t="inlineStr">
+        <is>
+          <t>SOL/USDT</t>
+        </is>
+      </c>
+      <c r="F12" s="246" t="n"/>
+      <c r="G12" s="183" t="n"/>
+      <c r="H12" s="271">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER(G12)),F12*G12,"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="246" t="n">
+        <v>30</v>
+      </c>
+      <c r="J12" s="183" t="n">
+        <v>149.7</v>
+      </c>
+      <c r="K12" s="271">
+        <f>IF(AND(ISNUMBER(I12),ISNUMBER(J12)),I12*J12,"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="246">
+        <f>IF(COUNT(F12,I12)=0,"",N(F12)-N(I12))</f>
+        <v/>
+      </c>
+      <c r="M12" s="247">
+        <f>IF(COUNT(H12,K12)=0,"",N(K12)-N(H12))</f>
+        <v/>
+      </c>
+      <c r="N12" s="246">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER(G12),F12&gt;0,1-N(Ввод!$J$19)/100&gt;0),G12/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I12),ISNUMBER(J12),I12&gt;0),J12/(1+N(Ввод!$J$19)/100),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="238" t="inlineStr">
+        <is>
+          <t>L-0011</t>
+        </is>
+      </c>
+      <c r="C13" s="237" t="n">
+        <v>46301</v>
+      </c>
+      <c r="D13" s="238" t="inlineStr">
+        <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="E12" s="245" t="inlineStr">
+      <c r="E13" s="239" t="inlineStr">
         <is>
           <t>SOL/USDT</t>
         </is>
       </c>
-      <c r="F12" s="246" t="n">
-        <v>15</v>
-      </c>
-      <c r="G12" s="183" t="n">
-        <v>142</v>
-      </c>
-      <c r="H12" s="247" t="n">
-        <v>2130</v>
-      </c>
-      <c r="I12" s="246" t="n">
-        <v>15</v>
-      </c>
-      <c r="J12" s="183" t="n">
-        <v>147</v>
-      </c>
-      <c r="K12" s="247" t="n">
-        <v>2205</v>
-      </c>
-      <c r="L12" s="246">
-        <f>IF(AND(AND(ISNUMBER(F12),ISNUMBER(I12),ISNUMBER(H12),ISNUMBER(K12)),F12&gt;0,I12&gt;0,H12&lt;&gt;0),ROUND(MIN(F12,I12)*(K12/I12-H12/F12),8),"")</f>
-        <v/>
-      </c>
-      <c r="M12" s="183">
-        <f>IF(AND(AND(ISNUMBER(F12),ISNUMBER(I12),ISNUMBER(H12),ISNUMBER(K12)),F12&gt;0,I12&gt;0,H12&lt;&gt;0),ROUND((K12/I12)/(H12/F12)*100-100,2),"")</f>
+      <c r="F13" s="240" t="n"/>
+      <c r="G13" s="177" t="n"/>
+      <c r="H13" s="271">
+        <f>IF(AND(ISNUMBER(F13),ISNUMBER(G13)),F13*G13,"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="240" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" s="177" t="n">
+        <v>151.696</v>
+      </c>
+      <c r="K13" s="271">
+        <f>IF(AND(ISNUMBER(I13),ISNUMBER(J13)),I13*J13,"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="240">
+        <f>IF(COUNT(F13,I13)=0,"",N(F13)-N(I13))</f>
+        <v/>
+      </c>
+      <c r="M13" s="241">
+        <f>IF(COUNT(H13,K13)=0,"",N(K13)-N(H13))</f>
+        <v/>
+      </c>
+      <c r="N13" s="240">
+        <f>IF(AND(ISNUMBER(F13),ISNUMBER(G13),F13&gt;0,1-N(Ввод!$J$19)/100&gt;0),G13/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I13),ISNUMBER(J13),I13&gt;0),J13/(1+N(Ввод!$J$19)/100),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="244" t="inlineStr">
+        <is>
+          <t>L-0012</t>
+        </is>
+      </c>
+      <c r="C14" s="243" t="n">
+        <v>46301</v>
+      </c>
+      <c r="D14" s="244" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="E14" s="245" t="inlineStr">
+        <is>
+          <t>SOL/USDT</t>
+        </is>
+      </c>
+      <c r="F14" s="246" t="n">
+        <v>25</v>
+      </c>
+      <c r="G14" s="183" t="n">
+        <v>146.292</v>
+      </c>
+      <c r="H14" s="271">
+        <f>IF(AND(ISNUMBER(F14),ISNUMBER(G14)),F14*G14,"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="246" t="n"/>
+      <c r="J14" s="183" t="n"/>
+      <c r="K14" s="271">
+        <f>IF(AND(ISNUMBER(I14),ISNUMBER(J14)),I14*J14,"")</f>
+        <v/>
+      </c>
+      <c r="L14" s="246">
+        <f>IF(COUNT(F14,I14)=0,"",N(F14)-N(I14))</f>
+        <v/>
+      </c>
+      <c r="M14" s="247">
+        <f>IF(COUNT(H14,K14)=0,"",N(K14)-N(H14))</f>
+        <v/>
+      </c>
+      <c r="N14" s="246">
+        <f>IF(AND(ISNUMBER(F14),ISNUMBER(G14),F14&gt;0,1-N(Ввод!$J$19)/100&gt;0),G14/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I14),ISNUMBER(J14),I14&gt;0),J14/(1+N(Ввод!$J$19)/100),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="238" t="n"/>
+      <c r="C15" s="237" t="n"/>
+      <c r="D15" s="238" t="n"/>
+      <c r="E15" s="239" t="n"/>
+      <c r="F15" s="240" t="n"/>
+      <c r="G15" s="177" t="n"/>
+      <c r="H15" s="271">
+        <f>IF(AND(ISNUMBER(F15),ISNUMBER(G15)),F15*G15,"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="240" t="n"/>
+      <c r="J15" s="177" t="n"/>
+      <c r="K15" s="271">
+        <f>IF(AND(ISNUMBER(I15),ISNUMBER(J15)),I15*J15,"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="240">
+        <f>IF(COUNT(F15,I15)=0,"",N(F15)-N(I15))</f>
+        <v/>
+      </c>
+      <c r="M15" s="241">
+        <f>IF(COUNT(H15,K15)=0,"",N(K15)-N(H15))</f>
+        <v/>
+      </c>
+      <c r="N15" s="240">
+        <f>IF(AND(ISNUMBER(F15),ISNUMBER(G15),F15&gt;0,1-N(Ввод!$J$19)/100&gt;0),G15/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I15),ISNUMBER(J15),I15&gt;0),J15/(1+N(Ввод!$J$19)/100),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="244" t="n"/>
+      <c r="C16" s="243" t="n"/>
+      <c r="D16" s="244" t="n"/>
+      <c r="E16" s="245" t="n"/>
+      <c r="F16" s="246" t="n"/>
+      <c r="G16" s="183" t="n"/>
+      <c r="H16" s="271">
+        <f>IF(AND(ISNUMBER(F16),ISNUMBER(G16)),F16*G16,"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="246" t="n"/>
+      <c r="J16" s="183" t="n"/>
+      <c r="K16" s="271">
+        <f>IF(AND(ISNUMBER(I16),ISNUMBER(J16)),I16*J16,"")</f>
+        <v/>
+      </c>
+      <c r="L16" s="246">
+        <f>IF(COUNT(F16,I16)=0,"",N(F16)-N(I16))</f>
+        <v/>
+      </c>
+      <c r="M16" s="247">
+        <f>IF(COUNT(H16,K16)=0,"",N(K16)-N(H16))</f>
+        <v/>
+      </c>
+      <c r="N16" s="246">
+        <f>IF(AND(ISNUMBER(F16),ISNUMBER(G16),F16&gt;0,1-N(Ввод!$J$19)/100&gt;0),G16/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I16),ISNUMBER(J16),I16&gt;0),J16/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:M12"/>
+  <autoFilter ref="B4:M16"/>
   <mergeCells count="1">
-    <mergeCell ref="B1:M2"/>
+    <mergeCell ref="B1:N2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -4227,43 +4405,46 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="239" t="inlineStr">
         <is>
-          <t>ETH/BTC</t>
-        </is>
-      </c>
-      <c r="C5" s="240" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D5" s="177" t="n">
-        <v>0.0521</v>
-      </c>
-      <c r="E5" s="241" t="n">
-        <v>0.02605</v>
-      </c>
-      <c r="F5" s="240" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="177" t="n">
-        <v>0.0534</v>
-      </c>
-      <c r="H5" s="241" t="n">
-        <v>0.0267</v>
-      </c>
-      <c r="I5" s="240">
-        <f>IF(AND(AND(ISNUMBER(C5),ISNUMBER(F5),ISNUMBER(E5),ISNUMBER(H5)),C5&gt;0,F5&gt;0,E5&lt;&gt;0),ROUND(MIN(C5,F5)*(H5/F5-E5/C5),8),"")</f>
-        <v/>
-      </c>
-      <c r="J5" s="241">
-        <f>IF(AND(AND(ISNUMBER(C5),ISNUMBER(F5),ISNUMBER(E5),ISNUMBER(H5)),C5&gt;0,F5&gt;0,E5&lt;&gt;0),ROUND((H5/F5)/(E5/C5)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="K5" s="240" t="n">
-        <v>0.00063</v>
-      </c>
-      <c r="L5" s="177" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="M5" s="177" t="n">
-        <v>0.0522</v>
+          <t>BNB/USDT</t>
+        </is>
+      </c>
+      <c r="C5" s="240">
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B5)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B5))</f>
+        <v/>
+      </c>
+      <c r="D5" s="177">
+        <f>IF(C5="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B5)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="241">
+        <f>IF(C5="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B5))</f>
+        <v/>
+      </c>
+      <c r="F5" s="240">
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B5)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="177">
+        <f>IF(F5="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B5)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="241">
+        <f>IF(F5="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B5))</f>
+        <v/>
+      </c>
+      <c r="I5" s="240" t="n"/>
+      <c r="J5" s="241" t="n"/>
+      <c r="K5" s="240">
+        <f>IF(MIN(N(C5),N(F5))&lt;=0,"",ROUND(MIN(N(C5),N(F5))*(N(G5)-N(D5)),8))</f>
+        <v/>
+      </c>
+      <c r="L5" s="177">
+        <f>IF(MIN(N(C5),N(F5))&lt;=0,"",IF(N(D5)=0,"",ROUND((N(G5)/N(D5)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M5" s="177">
+        <f>IF(OR(ROUND(N(C5)-N(F5),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C5)&gt;N(F5),(N(E5)-N(H5))/((N(C5)-N(F5))*(1-N(Ввод!$J$19)/100)),(N(H5)-N(E5))/((N(F5)-N(C5))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -4272,82 +4453,88 @@
           <t>BTC/USDT</t>
         </is>
       </c>
-      <c r="C6" s="246" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D6" s="183" t="n">
-        <v>62000</v>
-      </c>
-      <c r="E6" s="247" t="n">
-        <v>15500</v>
-      </c>
-      <c r="F6" s="246" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G6" s="183" t="n">
-        <v>64000</v>
-      </c>
-      <c r="H6" s="247" t="n">
-        <v>16000</v>
-      </c>
-      <c r="I6" s="246">
-        <f>IF(AND(AND(ISNUMBER(C6),ISNUMBER(F6),ISNUMBER(E6),ISNUMBER(H6)),C6&gt;0,F6&gt;0,E6&lt;&gt;0),ROUND(MIN(C6,F6)*(H6/F6-E6/C6),8),"")</f>
-        <v/>
-      </c>
-      <c r="J6" s="247">
-        <f>IF(AND(AND(ISNUMBER(C6),ISNUMBER(F6),ISNUMBER(E6),ISNUMBER(H6)),C6&gt;0,F6&gt;0,E6&lt;&gt;0),ROUND((H6/F6)/(E6/C6)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="K6" s="246" t="n">
-        <v>485</v>
-      </c>
-      <c r="L6" s="183" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="M6" s="183" t="n">
-        <v>62155</v>
+      <c r="C6" s="246">
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B6)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B6))</f>
+        <v/>
+      </c>
+      <c r="D6" s="183">
+        <f>IF(C6="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B6)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="247">
+        <f>IF(C6="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B6))</f>
+        <v/>
+      </c>
+      <c r="F6" s="246">
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B6)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="183">
+        <f>IF(F6="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B6)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="247">
+        <f>IF(F6="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B6))</f>
+        <v/>
+      </c>
+      <c r="I6" s="246" t="n"/>
+      <c r="J6" s="247" t="n"/>
+      <c r="K6" s="246">
+        <f>IF(MIN(N(C6),N(F6))&lt;=0,"",ROUND(MIN(N(C6),N(F6))*(N(G6)-N(D6)),8))</f>
+        <v/>
+      </c>
+      <c r="L6" s="183">
+        <f>IF(MIN(N(C6),N(F6))&lt;=0,"",IF(N(D6)=0,"",ROUND((N(G6)/N(D6)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M6" s="183">
+        <f>IF(OR(ROUND(N(C6)-N(F6),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C6)&gt;N(F6),(N(E6)-N(H6))/((N(C6)-N(F6))*(1-N(Ввод!$J$19)/100)),(N(H6)-N(E6))/((N(F6)-N(C6))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="239" t="inlineStr">
         <is>
-          <t>SOL/USDT</t>
-        </is>
-      </c>
-      <c r="C7" s="240" t="n">
-        <v>20</v>
-      </c>
-      <c r="D7" s="177" t="n">
-        <v>145</v>
-      </c>
-      <c r="E7" s="241" t="n">
-        <v>2900</v>
-      </c>
-      <c r="F7" s="240" t="n">
-        <v>20</v>
-      </c>
-      <c r="G7" s="177" t="n">
-        <v>139</v>
-      </c>
-      <c r="H7" s="241" t="n">
-        <v>2780</v>
-      </c>
-      <c r="I7" s="240">
-        <f>IF(AND(AND(ISNUMBER(C7),ISNUMBER(F7),ISNUMBER(E7),ISNUMBER(H7)),C7&gt;0,F7&gt;0,E7&lt;&gt;0),ROUND(MIN(C7,F7)*(H7/F7-E7/C7),8),"")</f>
-        <v/>
-      </c>
-      <c r="J7" s="241">
-        <f>IF(AND(AND(ISNUMBER(C7),ISNUMBER(F7),ISNUMBER(E7),ISNUMBER(H7)),C7&gt;0,F7&gt;0,E7&lt;&gt;0),ROUND((H7/F7)/(E7/C7)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="K7" s="240" t="n">
-        <v>-125</v>
-      </c>
-      <c r="L7" s="177" t="n">
-        <v>-4.31</v>
-      </c>
-      <c r="M7" s="177" t="n">
-        <v>145.3</v>
+          <t>ETH/BTC</t>
+        </is>
+      </c>
+      <c r="C7" s="240">
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B7)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B7))</f>
+        <v/>
+      </c>
+      <c r="D7" s="177">
+        <f>IF(C7="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B7)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="241">
+        <f>IF(C7="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B7))</f>
+        <v/>
+      </c>
+      <c r="F7" s="240">
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B7)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="177">
+        <f>IF(F7="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B7)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="241">
+        <f>IF(F7="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B7))</f>
+        <v/>
+      </c>
+      <c r="I7" s="240" t="n"/>
+      <c r="J7" s="241" t="n"/>
+      <c r="K7" s="240">
+        <f>IF(MIN(N(C7),N(F7))&lt;=0,"",ROUND(MIN(N(C7),N(F7))*(N(G7)-N(D7)),8))</f>
+        <v/>
+      </c>
+      <c r="L7" s="177">
+        <f>IF(MIN(N(C7),N(F7))&lt;=0,"",IF(N(D7)=0,"",ROUND((N(G7)/N(D7)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M7" s="177">
+        <f>IF(OR(ROUND(N(C7)-N(F7),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C7)&gt;N(F7),(N(E7)-N(H7))/((N(C7)-N(F7))*(1-N(Ввод!$J$19)/100)),(N(H7)-N(E7))/((N(F7)-N(C7))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -4356,208 +4543,211 @@
           <t>ETH/USDT</t>
         </is>
       </c>
-      <c r="C8" s="246" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D8" s="183" t="n">
-        <v>3200</v>
-      </c>
-      <c r="E8" s="247" t="n">
-        <v>3840</v>
-      </c>
-      <c r="F8" s="246" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G8" s="183" t="n">
-        <v>3350</v>
-      </c>
-      <c r="H8" s="247" t="n">
-        <v>4020</v>
-      </c>
-      <c r="I8" s="246">
-        <f>IF(AND(AND(ISNUMBER(C8),ISNUMBER(F8),ISNUMBER(E8),ISNUMBER(H8)),C8&gt;0,F8&gt;0,E8&lt;&gt;0),ROUND(MIN(C8,F8)*(H8/F8-E8/C8),8),"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="247">
-        <f>IF(AND(AND(ISNUMBER(C8),ISNUMBER(F8),ISNUMBER(E8),ISNUMBER(H8)),C8&gt;0,F8&gt;0,E8&lt;&gt;0),ROUND((H8/F8)/(E8/C8)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="K8" s="246" t="n">
-        <v>175</v>
-      </c>
-      <c r="L8" s="183" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="M8" s="183" t="n">
-        <v>3203.84</v>
+      <c r="C8" s="246">
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B8)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B8))</f>
+        <v/>
+      </c>
+      <c r="D8" s="183">
+        <f>IF(C8="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B8)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="247">
+        <f>IF(C8="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B8))</f>
+        <v/>
+      </c>
+      <c r="F8" s="246">
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B8)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="183">
+        <f>IF(F8="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B8)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="247">
+        <f>IF(F8="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B8))</f>
+        <v/>
+      </c>
+      <c r="I8" s="246" t="n"/>
+      <c r="J8" s="247" t="n"/>
+      <c r="K8" s="246">
+        <f>IF(MIN(N(C8),N(F8))&lt;=0,"",ROUND(MIN(N(C8),N(F8))*(N(G8)-N(D8)),8))</f>
+        <v/>
+      </c>
+      <c r="L8" s="183">
+        <f>IF(MIN(N(C8),N(F8))&lt;=0,"",IF(N(D8)=0,"",ROUND((N(G8)/N(D8)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M8" s="183">
+        <f>IF(OR(ROUND(N(C8)-N(F8),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C8)&gt;N(F8),(N(E8)-N(H8))/((N(C8)-N(F8))*(1-N(Ввод!$J$19)/100)),(N(H8)-N(E8))/((N(F8)-N(C8))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="239" t="inlineStr">
         <is>
-          <t>BNB/USDT</t>
-        </is>
-      </c>
-      <c r="C9" s="240" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="177" t="n">
-        <v>590</v>
-      </c>
-      <c r="E9" s="241" t="n">
-        <v>2950</v>
-      </c>
-      <c r="F9" s="240" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="177" t="n">
-        <v>575</v>
-      </c>
-      <c r="H9" s="241" t="n">
-        <v>2875</v>
-      </c>
-      <c r="I9" s="240">
-        <f>IF(AND(AND(ISNUMBER(C9),ISNUMBER(F9),ISNUMBER(E9),ISNUMBER(H9)),C9&gt;0,F9&gt;0,E9&lt;&gt;0),ROUND(MIN(C9,F9)*(H9/F9-E9/C9),8),"")</f>
-        <v/>
-      </c>
-      <c r="J9" s="241">
-        <f>IF(AND(AND(ISNUMBER(C9),ISNUMBER(F9),ISNUMBER(E9),ISNUMBER(H9)),C9&gt;0,F9&gt;0,E9&lt;&gt;0),ROUND((H9/F9)/(E9/C9)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="K9" s="240" t="n">
-        <v>-80</v>
-      </c>
-      <c r="L9" s="177" t="n">
-        <v>-2.71</v>
-      </c>
-      <c r="M9" s="177" t="n">
-        <v>590.6</v>
+          <t>SOL/USDT</t>
+        </is>
+      </c>
+      <c r="C9" s="240">
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B9)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B9))</f>
+        <v/>
+      </c>
+      <c r="D9" s="177">
+        <f>IF(C9="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B9)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="241">
+        <f>IF(C9="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B9))</f>
+        <v/>
+      </c>
+      <c r="F9" s="240">
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B9)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="177">
+        <f>IF(F9="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B9)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="241">
+        <f>IF(F9="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B9))</f>
+        <v/>
+      </c>
+      <c r="I9" s="240" t="n"/>
+      <c r="J9" s="241" t="n"/>
+      <c r="K9" s="240">
+        <f>IF(MIN(N(C9),N(F9))&lt;=0,"",ROUND(MIN(N(C9),N(F9))*(N(G9)-N(D9)),8))</f>
+        <v/>
+      </c>
+      <c r="L9" s="177">
+        <f>IF(MIN(N(C9),N(F9))&lt;=0,"",IF(N(D9)=0,"",ROUND((N(G9)/N(D9)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M9" s="177">
+        <f>IF(OR(ROUND(N(C9)-N(F9),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C9)&gt;N(F9),(N(E9)-N(H9))/((N(C9)-N(F9))*(1-N(Ввод!$J$19)/100)),(N(H9)-N(E9))/((N(F9)-N(C9))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="245" t="inlineStr">
-        <is>
-          <t>BTC/USDT</t>
-        </is>
-      </c>
-      <c r="C10" s="246" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D10" s="183" t="n">
-        <v>62500</v>
-      </c>
-      <c r="E10" s="247" t="n">
-        <v>6250</v>
-      </c>
-      <c r="F10" s="246" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G10" s="183" t="n">
-        <v>63100</v>
-      </c>
-      <c r="H10" s="247" t="n">
-        <v>6310</v>
-      </c>
-      <c r="I10" s="246">
-        <f>IF(AND(AND(ISNUMBER(C10),ISNUMBER(F10),ISNUMBER(E10),ISNUMBER(H10)),C10&gt;0,F10&gt;0,E10&lt;&gt;0),ROUND(MIN(C10,F10)*(H10/F10-E10/C10),8),"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="247">
-        <f>IF(AND(AND(ISNUMBER(C10),ISNUMBER(F10),ISNUMBER(E10),ISNUMBER(H10)),C10&gt;0,F10&gt;0,E10&lt;&gt;0),ROUND((H10/F10)/(E10/C10)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="K10" s="246" t="n">
-        <v>55</v>
-      </c>
-      <c r="L10" s="183" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="M10" s="183" t="n">
-        <v>62512.5</v>
+      <c r="B10" s="245" t="n"/>
+      <c r="C10" s="246">
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B10)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B10))</f>
+        <v/>
+      </c>
+      <c r="D10" s="183">
+        <f>IF(C10="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B10)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="247">
+        <f>IF(C10="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B10))</f>
+        <v/>
+      </c>
+      <c r="F10" s="246">
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B10)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="183">
+        <f>IF(F10="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B10)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="247">
+        <f>IF(F10="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B10))</f>
+        <v/>
+      </c>
+      <c r="I10" s="246" t="n"/>
+      <c r="J10" s="247" t="n"/>
+      <c r="K10" s="246">
+        <f>IF(MIN(N(C10),N(F10))&lt;=0,"",ROUND(MIN(N(C10),N(F10))*(N(G10)-N(D10)),8))</f>
+        <v/>
+      </c>
+      <c r="L10" s="183">
+        <f>IF(MIN(N(C10),N(F10))&lt;=0,"",IF(N(D10)=0,"",ROUND((N(G10)/N(D10)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M10" s="183">
+        <f>IF(OR(ROUND(N(C10)-N(F10),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C10)&gt;N(F10),(N(E10)-N(H10))/((N(C10)-N(F10))*(1-N(Ввод!$J$19)/100)),(N(H10)-N(E10))/((N(F10)-N(C10))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="239" t="inlineStr">
-        <is>
-          <t>ETH/BTC</t>
-        </is>
-      </c>
-      <c r="C11" s="240" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D11" s="177" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="E11" s="241" t="n">
-        <v>0.04144</v>
-      </c>
-      <c r="F11" s="240" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G11" s="177" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="H11" s="241" t="n">
-        <v>0.0424</v>
-      </c>
-      <c r="I11" s="240">
-        <f>IF(AND(AND(ISNUMBER(C11),ISNUMBER(F11),ISNUMBER(E11),ISNUMBER(H11)),C11&gt;0,F11&gt;0,E11&lt;&gt;0),ROUND(MIN(C11,F11)*(H11/F11-E11/C11),8),"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="241">
-        <f>IF(AND(AND(ISNUMBER(C11),ISNUMBER(F11),ISNUMBER(E11),ISNUMBER(H11)),C11&gt;0,F11&gt;0,E11&lt;&gt;0),ROUND((H11/F11)/(E11/C11)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="K11" s="240" t="n">
-        <v>0.00092</v>
-      </c>
-      <c r="L11" s="177" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="M11" s="177" t="n">
-        <v>0.05185</v>
+      <c r="B11" s="239" t="n"/>
+      <c r="C11" s="240">
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B11)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B11))</f>
+        <v/>
+      </c>
+      <c r="D11" s="177">
+        <f>IF(C11="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B11)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="241">
+        <f>IF(C11="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B11))</f>
+        <v/>
+      </c>
+      <c r="F11" s="240">
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B11)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="177">
+        <f>IF(F11="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B11)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="241">
+        <f>IF(F11="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B11))</f>
+        <v/>
+      </c>
+      <c r="I11" s="240" t="n"/>
+      <c r="J11" s="241" t="n"/>
+      <c r="K11" s="240">
+        <f>IF(MIN(N(C11),N(F11))&lt;=0,"",ROUND(MIN(N(C11),N(F11))*(N(G11)-N(D11)),8))</f>
+        <v/>
+      </c>
+      <c r="L11" s="177">
+        <f>IF(MIN(N(C11),N(F11))&lt;=0,"",IF(N(D11)=0,"",ROUND((N(G11)/N(D11)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M11" s="177">
+        <f>IF(OR(ROUND(N(C11)-N(F11),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C11)&gt;N(F11),(N(E11)-N(H11))/((N(C11)-N(F11))*(1-N(Ввод!$J$19)/100)),(N(H11)-N(E11))/((N(F11)-N(C11))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="245" t="inlineStr">
-        <is>
-          <t>SOL/USDT</t>
-        </is>
-      </c>
-      <c r="C12" s="246" t="n">
-        <v>15</v>
-      </c>
-      <c r="D12" s="183" t="n">
-        <v>142</v>
-      </c>
-      <c r="E12" s="247" t="n">
-        <v>2130</v>
-      </c>
-      <c r="F12" s="246" t="n">
-        <v>15</v>
-      </c>
-      <c r="G12" s="183" t="n">
-        <v>147</v>
-      </c>
-      <c r="H12" s="247" t="n">
-        <v>2205</v>
-      </c>
-      <c r="I12" s="246">
-        <f>IF(AND(AND(ISNUMBER(C12),ISNUMBER(F12),ISNUMBER(E12),ISNUMBER(H12)),C12&gt;0,F12&gt;0,E12&lt;&gt;0),ROUND(MIN(C12,F12)*(H12/F12-E12/C12),8),"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="247">
-        <f>IF(AND(AND(ISNUMBER(C12),ISNUMBER(F12),ISNUMBER(E12),ISNUMBER(H12)),C12&gt;0,F12&gt;0,E12&lt;&gt;0),ROUND((H12/F12)/(E12/C12)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="K12" s="246" t="n">
-        <v>70</v>
-      </c>
-      <c r="L12" s="183" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="M12" s="183" t="n">
-        <v>142.28</v>
+      <c r="B12" s="245" t="n"/>
+      <c r="C12" s="246">
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B12)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B12))</f>
+        <v/>
+      </c>
+      <c r="D12" s="183">
+        <f>IF(C12="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B12)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="247">
+        <f>IF(C12="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B12))</f>
+        <v/>
+      </c>
+      <c r="F12" s="246">
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B12)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="183">
+        <f>IF(F12="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B12)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="247">
+        <f>IF(F12="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B12))</f>
+        <v/>
+      </c>
+      <c r="I12" s="246" t="n"/>
+      <c r="J12" s="247" t="n"/>
+      <c r="K12" s="246">
+        <f>IF(MIN(N(C12),N(F12))&lt;=0,"",ROUND(MIN(N(C12),N(F12))*(N(G12)-N(D12)),8))</f>
+        <v/>
+      </c>
+      <c r="L12" s="183">
+        <f>IF(MIN(N(C12),N(F12))&lt;=0,"",IF(N(D12)=0,"",ROUND((N(G12)/N(D12)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M12" s="183">
+        <f>IF(OR(ROUND(N(C12)-N(F12),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C12)&gt;N(F12),(N(E12)-N(H12))/((N(C12)-N(F12))*(1-N(Ввод!$J$19)/100)),(N(H12)-N(E12))/((N(F12)-N(C12))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -22,11 +22,11 @@
     <definedName name="Список_Протокол">OFFSET(Справочники!$B$5,0,0,MAX(1,COUNTA(Справочники!$B$5:$B$104)),1)</definedName>
     <definedName name="Список_Действие_Торговля">OFFSET(Справочники!$C$5,0,0,MAX(1,COUNTA(Справочники!$C$5:$C$104)),1)</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Ввод'!$A$1:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Торговля'!$B$4:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Торговля'!$B$4:$N$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Торговля'!$A$1:$N$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ИТОГО Торговля'!$B$4:$M$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'ИТОГО Торговля'!$A$1:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Лэндинг'!$B$4:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Лэндинг'!$B$4:$N$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Лэндинг'!$A$1:$N$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ИТОГО Лэндинг'!$B$4:$M$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'ИТОГО Лэндинг'!$A$1:$N$13</definedName>
@@ -34,8 +34,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Пул'!$A$1:$K$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'ИТОГО ПУЛ'!$B$4:$L$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'ИТОГО ПУЛ'!$A$1:$M$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Закрытые'!$B$4:$Q$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Закрытые'!$A$1:$R$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Закрытые'!$B$4:$O$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Закрытые'!$A$1:$P$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'ИТОГО'!$B$4:$M$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'ИТОГО'!$A$1:$N$13</definedName>
   </definedNames>
@@ -1482,12 +1482,20 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FDE9D9"/>
           <bgColor rgb="00FDE9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDE9D9"/>
+          <bgColor rgb="FFFDE9D9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2518,7 +2526,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
@@ -3138,7 +3146,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:M16"/>
+  <autoFilter ref="B4:N16"/>
   <mergeCells count="1">
     <mergeCell ref="B1:N2"/>
   </mergeCells>
@@ -3165,7 +3173,7 @@
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -3174,7 +3182,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
@@ -3255,35 +3263,35 @@
         </is>
       </c>
       <c r="C5" s="240">
-        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B5)=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B5))</f>
+        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="D5" s="177">
-        <f>IF(C5="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B5)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B5)*Закрытые!$G$5:$G$200*Закрытые!$H$5:$H$200))/C5)</f>
+        <f>IF(C5="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B5)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B5)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C5)</f>
         <v/>
       </c>
       <c r="E5" s="241">
-        <f>IF(C5="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B5))</f>
+        <f>IF(C5="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="F5" s="240">
-        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B5)=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B5))</f>
+        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="G5" s="177">
-        <f>IF(F5="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B5)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B5)*Закрытые!$J$5:$J$200*Закрытые!$K$5:$K$200))/F5)</f>
+        <f>IF(F5="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B5)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B5)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F5)</f>
         <v/>
       </c>
       <c r="H5" s="241">
-        <f>IF(F5="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$F$5:$F$200,$B5))</f>
+        <f>IF(F5="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="I5" s="240">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B5)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B5),8))</f>
+        <f>IF($B5="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B5)+COUNTIFS(Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="J5" s="241">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B5)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B5)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B5)*100,2))</f>
+        <f>IF($B5="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B5)+COUNTIFS(Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="K5" s="240">
@@ -3306,35 +3314,35 @@
         </is>
       </c>
       <c r="C6" s="246">
-        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B6)=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B6))</f>
+        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="D6" s="183">
-        <f>IF(C6="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B6)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B6)*Закрытые!$G$5:$G$200*Закрытые!$H$5:$H$200))/C6)</f>
+        <f>IF(C6="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B6)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B6)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C6)</f>
         <v/>
       </c>
       <c r="E6" s="247">
-        <f>IF(C6="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B6))</f>
+        <f>IF(C6="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="F6" s="246">
-        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B6)=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B6))</f>
+        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="G6" s="183">
-        <f>IF(F6="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B6)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B6)*Закрытые!$J$5:$J$200*Закрытые!$K$5:$K$200))/F6)</f>
+        <f>IF(F6="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B6)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B6)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F6)</f>
         <v/>
       </c>
       <c r="H6" s="247">
-        <f>IF(F6="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$F$5:$F$200,$B6))</f>
+        <f>IF(F6="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="I6" s="246">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B6)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B6),8))</f>
+        <f>IF($B6="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B6)+COUNTIFS(Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="J6" s="247">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B6)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B6)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B6)*100,2))</f>
+        <f>IF($B6="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B6)+COUNTIFS(Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="K6" s="246">
@@ -3357,35 +3365,35 @@
         </is>
       </c>
       <c r="C7" s="240">
-        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B7)=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B7))</f>
+        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="D7" s="177">
-        <f>IF(C7="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B7)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B7)*Закрытые!$G$5:$G$200*Закрытые!$H$5:$H$200))/C7)</f>
+        <f>IF(C7="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B7)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B7)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C7)</f>
         <v/>
       </c>
       <c r="E7" s="241">
-        <f>IF(C7="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B7))</f>
+        <f>IF(C7="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="F7" s="240">
-        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B7)=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B7))</f>
+        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="G7" s="177">
-        <f>IF(F7="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B7)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B7)*Закрытые!$J$5:$J$200*Закрытые!$K$5:$K$200))/F7)</f>
+        <f>IF(F7="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B7)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B7)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F7)</f>
         <v/>
       </c>
       <c r="H7" s="241">
-        <f>IF(F7="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$F$5:$F$200,$B7))</f>
+        <f>IF(F7="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="I7" s="240">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B7)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B7),8))</f>
+        <f>IF($B7="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B7)+COUNTIFS(Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="J7" s="241">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B7)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B7)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B7)*100,2))</f>
+        <f>IF($B7="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B7)+COUNTIFS(Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="K7" s="240">
@@ -3408,35 +3416,35 @@
         </is>
       </c>
       <c r="C8" s="246">
-        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B8)=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B8))</f>
+        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="D8" s="183">
-        <f>IF(C8="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B8)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B8)*Закрытые!$G$5:$G$200*Закрытые!$H$5:$H$200))/C8)</f>
+        <f>IF(C8="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B8)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B8)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C8)</f>
         <v/>
       </c>
       <c r="E8" s="247">
-        <f>IF(C8="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B8))</f>
+        <f>IF(C8="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="F8" s="246">
-        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B8)=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B8))</f>
+        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="G8" s="183">
-        <f>IF(F8="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B8)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B8)*Закрытые!$J$5:$J$200*Закрытые!$K$5:$K$200))/F8)</f>
+        <f>IF(F8="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B8)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B8)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F8)</f>
         <v/>
       </c>
       <c r="H8" s="247">
-        <f>IF(F8="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$F$5:$F$200,$B8))</f>
+        <f>IF(F8="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="I8" s="246">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B8)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B8),8))</f>
+        <f>IF($B8="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B8)+COUNTIFS(Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="J8" s="247">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B8)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B8)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B8)*100,2))</f>
+        <f>IF($B8="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B8)+COUNTIFS(Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="K8" s="246">
@@ -3459,35 +3467,35 @@
         </is>
       </c>
       <c r="C9" s="240">
-        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B9)=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B9))</f>
+        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="D9" s="177">
-        <f>IF(C9="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B9)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B9)*Закрытые!$G$5:$G$200*Закрытые!$H$5:$H$200))/C9)</f>
+        <f>IF(C9="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B9)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B9)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C9)</f>
         <v/>
       </c>
       <c r="E9" s="241">
-        <f>IF(C9="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B9))</f>
+        <f>IF(C9="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="F9" s="240">
-        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B9)=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B9))</f>
+        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="G9" s="177">
-        <f>IF(F9="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B9)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B9)*Закрытые!$J$5:$J$200*Закрытые!$K$5:$K$200))/F9)</f>
+        <f>IF(F9="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B9)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B9)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F9)</f>
         <v/>
       </c>
       <c r="H9" s="241">
-        <f>IF(F9="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$F$5:$F$200,$B9))</f>
+        <f>IF(F9="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="I9" s="240">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B9)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B9),8))</f>
+        <f>IF($B9="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B9)+COUNTIFS(Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="J9" s="241">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B9)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B9)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B9)*100,2))</f>
+        <f>IF($B9="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B9)+COUNTIFS(Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="K9" s="240">
@@ -3506,35 +3514,35 @@
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="245" t="n"/>
       <c r="C10" s="246">
-        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B10)=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B10))</f>
+        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="D10" s="183">
-        <f>IF(C10="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B10)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B10)*Закрытые!$G$5:$G$200*Закрытые!$H$5:$H$200))/C10)</f>
+        <f>IF(C10="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B10)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B10)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C10)</f>
         <v/>
       </c>
       <c r="E10" s="247">
-        <f>IF(C10="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B10))</f>
+        <f>IF(C10="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="F10" s="246">
-        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B10)=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B10))</f>
+        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="G10" s="183">
-        <f>IF(F10="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B10)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B10)*Закрытые!$J$5:$J$200*Закрытые!$K$5:$K$200))/F10)</f>
+        <f>IF(F10="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B10)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B10)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F10)</f>
         <v/>
       </c>
       <c r="H10" s="247">
-        <f>IF(F10="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$F$5:$F$200,$B10))</f>
+        <f>IF(F10="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="I10" s="246">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B10)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B10),8))</f>
+        <f>IF($B10="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B10)+COUNTIFS(Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="J10" s="247">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B10)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B10)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B10)*100,2))</f>
+        <f>IF($B10="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B10)+COUNTIFS(Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="K10" s="246">
@@ -3553,35 +3561,35 @@
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="239" t="n"/>
       <c r="C11" s="240">
-        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B11)=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B11))</f>
+        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="D11" s="177">
-        <f>IF(C11="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B11)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B11)*Закрытые!$G$5:$G$200*Закрытые!$H$5:$H$200))/C11)</f>
+        <f>IF(C11="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B11)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B11)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C11)</f>
         <v/>
       </c>
       <c r="E11" s="241">
-        <f>IF(C11="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B11))</f>
+        <f>IF(C11="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="F11" s="240">
-        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B11)=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B11))</f>
+        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="G11" s="177">
-        <f>IF(F11="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B11)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B11)*Закрытые!$J$5:$J$200*Закрытые!$K$5:$K$200))/F11)</f>
+        <f>IF(F11="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B11)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B11)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F11)</f>
         <v/>
       </c>
       <c r="H11" s="241">
-        <f>IF(F11="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$F$5:$F$200,$B11))</f>
+        <f>IF(F11="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="I11" s="240">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B11)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B11),8))</f>
+        <f>IF($B11="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B11)+COUNTIFS(Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="J11" s="241">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B11)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B11)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B11)*100,2))</f>
+        <f>IF($B11="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B11)+COUNTIFS(Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="K11" s="240">
@@ -3600,35 +3608,35 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="245" t="n"/>
       <c r="C12" s="246">
-        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B12)=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$G$5:$G$200,Закрытые!$F$5:$F$200,$B12))</f>
+        <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="D12" s="183">
-        <f>IF(C12="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B12)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B12)*Закрытые!$G$5:$G$200*Закрытые!$H$5:$H$200))/C12)</f>
+        <f>IF(C12="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B12)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B12)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C12)</f>
         <v/>
       </c>
       <c r="E12" s="247">
-        <f>IF(C12="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B12))</f>
+        <f>IF(C12="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="F12" s="246">
-        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B12)=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$J$5:$J$200,Закрытые!$F$5:$F$200,$B12))</f>
+        <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="G12" s="183">
-        <f>IF(F12="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B12)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$F$5:$F$200=$B12)*Закрытые!$J$5:$J$200*Закрытые!$K$5:$K$200))/F12)</f>
+        <f>IF(F12="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B12)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B12)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F12)</f>
         <v/>
       </c>
       <c r="H12" s="247">
-        <f>IF(F12="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$F$5:$F$200,$B12))</f>
+        <f>IF(F12="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="I12" s="246">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B12)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B12),8))</f>
+        <f>IF($B12="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B12)+COUNTIFS(Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="J12" s="247">
-        <f>IF(COUNTIFS(Закрытые!$F$5:$F$200,$B12)=0,"",ROUND(SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$F$5:$F$200,$B12)/SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$F$5:$F$200,$B12)*100,2))</f>
+        <f>IF($B12="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B12)+COUNTIFS(Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
       <c r="K12" s="246">
@@ -3677,7 +3685,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
@@ -4297,10 +4305,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:M16"/>
+  <autoFilter ref="B4:N16"/>
   <mergeCells count="1">
     <mergeCell ref="B1:N2"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5:N200">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND($B5&lt;&gt;"",COUNTIF(Закрытые!$B$5:$B$200,$B5)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -4319,7 +4332,7 @@
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -4328,7 +4341,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
@@ -4409,31 +4422,37 @@
         </is>
       </c>
       <c r="C5" s="240">
-        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B5)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B5))</f>
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="D5" s="177">
-        <f>IF(C5="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B5)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C5)</f>
+        <f>IF(C5="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B5)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B5)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C5)</f>
         <v/>
       </c>
       <c r="E5" s="241">
-        <f>IF(C5="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B5))</f>
+        <f>IF(C5="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="F5" s="240">
-        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B5)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B5))</f>
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="G5" s="177">
-        <f>IF(F5="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B5)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F5)</f>
+        <f>IF(F5="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B5)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B5)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F5)</f>
         <v/>
       </c>
       <c r="H5" s="241">
-        <f>IF(F5="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B5))</f>
-        <v/>
-      </c>
-      <c r="I5" s="240" t="n"/>
-      <c r="J5" s="241" t="n"/>
+        <f>IF(F5="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*"))</f>
+        <v/>
+      </c>
+      <c r="I5" s="240">
+        <f>IF($B5="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B5)+COUNTIFS(Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
+      <c r="J5" s="241">
+        <f>IF($B5="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B5)+COUNTIFS(Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
       <c r="K5" s="240">
         <f>IF(MIN(N(C5),N(F5))&lt;=0,"",ROUND(MIN(N(C5),N(F5))*(N(G5)-N(D5)),8))</f>
         <v/>
@@ -4454,31 +4473,37 @@
         </is>
       </c>
       <c r="C6" s="246">
-        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B6)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B6))</f>
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="D6" s="183">
-        <f>IF(C6="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B6)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C6)</f>
+        <f>IF(C6="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B6)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B6)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C6)</f>
         <v/>
       </c>
       <c r="E6" s="247">
-        <f>IF(C6="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B6))</f>
+        <f>IF(C6="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="F6" s="246">
-        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B6)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B6))</f>
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="G6" s="183">
-        <f>IF(F6="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B6)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F6)</f>
+        <f>IF(F6="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B6)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B6)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F6)</f>
         <v/>
       </c>
       <c r="H6" s="247">
-        <f>IF(F6="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B6))</f>
-        <v/>
-      </c>
-      <c r="I6" s="246" t="n"/>
-      <c r="J6" s="247" t="n"/>
+        <f>IF(F6="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*"))</f>
+        <v/>
+      </c>
+      <c r="I6" s="246">
+        <f>IF($B6="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B6)+COUNTIFS(Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
+      <c r="J6" s="247">
+        <f>IF($B6="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B6)+COUNTIFS(Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
       <c r="K6" s="246">
         <f>IF(MIN(N(C6),N(F6))&lt;=0,"",ROUND(MIN(N(C6),N(F6))*(N(G6)-N(D6)),8))</f>
         <v/>
@@ -4499,31 +4524,37 @@
         </is>
       </c>
       <c r="C7" s="240">
-        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B7)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B7))</f>
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="D7" s="177">
-        <f>IF(C7="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B7)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C7)</f>
+        <f>IF(C7="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B7)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B7)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C7)</f>
         <v/>
       </c>
       <c r="E7" s="241">
-        <f>IF(C7="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B7))</f>
+        <f>IF(C7="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="F7" s="240">
-        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B7)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B7))</f>
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="G7" s="177">
-        <f>IF(F7="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B7)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F7)</f>
+        <f>IF(F7="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B7)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B7)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F7)</f>
         <v/>
       </c>
       <c r="H7" s="241">
-        <f>IF(F7="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B7))</f>
-        <v/>
-      </c>
-      <c r="I7" s="240" t="n"/>
-      <c r="J7" s="241" t="n"/>
+        <f>IF(F7="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*"))</f>
+        <v/>
+      </c>
+      <c r="I7" s="240">
+        <f>IF($B7="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B7)+COUNTIFS(Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
+      <c r="J7" s="241">
+        <f>IF($B7="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B7)+COUNTIFS(Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
       <c r="K7" s="240">
         <f>IF(MIN(N(C7),N(F7))&lt;=0,"",ROUND(MIN(N(C7),N(F7))*(N(G7)-N(D7)),8))</f>
         <v/>
@@ -4544,31 +4575,37 @@
         </is>
       </c>
       <c r="C8" s="246">
-        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B8)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B8))</f>
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="D8" s="183">
-        <f>IF(C8="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B8)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C8)</f>
+        <f>IF(C8="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B8)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B8)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C8)</f>
         <v/>
       </c>
       <c r="E8" s="247">
-        <f>IF(C8="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B8))</f>
+        <f>IF(C8="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="F8" s="246">
-        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B8)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B8))</f>
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="G8" s="183">
-        <f>IF(F8="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B8)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F8)</f>
+        <f>IF(F8="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B8)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B8)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F8)</f>
         <v/>
       </c>
       <c r="H8" s="247">
-        <f>IF(F8="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B8))</f>
-        <v/>
-      </c>
-      <c r="I8" s="246" t="n"/>
-      <c r="J8" s="247" t="n"/>
+        <f>IF(F8="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*"))</f>
+        <v/>
+      </c>
+      <c r="I8" s="246">
+        <f>IF($B8="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B8)+COUNTIFS(Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
+      <c r="J8" s="247">
+        <f>IF($B8="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B8)+COUNTIFS(Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
       <c r="K8" s="246">
         <f>IF(MIN(N(C8),N(F8))&lt;=0,"",ROUND(MIN(N(C8),N(F8))*(N(G8)-N(D8)),8))</f>
         <v/>
@@ -4589,31 +4626,37 @@
         </is>
       </c>
       <c r="C9" s="240">
-        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B9)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B9))</f>
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="D9" s="177">
-        <f>IF(C9="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B9)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C9)</f>
+        <f>IF(C9="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B9)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B9)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C9)</f>
         <v/>
       </c>
       <c r="E9" s="241">
-        <f>IF(C9="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B9))</f>
+        <f>IF(C9="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="F9" s="240">
-        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B9)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B9))</f>
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="G9" s="177">
-        <f>IF(F9="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B9)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F9)</f>
+        <f>IF(F9="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B9)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B9)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F9)</f>
         <v/>
       </c>
       <c r="H9" s="241">
-        <f>IF(F9="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B9))</f>
-        <v/>
-      </c>
-      <c r="I9" s="240" t="n"/>
-      <c r="J9" s="241" t="n"/>
+        <f>IF(F9="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*"))</f>
+        <v/>
+      </c>
+      <c r="I9" s="240">
+        <f>IF($B9="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B9)+COUNTIFS(Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="241">
+        <f>IF($B9="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B9)+COUNTIFS(Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
       <c r="K9" s="240">
         <f>IF(MIN(N(C9),N(F9))&lt;=0,"",ROUND(MIN(N(C9),N(F9))*(N(G9)-N(D9)),8))</f>
         <v/>
@@ -4630,31 +4673,37 @@
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="245" t="n"/>
       <c r="C10" s="246">
-        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B10)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B10))</f>
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="D10" s="183">
-        <f>IF(C10="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B10)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C10)</f>
+        <f>IF(C10="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B10)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B10)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C10)</f>
         <v/>
       </c>
       <c r="E10" s="247">
-        <f>IF(C10="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B10))</f>
+        <f>IF(C10="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="F10" s="246">
-        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B10)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B10))</f>
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="G10" s="183">
-        <f>IF(F10="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B10)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F10)</f>
+        <f>IF(F10="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B10)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B10)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F10)</f>
         <v/>
       </c>
       <c r="H10" s="247">
-        <f>IF(F10="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B10))</f>
-        <v/>
-      </c>
-      <c r="I10" s="246" t="n"/>
-      <c r="J10" s="247" t="n"/>
+        <f>IF(F10="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*"))</f>
+        <v/>
+      </c>
+      <c r="I10" s="246">
+        <f>IF($B10="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B10)+COUNTIFS(Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="247">
+        <f>IF($B10="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B10)+COUNTIFS(Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
       <c r="K10" s="246">
         <f>IF(MIN(N(C10),N(F10))&lt;=0,"",ROUND(MIN(N(C10),N(F10))*(N(G10)-N(D10)),8))</f>
         <v/>
@@ -4671,31 +4720,37 @@
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="239" t="n"/>
       <c r="C11" s="240">
-        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B11)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B11))</f>
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="D11" s="177">
-        <f>IF(C11="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B11)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C11)</f>
+        <f>IF(C11="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B11)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B11)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C11)</f>
         <v/>
       </c>
       <c r="E11" s="241">
-        <f>IF(C11="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B11))</f>
+        <f>IF(C11="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="F11" s="240">
-        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B11)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B11))</f>
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="G11" s="177">
-        <f>IF(F11="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B11)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F11)</f>
+        <f>IF(F11="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B11)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B11)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F11)</f>
         <v/>
       </c>
       <c r="H11" s="241">
-        <f>IF(F11="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B11))</f>
-        <v/>
-      </c>
-      <c r="I11" s="240" t="n"/>
-      <c r="J11" s="241" t="n"/>
+        <f>IF(F11="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*"))</f>
+        <v/>
+      </c>
+      <c r="I11" s="240">
+        <f>IF($B11="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B11)+COUNTIFS(Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="241">
+        <f>IF($B11="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B11)+COUNTIFS(Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
       <c r="K11" s="240">
         <f>IF(MIN(N(C11),N(F11))&lt;=0,"",ROUND(MIN(N(C11),N(F11))*(N(G11)-N(D11)),8))</f>
         <v/>
@@ -4712,31 +4767,37 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="245" t="n"/>
       <c r="C12" s="246">
-        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B12)=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B12))</f>
+        <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="D12" s="183">
-        <f>IF(C12="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B12)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)/C12)</f>
+        <f>IF(C12="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B12)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B12)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C12)</f>
         <v/>
       </c>
       <c r="E12" s="247">
-        <f>IF(C12="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B12))</f>
+        <f>IF(C12="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="F12" s="246">
-        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B12)=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B12))</f>
+        <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="G12" s="183">
-        <f>IF(F12="","",SUMPRODUCT((Лэндинг!$E$5:$E$200=$B12)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)/F12)</f>
+        <f>IF(F12="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B12)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B12)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F12)</f>
         <v/>
       </c>
       <c r="H12" s="247">
-        <f>IF(F12="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B12))</f>
-        <v/>
-      </c>
-      <c r="I12" s="246" t="n"/>
-      <c r="J12" s="247" t="n"/>
+        <f>IF(F12="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*"))</f>
+        <v/>
+      </c>
+      <c r="I12" s="246">
+        <f>IF($B12="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B12)+COUNTIFS(Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="247">
+        <f>IF($B12="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B12)+COUNTIFS(Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
+        <v/>
+      </c>
       <c r="K12" s="246">
         <f>IF(MIN(N(C12),N(F12))&lt;=0,"",ROUND(MIN(N(C12),N(F12))*(N(G12)-N(D12)),8))</f>
         <v/>
@@ -4791,19 +4852,17 @@
       </c>
     </row>
     <row r="2" ht="21" customHeight="1"/>
-    <row r="3" ht="28" customHeight="1">
-      <c r="F3" s="254" t="inlineStr">
-        <is>
-          <t>Открыто</t>
-        </is>
-      </c>
-      <c r="G3" s="270" t="n"/>
-      <c r="H3" s="256" t="inlineStr">
-        <is>
-          <t>Закрыто</t>
-        </is>
-      </c>
-      <c r="I3" s="270" t="n"/>
+    <row r="3" ht="10" customHeight="1">
+      <c r="B3" s="207" t="n"/>
+      <c r="C3" s="207" t="n"/>
+      <c r="D3" s="207" t="n"/>
+      <c r="E3" s="207" t="n"/>
+      <c r="F3" s="207" t="n"/>
+      <c r="G3" s="207" t="n"/>
+      <c r="H3" s="207" t="n"/>
+      <c r="I3" s="207" t="n"/>
+      <c r="J3" s="207" t="n"/>
+      <c r="K3" s="207" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="227" t="inlineStr">
@@ -4828,7 +4887,7 @@
       </c>
       <c r="F4" s="254" t="inlineStr">
         <is>
-          <t>Актив 1</t>
+          <t>Открыто</t>
         </is>
       </c>
       <c r="G4" s="255" t="inlineStr">
@@ -4838,7 +4897,7 @@
       </c>
       <c r="H4" s="256" t="inlineStr">
         <is>
-          <t>Актив 1</t>
+          <t>Закрыто</t>
         </is>
       </c>
       <c r="I4" s="257" t="inlineStr">
@@ -4882,10 +4941,20 @@
       <c r="G5" s="241" t="n">
         <v>2360</v>
       </c>
-      <c r="H5" s="236" t="n"/>
-      <c r="I5" s="239" t="n"/>
-      <c r="J5" s="236" t="n"/>
-      <c r="K5" s="239" t="n"/>
+      <c r="H5" s="240" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I5" s="241" t="n">
+        <v>2300</v>
+      </c>
+      <c r="J5" s="240">
+        <f>IF(AND(ISNUMBER(F5),ISNUMBER(H5)),ROUND(H5-F5,8),"")</f>
+        <v/>
+      </c>
+      <c r="K5" s="241">
+        <f>IF(AND(ISNUMBER(G5),ISNUMBER(I5)),ROUND(I5-G5,8),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="242" t="inlineStr">
@@ -4912,10 +4981,16 @@
       <c r="G6" s="247" t="n">
         <v>3125</v>
       </c>
-      <c r="H6" s="242" t="n"/>
-      <c r="I6" s="245" t="n"/>
-      <c r="J6" s="242" t="n"/>
-      <c r="K6" s="245" t="n"/>
+      <c r="H6" s="246" t="n"/>
+      <c r="I6" s="247" t="n"/>
+      <c r="J6" s="246">
+        <f>IF(AND(ISNUMBER(F6),ISNUMBER(H6)),ROUND(H6-F6,8),"")</f>
+        <v/>
+      </c>
+      <c r="K6" s="247">
+        <f>IF(AND(ISNUMBER(G6),ISNUMBER(I6)),ROUND(I6-G6,8),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="236" t="inlineStr">
@@ -4942,10 +5017,20 @@
       <c r="G7" s="241" t="n">
         <v>0.104</v>
       </c>
-      <c r="H7" s="236" t="n"/>
-      <c r="I7" s="239" t="n"/>
-      <c r="J7" s="236" t="n"/>
-      <c r="K7" s="239" t="n"/>
+      <c r="H7" s="240" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I7" s="241" t="n">
+        <v>0.1092</v>
+      </c>
+      <c r="J7" s="240">
+        <f>IF(AND(ISNUMBER(F7),ISNUMBER(H7)),ROUND(H7-F7,8),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="241">
+        <f>IF(AND(ISNUMBER(G7),ISNUMBER(I7)),ROUND(I7-G7,8),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="242" t="inlineStr">
@@ -4972,10 +5057,16 @@
       <c r="G8" s="247" t="n">
         <v>0.0624</v>
       </c>
-      <c r="H8" s="242" t="n"/>
-      <c r="I8" s="245" t="n"/>
-      <c r="J8" s="242" t="n"/>
-      <c r="K8" s="245" t="n"/>
+      <c r="H8" s="246" t="n"/>
+      <c r="I8" s="247" t="n"/>
+      <c r="J8" s="246">
+        <f>IF(AND(ISNUMBER(F8),ISNUMBER(H8)),ROUND(H8-F8,8),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="247">
+        <f>IF(AND(ISNUMBER(G8),ISNUMBER(I8)),ROUND(I8-G8,8),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="236" t="inlineStr">
@@ -5002,10 +5093,16 @@
       <c r="G9" s="241" t="n">
         <v>4800</v>
       </c>
-      <c r="H9" s="236" t="n"/>
-      <c r="I9" s="239" t="n"/>
-      <c r="J9" s="236" t="n"/>
-      <c r="K9" s="239" t="n"/>
+      <c r="H9" s="240" t="n"/>
+      <c r="I9" s="241" t="n"/>
+      <c r="J9" s="240">
+        <f>IF(AND(ISNUMBER(F9),ISNUMBER(H9)),ROUND(H9-F9,8),"")</f>
+        <v/>
+      </c>
+      <c r="K9" s="241">
+        <f>IF(AND(ISNUMBER(G9),ISNUMBER(I9)),ROUND(I9-G9,8),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="242" t="inlineStr">
@@ -5032,10 +5129,20 @@
       <c r="G10" s="247" t="n">
         <v>4350</v>
       </c>
-      <c r="H10" s="242" t="n"/>
-      <c r="I10" s="245" t="n"/>
-      <c r="J10" s="242" t="n"/>
-      <c r="K10" s="245" t="n"/>
+      <c r="H10" s="246" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I10" s="247" t="n">
+        <v>4560</v>
+      </c>
+      <c r="J10" s="246">
+        <f>IF(AND(ISNUMBER(F10),ISNUMBER(H10)),ROUND(H10-F10,8),"")</f>
+        <v/>
+      </c>
+      <c r="K10" s="247">
+        <f>IF(AND(ISNUMBER(G10),ISNUMBER(I10)),ROUND(I10-G10,8),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="236" t="inlineStr">
@@ -5062,10 +5169,20 @@
       <c r="G11" s="241" t="n">
         <v>1740</v>
       </c>
-      <c r="H11" s="236" t="n"/>
-      <c r="I11" s="239" t="n"/>
-      <c r="J11" s="236" t="n"/>
-      <c r="K11" s="239" t="n"/>
+      <c r="H11" s="240" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I11" s="241" t="n">
+        <v>1688</v>
+      </c>
+      <c r="J11" s="240">
+        <f>IF(AND(ISNUMBER(F11),ISNUMBER(H11)),ROUND(H11-F11,8),"")</f>
+        <v/>
+      </c>
+      <c r="K11" s="241">
+        <f>IF(AND(ISNUMBER(G11),ISNUMBER(I11)),ROUND(I11-G11,8),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="242" t="inlineStr">
@@ -5092,17 +5209,21 @@
       <c r="G12" s="247" t="n">
         <v>3625</v>
       </c>
-      <c r="H12" s="242" t="n"/>
-      <c r="I12" s="245" t="n"/>
-      <c r="J12" s="242" t="n"/>
-      <c r="K12" s="245" t="n"/>
+      <c r="H12" s="246" t="n"/>
+      <c r="I12" s="247" t="n"/>
+      <c r="J12" s="246">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER(H12)),ROUND(H12-F12,8),"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="247">
+        <f>IF(AND(ISNUMBER(G12),ISNUMBER(I12)),ROUND(I12-G12,8),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B4:K12"/>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="B1:K2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -5141,19 +5262,18 @@
       </c>
     </row>
     <row r="2" ht="21" customHeight="1"/>
-    <row r="3" ht="28" customHeight="1">
-      <c r="C3" s="254" t="inlineStr">
-        <is>
-          <t>Открыто</t>
-        </is>
-      </c>
-      <c r="D3" s="270" t="n"/>
-      <c r="E3" s="256" t="inlineStr">
-        <is>
-          <t>Закрыто</t>
-        </is>
-      </c>
-      <c r="F3" s="270" t="n"/>
+    <row r="3" ht="10" customHeight="1">
+      <c r="B3" s="207" t="n"/>
+      <c r="C3" s="207" t="n"/>
+      <c r="D3" s="207" t="n"/>
+      <c r="E3" s="207" t="n"/>
+      <c r="F3" s="207" t="n"/>
+      <c r="G3" s="207" t="n"/>
+      <c r="H3" s="207" t="n"/>
+      <c r="I3" s="207" t="n"/>
+      <c r="J3" s="207" t="n"/>
+      <c r="K3" s="207" t="n"/>
+      <c r="L3" s="207" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="162" t="inlineStr">
@@ -5163,7 +5283,7 @@
       </c>
       <c r="C4" s="254" t="inlineStr">
         <is>
-          <t>Актив 1</t>
+          <t>Открыто</t>
         </is>
       </c>
       <c r="D4" s="255" t="inlineStr">
@@ -5173,7 +5293,7 @@
       </c>
       <c r="E4" s="256" t="inlineStr">
         <is>
-          <t>Актив 1</t>
+          <t>Закрыто</t>
         </is>
       </c>
       <c r="F4" s="257" t="inlineStr">
@@ -5215,118 +5335,142 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="239" t="inlineStr">
         <is>
-          <t>ETH/BTC</t>
-        </is>
-      </c>
-      <c r="C5" s="240" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="241" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="E5" s="240" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="F5" s="241" t="n">
-        <v>0.1092</v>
-      </c>
-      <c r="G5" s="240" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="H5" s="241" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="I5" s="236" t="inlineStr">
-        <is>
-          <t>Удалить</t>
-        </is>
-      </c>
-      <c r="J5" s="177" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K5" s="177" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="L5" s="177" t="n">
-        <v>0.026</v>
+          <t>BNB/USDT</t>
+        </is>
+      </c>
+      <c r="C5" s="240">
+        <f>IF($B5="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B5,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B5),8)))</f>
+        <v/>
+      </c>
+      <c r="D5" s="241">
+        <f>IF($B5="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B5,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B5),8)))</f>
+        <v/>
+      </c>
+      <c r="E5" s="240">
+        <f>IF($B5="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B5,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B5),8)))</f>
+        <v/>
+      </c>
+      <c r="F5" s="241">
+        <f>IF($B5="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B5,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B5),8)))</f>
+        <v/>
+      </c>
+      <c r="G5" s="240">
+        <f>IF($B5="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B5,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B5),8)))</f>
+        <v/>
+      </c>
+      <c r="H5" s="241">
+        <f>IF($B5="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B5,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B5),8)))</f>
+        <v/>
+      </c>
+      <c r="I5" s="236">
+        <f>IF(AND(ISNUMBER(G5),ISNUMBER(H5)),IF(AND(G5&gt;0,H5&lt;0),"Buy",IF(AND(G5&lt;0,H5&gt;0),"Sell","")),"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="177">
+        <f>IF(I5="Buy",G5,IF(I5="Sell",-G5,""))</f>
+        <v/>
+      </c>
+      <c r="K5" s="177">
+        <f>IF(AND(ISNUMBER(J5),ISNUMBER(L5),N(J5)&lt;&gt;0),ROUND(L5/J5,8),"")</f>
+        <v/>
+      </c>
+      <c r="L5" s="177">
+        <f>IF(I5="Buy",-H5,IF(I5="Sell",H5,""))</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="245" t="inlineStr">
         <is>
-          <t>SOL/USDT</t>
-        </is>
-      </c>
-      <c r="C6" s="246" t="n">
-        <v>30</v>
-      </c>
-      <c r="D6" s="247" t="n">
-        <v>4350</v>
-      </c>
-      <c r="E6" s="246" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="F6" s="247" t="n">
-        <v>4560</v>
-      </c>
-      <c r="G6" s="246" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="H6" s="247" t="n">
-        <v>210</v>
-      </c>
-      <c r="I6" s="242" t="inlineStr">
-        <is>
-          <t>Удалить</t>
-        </is>
-      </c>
-      <c r="J6" s="183" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" s="183" t="n">
-        <v>145</v>
-      </c>
-      <c r="L6" s="183" t="n">
-        <v>1450</v>
+          <t>BTC/USDT</t>
+        </is>
+      </c>
+      <c r="C6" s="246">
+        <f>IF($B6="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B6,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B6),8)))</f>
+        <v/>
+      </c>
+      <c r="D6" s="247">
+        <f>IF($B6="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B6,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B6),8)))</f>
+        <v/>
+      </c>
+      <c r="E6" s="246">
+        <f>IF($B6="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B6,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B6),8)))</f>
+        <v/>
+      </c>
+      <c r="F6" s="247">
+        <f>IF($B6="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B6,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B6),8)))</f>
+        <v/>
+      </c>
+      <c r="G6" s="246">
+        <f>IF($B6="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B6,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B6),8)))</f>
+        <v/>
+      </c>
+      <c r="H6" s="247">
+        <f>IF($B6="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B6,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B6),8)))</f>
+        <v/>
+      </c>
+      <c r="I6" s="242">
+        <f>IF(AND(ISNUMBER(G6),ISNUMBER(H6)),IF(AND(G6&gt;0,H6&lt;0),"Buy",IF(AND(G6&lt;0,H6&gt;0),"Sell","")),"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="183">
+        <f>IF(I6="Buy",G6,IF(I6="Sell",-G6,""))</f>
+        <v/>
+      </c>
+      <c r="K6" s="183">
+        <f>IF(AND(ISNUMBER(J6),ISNUMBER(L6),N(J6)&lt;&gt;0),ROUND(L6/J6,8),"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="183">
+        <f>IF(I6="Buy",-H6,IF(I6="Sell",H6,""))</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="239" t="inlineStr">
         <is>
-          <t>BNB/USDT</t>
-        </is>
-      </c>
-      <c r="C7" s="240" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="241" t="n">
-        <v>2360</v>
-      </c>
-      <c r="E7" s="240" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F7" s="241" t="n">
-        <v>2300</v>
-      </c>
-      <c r="G7" s="240" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H7" s="241" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I7" s="236" t="inlineStr">
-        <is>
-          <t>Добавить</t>
-        </is>
-      </c>
-      <c r="J7" s="177" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="177" t="n">
-        <v>590</v>
-      </c>
-      <c r="L7" s="177" t="n">
-        <v>590</v>
+          <t>ETH/BTC</t>
+        </is>
+      </c>
+      <c r="C7" s="240">
+        <f>IF($B7="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B7,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B7),8)))</f>
+        <v/>
+      </c>
+      <c r="D7" s="241">
+        <f>IF($B7="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B7,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B7),8)))</f>
+        <v/>
+      </c>
+      <c r="E7" s="240">
+        <f>IF($B7="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B7,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B7),8)))</f>
+        <v/>
+      </c>
+      <c r="F7" s="241">
+        <f>IF($B7="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B7,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B7),8)))</f>
+        <v/>
+      </c>
+      <c r="G7" s="240">
+        <f>IF($B7="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B7,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B7),8)))</f>
+        <v/>
+      </c>
+      <c r="H7" s="241">
+        <f>IF($B7="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B7,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B7),8)))</f>
+        <v/>
+      </c>
+      <c r="I7" s="236">
+        <f>IF(AND(ISNUMBER(G7),ISNUMBER(H7)),IF(AND(G7&gt;0,H7&lt;0),"Buy",IF(AND(G7&lt;0,H7&gt;0),"Sell","")),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="177">
+        <f>IF(I7="Buy",G7,IF(I7="Sell",-G7,""))</f>
+        <v/>
+      </c>
+      <c r="K7" s="177">
+        <f>IF(AND(ISNUMBER(J7),ISNUMBER(L7),N(J7)&lt;&gt;0),ROUND(L7/J7,8),"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="177">
+        <f>IF(I7="Buy",-H7,IF(I7="Sell",H7,""))</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -5335,37 +5479,45 @@
           <t>ETH/USDT</t>
         </is>
       </c>
-      <c r="C8" s="246" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D8" s="247" t="n">
-        <v>4800</v>
-      </c>
-      <c r="E8" s="246" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="F8" s="247" t="n">
-        <v>4960</v>
-      </c>
-      <c r="G8" s="246" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="H8" s="247" t="n">
-        <v>160</v>
-      </c>
-      <c r="I8" s="242" t="inlineStr">
-        <is>
-          <t>Удалить</t>
-        </is>
-      </c>
-      <c r="J8" s="183" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K8" s="183" t="n">
-        <v>3200</v>
-      </c>
-      <c r="L8" s="183" t="n">
-        <v>1600</v>
+      <c r="C8" s="246">
+        <f>IF($B8="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B8,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B8),8)))</f>
+        <v/>
+      </c>
+      <c r="D8" s="247">
+        <f>IF($B8="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B8,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B8),8)))</f>
+        <v/>
+      </c>
+      <c r="E8" s="246">
+        <f>IF($B8="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B8,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B8),8)))</f>
+        <v/>
+      </c>
+      <c r="F8" s="247">
+        <f>IF($B8="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B8,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B8),8)))</f>
+        <v/>
+      </c>
+      <c r="G8" s="246">
+        <f>IF($B8="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B8,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B8),8)))</f>
+        <v/>
+      </c>
+      <c r="H8" s="247">
+        <f>IF($B8="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B8,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B8),8)))</f>
+        <v/>
+      </c>
+      <c r="I8" s="242">
+        <f>IF(AND(ISNUMBER(G8),ISNUMBER(H8)),IF(AND(G8&gt;0,H8&lt;0),"Buy",IF(AND(G8&lt;0,H8&gt;0),"Sell","")),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="183">
+        <f>IF(I8="Buy",G8,IF(I8="Sell",-G8,""))</f>
+        <v/>
+      </c>
+      <c r="K8" s="183">
+        <f>IF(AND(ISNUMBER(J8),ISNUMBER(L8),N(J8)&lt;&gt;0),ROUND(L8/J8,8),"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="183">
+        <f>IF(I8="Buy",-H8,IF(I8="Sell",H8,""))</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -5374,162 +5526,180 @@
           <t>SOL/USDT</t>
         </is>
       </c>
-      <c r="C9" s="240" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" s="241" t="n">
-        <v>1740</v>
-      </c>
-      <c r="E9" s="240" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F9" s="241" t="n">
-        <v>1692</v>
-      </c>
-      <c r="G9" s="240" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H9" s="241" t="n">
-        <v>-48</v>
-      </c>
-      <c r="I9" s="236" t="inlineStr">
-        <is>
-          <t>Добавить</t>
-        </is>
-      </c>
-      <c r="J9" s="177" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" s="177" t="n">
-        <v>145</v>
-      </c>
-      <c r="L9" s="177" t="n">
-        <v>435</v>
+      <c r="C9" s="240">
+        <f>IF($B9="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B9,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B9),8)))</f>
+        <v/>
+      </c>
+      <c r="D9" s="241">
+        <f>IF($B9="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B9,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B9),8)))</f>
+        <v/>
+      </c>
+      <c r="E9" s="240">
+        <f>IF($B9="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B9,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B9),8)))</f>
+        <v/>
+      </c>
+      <c r="F9" s="241">
+        <f>IF($B9="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B9,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B9),8)))</f>
+        <v/>
+      </c>
+      <c r="G9" s="240">
+        <f>IF($B9="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B9,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B9),8)))</f>
+        <v/>
+      </c>
+      <c r="H9" s="241">
+        <f>IF($B9="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B9,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B9),8)))</f>
+        <v/>
+      </c>
+      <c r="I9" s="236">
+        <f>IF(AND(ISNUMBER(G9),ISNUMBER(H9)),IF(AND(G9&gt;0,H9&lt;0),"Buy",IF(AND(G9&lt;0,H9&gt;0),"Sell","")),"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="177">
+        <f>IF(I9="Buy",G9,IF(I9="Sell",-G9,""))</f>
+        <v/>
+      </c>
+      <c r="K9" s="177">
+        <f>IF(AND(ISNUMBER(J9),ISNUMBER(L9),N(J9)&lt;&gt;0),ROUND(L9/J9,8),"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="177">
+        <f>IF(I9="Buy",-H9,IF(I9="Sell",H9,""))</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="245" t="inlineStr">
-        <is>
-          <t>BTC/USDT</t>
-        </is>
-      </c>
-      <c r="C10" s="246" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D10" s="247" t="n">
-        <v>3125</v>
-      </c>
-      <c r="E10" s="246" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="F10" s="247" t="n">
-        <v>3225</v>
-      </c>
-      <c r="G10" s="246" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="H10" s="247" t="n">
-        <v>100</v>
-      </c>
-      <c r="I10" s="242" t="inlineStr">
-        <is>
-          <t>Удалить</t>
-        </is>
-      </c>
-      <c r="J10" s="183" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K10" s="183" t="n">
-        <v>62500</v>
-      </c>
-      <c r="L10" s="183" t="n">
-        <v>625</v>
+      <c r="B10" s="245" t="n"/>
+      <c r="C10" s="246">
+        <f>IF($B10="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B10,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B10),8)))</f>
+        <v/>
+      </c>
+      <c r="D10" s="247">
+        <f>IF($B10="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B10,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B10),8)))</f>
+        <v/>
+      </c>
+      <c r="E10" s="246">
+        <f>IF($B10="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B10,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B10),8)))</f>
+        <v/>
+      </c>
+      <c r="F10" s="247">
+        <f>IF($B10="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B10,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B10),8)))</f>
+        <v/>
+      </c>
+      <c r="G10" s="246">
+        <f>IF($B10="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B10,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B10),8)))</f>
+        <v/>
+      </c>
+      <c r="H10" s="247">
+        <f>IF($B10="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B10,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B10),8)))</f>
+        <v/>
+      </c>
+      <c r="I10" s="242">
+        <f>IF(AND(ISNUMBER(G10),ISNUMBER(H10)),IF(AND(G10&gt;0,H10&lt;0),"Buy",IF(AND(G10&lt;0,H10&gt;0),"Sell","")),"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="183">
+        <f>IF(I10="Buy",G10,IF(I10="Sell",-G10,""))</f>
+        <v/>
+      </c>
+      <c r="K10" s="183">
+        <f>IF(AND(ISNUMBER(J10),ISNUMBER(L10),N(J10)&lt;&gt;0),ROUND(L10/J10,8),"")</f>
+        <v/>
+      </c>
+      <c r="L10" s="183">
+        <f>IF(I10="Buy",-H10,IF(I10="Sell",H10,""))</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="239" t="inlineStr">
-        <is>
-          <t>ETH/BTC</t>
-        </is>
-      </c>
-      <c r="C11" s="240" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D11" s="241" t="n">
-        <v>0.0624</v>
-      </c>
-      <c r="E11" s="240" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F11" s="241" t="n">
-        <v>0.0598</v>
-      </c>
-      <c r="G11" s="240" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H11" s="241" t="n">
-        <v>-0.0026</v>
-      </c>
-      <c r="I11" s="236" t="inlineStr">
-        <is>
-          <t>Добавить</t>
-        </is>
-      </c>
-      <c r="J11" s="177" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K11" s="177" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="L11" s="177" t="n">
-        <v>0.0156</v>
+      <c r="B11" s="239" t="n"/>
+      <c r="C11" s="240">
+        <f>IF($B11="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B11,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B11),8)))</f>
+        <v/>
+      </c>
+      <c r="D11" s="241">
+        <f>IF($B11="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B11,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B11),8)))</f>
+        <v/>
+      </c>
+      <c r="E11" s="240">
+        <f>IF($B11="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B11,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B11),8)))</f>
+        <v/>
+      </c>
+      <c r="F11" s="241">
+        <f>IF($B11="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B11,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B11),8)))</f>
+        <v/>
+      </c>
+      <c r="G11" s="240">
+        <f>IF($B11="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B11,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B11),8)))</f>
+        <v/>
+      </c>
+      <c r="H11" s="241">
+        <f>IF($B11="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B11,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B11),8)))</f>
+        <v/>
+      </c>
+      <c r="I11" s="236">
+        <f>IF(AND(ISNUMBER(G11),ISNUMBER(H11)),IF(AND(G11&gt;0,H11&lt;0),"Buy",IF(AND(G11&lt;0,H11&gt;0),"Sell","")),"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="177">
+        <f>IF(I11="Buy",G11,IF(I11="Sell",-G11,""))</f>
+        <v/>
+      </c>
+      <c r="K11" s="177">
+        <f>IF(AND(ISNUMBER(J11),ISNUMBER(L11),N(J11)&lt;&gt;0),ROUND(L11/J11,8),"")</f>
+        <v/>
+      </c>
+      <c r="L11" s="177">
+        <f>IF(I11="Buy",-H11,IF(I11="Sell",H11,""))</f>
+        <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="245" t="inlineStr">
-        <is>
-          <t>SOL/USDT</t>
-        </is>
-      </c>
-      <c r="C12" s="246" t="n">
-        <v>25</v>
-      </c>
-      <c r="D12" s="247" t="n">
-        <v>3625</v>
-      </c>
-      <c r="E12" s="246" t="n">
-        <v>24</v>
-      </c>
-      <c r="F12" s="247" t="n">
-        <v>3770</v>
-      </c>
-      <c r="G12" s="246" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H12" s="247" t="n">
-        <v>145</v>
-      </c>
-      <c r="I12" s="242" t="inlineStr">
-        <is>
-          <t>Удалить</t>
-        </is>
-      </c>
-      <c r="J12" s="183" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" s="183" t="n">
-        <v>145</v>
-      </c>
-      <c r="L12" s="183" t="n">
-        <v>725</v>
+      <c r="B12" s="245" t="n"/>
+      <c r="C12" s="246">
+        <f>IF($B12="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B12,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B12),8)))</f>
+        <v/>
+      </c>
+      <c r="D12" s="247">
+        <f>IF($B12="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B12,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B12),8)))</f>
+        <v/>
+      </c>
+      <c r="E12" s="246">
+        <f>IF($B12="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B12,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B12),8)))</f>
+        <v/>
+      </c>
+      <c r="F12" s="247">
+        <f>IF($B12="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B12,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B12),8)))</f>
+        <v/>
+      </c>
+      <c r="G12" s="246">
+        <f>IF($B12="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B12,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B12),8)))</f>
+        <v/>
+      </c>
+      <c r="H12" s="247">
+        <f>IF($B12="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B12,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B12),8)))</f>
+        <v/>
+      </c>
+      <c r="I12" s="242">
+        <f>IF(AND(ISNUMBER(G12),ISNUMBER(H12)),IF(AND(G12&gt;0,H12&lt;0),"Buy",IF(AND(G12&lt;0,H12&gt;0),"Sell","")),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="183">
+        <f>IF(I12="Buy",G12,IF(I12="Sell",-G12,""))</f>
+        <v/>
+      </c>
+      <c r="K12" s="183">
+        <f>IF(AND(ISNUMBER(J12),ISNUMBER(L12),N(J12)&lt;&gt;0),ROUND(L12/J12,8),"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="183">
+        <f>IF(I12="Buy",-H12,IF(I12="Sell",H12,""))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B4:L12"/>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="B1:L2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C3:D3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -5543,26 +5713,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Q12"/>
+  <dimension ref="B1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="8.43" customWidth="1" min="16" max="16"/>
+    <col width="8.43" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
@@ -5571,9 +5741,17 @@
           <t>CRYPTO JOURNAL • ЗАКРЫТЫЕ</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="21" customHeight="1"/>
-    <row r="3" ht="10" customHeight="1"/>
+      <c r="P1" s="207" t="n"/>
+      <c r="Q1" s="207" t="n"/>
+    </row>
+    <row r="2" ht="21" customHeight="1">
+      <c r="P2" s="207" t="n"/>
+      <c r="Q2" s="207" t="n"/>
+    </row>
+    <row r="3" ht="10" customHeight="1">
+      <c r="P3" s="207" t="n"/>
+      <c r="Q3" s="207" t="n"/>
+    </row>
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="161" t="inlineStr">
         <is>
@@ -5582,79 +5760,71 @@
       </c>
       <c r="C4" s="161" t="inlineStr">
         <is>
-          <t>Дата открытия</t>
+          <t>Дата</t>
         </is>
       </c>
       <c r="D4" s="161" t="inlineStr">
         <is>
-          <t>Дата закрытия</t>
-        </is>
-      </c>
-      <c r="E4" s="161" t="inlineStr">
-        <is>
           <t>Протокол</t>
         </is>
       </c>
-      <c r="F4" s="162" t="inlineStr">
+      <c r="E4" s="162" t="inlineStr">
         <is>
           <t>Пара</t>
         </is>
       </c>
-      <c r="G4" s="163" t="inlineStr">
+      <c r="F4" s="163" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="H4" s="185" t="inlineStr">
+      <c r="G4" s="185" t="inlineStr">
         <is>
           <t>Курс</t>
         </is>
       </c>
-      <c r="I4" s="165" t="inlineStr">
+      <c r="H4" s="165" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="J4" s="166" t="inlineStr">
+      <c r="I4" s="166" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="K4" s="167" t="inlineStr">
+      <c r="J4" s="167" t="inlineStr">
         <is>
           <t>Курс</t>
         </is>
       </c>
-      <c r="L4" s="168" t="inlineStr">
+      <c r="K4" s="168" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-      <c r="M4" s="169" t="inlineStr">
+      <c r="L4" s="169" t="inlineStr">
         <is>
           <t>Дельта 1</t>
         </is>
       </c>
-      <c r="N4" s="170" t="inlineStr">
+      <c r="M4" s="170" t="inlineStr">
         <is>
           <t>Дельта 2</t>
         </is>
       </c>
-      <c r="O4" s="171" t="inlineStr">
+      <c r="N4" s="171" t="inlineStr">
         <is>
           <t>P&amp;L</t>
         </is>
       </c>
-      <c r="P4" s="172" t="inlineStr">
+      <c r="O4" s="172" t="inlineStr">
         <is>
           <t>P&amp;L%</t>
         </is>
       </c>
-      <c r="Q4" s="172" t="inlineStr">
-        <is>
-          <t>Break even</t>
-        </is>
-      </c>
+      <c r="P4" s="207" t="n"/>
+      <c r="Q4" s="207" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="238" t="inlineStr">
@@ -5665,48 +5835,52 @@
       <c r="C5" s="237" t="n">
         <v>46299</v>
       </c>
-      <c r="D5" s="237" t="n">
-        <v>46300</v>
-      </c>
-      <c r="E5" s="238" t="inlineStr">
+      <c r="D5" s="238" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="F5" s="239" t="inlineStr">
+      <c r="E5" s="239" t="inlineStr">
         <is>
           <t>BNB/USDT</t>
         </is>
       </c>
-      <c r="G5" s="240" t="n">
+      <c r="F5" s="240" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="177" t="n">
+      <c r="G5" s="177" t="n">
         <v>586.17</v>
       </c>
-      <c r="I5" s="241" t="n">
+      <c r="H5" s="241" t="n">
         <v>1172.34</v>
       </c>
-      <c r="J5" s="240" t="n">
+      <c r="I5" s="240" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="177" t="n">
+      <c r="J5" s="177" t="n">
         <v>598.8</v>
       </c>
-      <c r="L5" s="241" t="n">
+      <c r="K5" s="241" t="n">
         <v>1197.6</v>
       </c>
-      <c r="M5" s="240">
-        <f>IF(AND(AND(ISNUMBER(G5),ISNUMBER(J5),ISNUMBER(I5),ISNUMBER(L5)),G5&gt;0,J5&gt;0,I5&lt;&gt;0),ROUND(MIN(G5,J5)*(L5/J5-I5/G5),8),"")</f>
-        <v/>
-      </c>
-      <c r="N5" s="241">
-        <f>IF(AND(AND(ISNUMBER(G5),ISNUMBER(J5),ISNUMBER(I5),ISNUMBER(L5)),G5&gt;0,J5&gt;0,I5&lt;&gt;0),ROUND((L5/J5)/(I5/G5)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="O5" s="240" t="n"/>
-      <c r="P5" s="177" t="n"/>
-      <c r="Q5" s="177" t="n"/>
+      <c r="L5" s="240">
+        <f>IF(COUNT(F5,I5)=0,"",N(F5)-N(I5))</f>
+        <v/>
+      </c>
+      <c r="M5" s="241">
+        <f>IF(COUNT(H5,K5)=0,"",N(K5)-N(H5))</f>
+        <v/>
+      </c>
+      <c r="N5" s="240">
+        <f>IF(AND(ISNUMBER(F5),ISNUMBER(I5),ISNUMBER(H5),ISNUMBER(K5),F5&gt;0,I5&gt;0,H5&lt;&gt;0),ROUND(MIN(F5,I5)*(K5/I5-H5/F5),8),"")</f>
+        <v/>
+      </c>
+      <c r="O5" s="177">
+        <f>IF(ISNUMBER(N5),ROUND(N5/(MIN(F5,I5)*H5/F5)*100,2),"")</f>
+        <v/>
+      </c>
+      <c r="P5" s="207" t="n"/>
+      <c r="Q5" s="207" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="244" t="inlineStr">
@@ -5717,48 +5891,52 @@
       <c r="C6" s="243" t="n">
         <v>46299</v>
       </c>
-      <c r="D6" s="243" t="n">
-        <v>46300</v>
-      </c>
-      <c r="E6" s="244" t="inlineStr">
+      <c r="D6" s="244" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="F6" s="245" t="inlineStr">
+      <c r="E6" s="245" t="inlineStr">
         <is>
           <t>BTC/USDT</t>
         </is>
       </c>
-      <c r="G6" s="246" t="n">
+      <c r="F6" s="246" t="n">
         <v>0.05</v>
       </c>
-      <c r="H6" s="183" t="n">
+      <c r="G6" s="183" t="n">
         <v>62324.4</v>
       </c>
-      <c r="I6" s="247" t="n">
+      <c r="H6" s="247" t="n">
         <v>3116.22</v>
       </c>
-      <c r="J6" s="246" t="n">
+      <c r="I6" s="246" t="n">
         <v>0.05</v>
       </c>
-      <c r="K6" s="183" t="n">
+      <c r="J6" s="183" t="n">
         <v>62874</v>
       </c>
-      <c r="L6" s="247" t="n">
+      <c r="K6" s="247" t="n">
         <v>3143.7</v>
       </c>
-      <c r="M6" s="246">
-        <f>IF(AND(AND(ISNUMBER(G6),ISNUMBER(J6),ISNUMBER(I6),ISNUMBER(L6)),G6&gt;0,J6&gt;0,I6&lt;&gt;0),ROUND(MIN(G6,J6)*(L6/J6-I6/G6),8),"")</f>
-        <v/>
-      </c>
-      <c r="N6" s="247">
-        <f>IF(AND(AND(ISNUMBER(G6),ISNUMBER(J6),ISNUMBER(I6),ISNUMBER(L6)),G6&gt;0,J6&gt;0,I6&lt;&gt;0),ROUND((L6/J6)/(I6/G6)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="O6" s="246" t="n"/>
-      <c r="P6" s="183" t="n"/>
-      <c r="Q6" s="183" t="n"/>
+      <c r="L6" s="246">
+        <f>IF(COUNT(F6,I6)=0,"",N(F6)-N(I6))</f>
+        <v/>
+      </c>
+      <c r="M6" s="247">
+        <f>IF(COUNT(H6,K6)=0,"",N(K6)-N(H6))</f>
+        <v/>
+      </c>
+      <c r="N6" s="246">
+        <f>IF(AND(ISNUMBER(F6),ISNUMBER(I6),ISNUMBER(H6),ISNUMBER(K6),F6&gt;0,I6&gt;0,H6&lt;&gt;0),ROUND(MIN(F6,I6)*(K6/I6-H6/F6),8),"")</f>
+        <v/>
+      </c>
+      <c r="O6" s="183">
+        <f>IF(ISNUMBER(N6),ROUND(N6/(MIN(F6,I6)*H6/F6)*100,2),"")</f>
+        <v/>
+      </c>
+      <c r="P6" s="207" t="n"/>
+      <c r="Q6" s="207" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="238" t="inlineStr">
@@ -5769,48 +5947,52 @@
       <c r="C7" s="237" t="n">
         <v>46297</v>
       </c>
-      <c r="D7" s="237" t="n">
-        <v>46299</v>
-      </c>
-      <c r="E7" s="238" t="inlineStr">
+      <c r="D7" s="238" t="inlineStr">
         <is>
           <t>Bybit</t>
         </is>
       </c>
-      <c r="F7" s="239" t="inlineStr">
+      <c r="E7" s="239" t="inlineStr">
         <is>
           <t>ETH/USDT</t>
         </is>
       </c>
-      <c r="G7" s="240" t="n">
+      <c r="F7" s="240" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="177" t="n">
+      <c r="G7" s="177" t="n">
         <v>3206.4</v>
       </c>
-      <c r="I7" s="241" t="n">
+      <c r="H7" s="241" t="n">
         <v>3206.4</v>
       </c>
-      <c r="J7" s="240" t="n">
+      <c r="I7" s="240" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="177" t="n">
+      <c r="J7" s="177" t="n">
         <v>3343.3</v>
       </c>
-      <c r="L7" s="241" t="n">
+      <c r="K7" s="241" t="n">
         <v>3343.3</v>
       </c>
-      <c r="M7" s="240">
-        <f>IF(AND(AND(ISNUMBER(G7),ISNUMBER(J7),ISNUMBER(I7),ISNUMBER(L7)),G7&gt;0,J7&gt;0,I7&lt;&gt;0),ROUND(MIN(G7,J7)*(L7/J7-I7/G7),8),"")</f>
-        <v/>
-      </c>
-      <c r="N7" s="241">
-        <f>IF(AND(AND(ISNUMBER(G7),ISNUMBER(J7),ISNUMBER(I7),ISNUMBER(L7)),G7&gt;0,J7&gt;0,I7&lt;&gt;0),ROUND((L7/J7)/(I7/G7)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="O7" s="240" t="n"/>
-      <c r="P7" s="177" t="n"/>
-      <c r="Q7" s="177" t="n"/>
+      <c r="L7" s="240">
+        <f>IF(COUNT(F7,I7)=0,"",N(F7)-N(I7))</f>
+        <v/>
+      </c>
+      <c r="M7" s="241">
+        <f>IF(COUNT(H7,K7)=0,"",N(K7)-N(H7))</f>
+        <v/>
+      </c>
+      <c r="N7" s="240">
+        <f>IF(AND(ISNUMBER(F7),ISNUMBER(I7),ISNUMBER(H7),ISNUMBER(K7),F7&gt;0,I7&gt;0,H7&lt;&gt;0),ROUND(MIN(F7,I7)*(K7/I7-H7/F7),8),"")</f>
+        <v/>
+      </c>
+      <c r="O7" s="177">
+        <f>IF(ISNUMBER(N7),ROUND(N7/(MIN(F7,I7)*H7/F7)*100,2),"")</f>
+        <v/>
+      </c>
+      <c r="P7" s="207" t="n"/>
+      <c r="Q7" s="207" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="244" t="inlineStr">
@@ -5821,153 +6003,263 @@
       <c r="C8" s="243" t="n">
         <v>46298</v>
       </c>
-      <c r="D8" s="243" t="n">
-        <v>46300</v>
-      </c>
-      <c r="E8" s="244" t="inlineStr">
+      <c r="D8" s="244" t="inlineStr">
         <is>
           <t>OKX</t>
         </is>
       </c>
-      <c r="F8" s="245" t="inlineStr">
+      <c r="E8" s="245" t="inlineStr">
         <is>
           <t>SOL/USDT</t>
         </is>
       </c>
-      <c r="G8" s="246" t="n">
+      <c r="F8" s="246" t="n">
         <v>20</v>
       </c>
-      <c r="H8" s="183" t="n">
+      <c r="G8" s="183" t="n">
         <v>145.29</v>
       </c>
-      <c r="I8" s="247" t="n">
+      <c r="H8" s="247" t="n">
         <v>2905.8</v>
       </c>
-      <c r="J8" s="246" t="n">
+      <c r="I8" s="246" t="n">
         <v>20</v>
       </c>
-      <c r="K8" s="183" t="n">
+      <c r="J8" s="183" t="n">
         <v>151.696</v>
       </c>
-      <c r="L8" s="247" t="n">
+      <c r="K8" s="247" t="n">
         <v>3033.92</v>
       </c>
-      <c r="M8" s="246">
-        <f>IF(AND(AND(ISNUMBER(G8),ISNUMBER(J8),ISNUMBER(I8),ISNUMBER(L8)),G8&gt;0,J8&gt;0,I8&lt;&gt;0),ROUND(MIN(G8,J8)*(L8/J8-I8/G8),8),"")</f>
-        <v/>
-      </c>
-      <c r="N8" s="247">
-        <f>IF(AND(AND(ISNUMBER(G8),ISNUMBER(J8),ISNUMBER(I8),ISNUMBER(L8)),G8&gt;0,J8&gt;0,I8&lt;&gt;0),ROUND((L8/J8)/(I8/G8)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="O8" s="246" t="n"/>
-      <c r="P8" s="183" t="n"/>
-      <c r="Q8" s="183" t="n"/>
+      <c r="L8" s="246">
+        <f>IF(COUNT(F8,I8)=0,"",N(F8)-N(I8))</f>
+        <v/>
+      </c>
+      <c r="M8" s="247">
+        <f>IF(COUNT(H8,K8)=0,"",N(K8)-N(H8))</f>
+        <v/>
+      </c>
+      <c r="N8" s="246">
+        <f>IF(AND(ISNUMBER(F8),ISNUMBER(I8),ISNUMBER(H8),ISNUMBER(K8),F8&gt;0,I8&gt;0,H8&lt;&gt;0),ROUND(MIN(F8,I8)*(K8/I8-H8/F8),8),"")</f>
+        <v/>
+      </c>
+      <c r="O8" s="183">
+        <f>IF(ISNUMBER(N8),ROUND(N8/(MIN(F8,I8)*H8/F8)*100,2),"")</f>
+        <v/>
+      </c>
+      <c r="P8" s="207" t="n"/>
+      <c r="Q8" s="207" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="238" t="n"/>
-      <c r="C9" s="237" t="n"/>
-      <c r="D9" s="237" t="n"/>
-      <c r="E9" s="238" t="n"/>
-      <c r="F9" s="239" t="n"/>
-      <c r="G9" s="240" t="n"/>
-      <c r="H9" s="177" t="n"/>
-      <c r="I9" s="241" t="n"/>
-      <c r="J9" s="240" t="n"/>
-      <c r="K9" s="177" t="n"/>
-      <c r="L9" s="241" t="n"/>
-      <c r="M9" s="240">
-        <f>IF(AND(AND(ISNUMBER(G9),ISNUMBER(J9),ISNUMBER(I9),ISNUMBER(L9)),G9&gt;0,J9&gt;0,I9&lt;&gt;0),ROUND(MIN(G9,J9)*(L9/J9-I9/G9),8),"")</f>
-        <v/>
-      </c>
-      <c r="N9" s="241">
-        <f>IF(AND(AND(ISNUMBER(G9),ISNUMBER(J9),ISNUMBER(I9),ISNUMBER(L9)),G9&gt;0,J9&gt;0,I9&lt;&gt;0),ROUND((L9/J9)/(I9/G9)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="O9" s="240" t="n"/>
-      <c r="P9" s="177" t="n"/>
-      <c r="Q9" s="177" t="n"/>
+      <c r="B9" s="238" t="inlineStr">
+        <is>
+          <t>L-0013</t>
+        </is>
+      </c>
+      <c r="C9" s="237" t="n">
+        <v>46299</v>
+      </c>
+      <c r="D9" s="238" t="inlineStr">
+        <is>
+          <t>Binance</t>
+        </is>
+      </c>
+      <c r="E9" s="239" t="inlineStr">
+        <is>
+          <t>BNB/USDT</t>
+        </is>
+      </c>
+      <c r="F9" s="240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G9" s="177" t="n">
+        <v>585</v>
+      </c>
+      <c r="H9" s="241" t="n">
+        <v>877.5</v>
+      </c>
+      <c r="I9" s="240" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J9" s="177" t="n">
+        <v>597</v>
+      </c>
+      <c r="K9" s="241" t="n">
+        <v>895.5</v>
+      </c>
+      <c r="L9" s="240">
+        <f>IF(COUNT(F9,I9)=0,"",N(F9)-N(I9))</f>
+        <v/>
+      </c>
+      <c r="M9" s="241">
+        <f>IF(COUNT(H9,K9)=0,"",N(K9)-N(H9))</f>
+        <v/>
+      </c>
+      <c r="N9" s="240">
+        <f>IF(AND(ISNUMBER(F9),ISNUMBER(I9),ISNUMBER(H9),ISNUMBER(K9),F9&gt;0,I9&gt;0,H9&lt;&gt;0),ROUND(MIN(F9,I9)*(K9/I9-H9/F9),8),"")</f>
+        <v/>
+      </c>
+      <c r="O9" s="177">
+        <f>IF(ISNUMBER(N9),ROUND(N9/(MIN(F9,I9)*H9/F9)*100,2),"")</f>
+        <v/>
+      </c>
+      <c r="P9" s="207" t="n"/>
+      <c r="Q9" s="207" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="244" t="n"/>
-      <c r="C10" s="243" t="n"/>
-      <c r="D10" s="243" t="n"/>
-      <c r="E10" s="244" t="n"/>
-      <c r="F10" s="245" t="n"/>
-      <c r="G10" s="246" t="n"/>
-      <c r="H10" s="183" t="n"/>
-      <c r="I10" s="247" t="n"/>
-      <c r="J10" s="246" t="n"/>
-      <c r="K10" s="183" t="n"/>
-      <c r="L10" s="247" t="n"/>
-      <c r="M10" s="246">
-        <f>IF(AND(AND(ISNUMBER(G10),ISNUMBER(J10),ISNUMBER(I10),ISNUMBER(L10)),G10&gt;0,J10&gt;0,I10&lt;&gt;0),ROUND(MIN(G10,J10)*(L10/J10-I10/G10),8),"")</f>
-        <v/>
-      </c>
-      <c r="N10" s="247">
-        <f>IF(AND(AND(ISNUMBER(G10),ISNUMBER(J10),ISNUMBER(I10),ISNUMBER(L10)),G10&gt;0,J10&gt;0,I10&lt;&gt;0),ROUND((L10/J10)/(I10/G10)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="O10" s="246" t="n"/>
-      <c r="P10" s="183" t="n"/>
-      <c r="Q10" s="183" t="n"/>
+      <c r="B10" s="244" t="inlineStr">
+        <is>
+          <t>L-0014</t>
+        </is>
+      </c>
+      <c r="C10" s="243" t="n">
+        <v>46298</v>
+      </c>
+      <c r="D10" s="244" t="inlineStr">
+        <is>
+          <t>OKX</t>
+        </is>
+      </c>
+      <c r="E10" s="245" t="inlineStr">
+        <is>
+          <t>ETH/USDT</t>
+        </is>
+      </c>
+      <c r="F10" s="246" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="183" t="n">
+        <v>3210</v>
+      </c>
+      <c r="H10" s="247" t="n">
+        <v>1605</v>
+      </c>
+      <c r="I10" s="246" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J10" s="183" t="n">
+        <v>3340</v>
+      </c>
+      <c r="K10" s="247" t="n">
+        <v>1670</v>
+      </c>
+      <c r="L10" s="246">
+        <f>IF(COUNT(F10,I10)=0,"",N(F10)-N(I10))</f>
+        <v/>
+      </c>
+      <c r="M10" s="247">
+        <f>IF(COUNT(H10,K10)=0,"",N(K10)-N(H10))</f>
+        <v/>
+      </c>
+      <c r="N10" s="246">
+        <f>IF(AND(ISNUMBER(F10),ISNUMBER(I10),ISNUMBER(H10),ISNUMBER(K10),F10&gt;0,I10&gt;0,H10&lt;&gt;0),ROUND(MIN(F10,I10)*(K10/I10-H10/F10),8),"")</f>
+        <v/>
+      </c>
+      <c r="O10" s="183">
+        <f>IF(ISNUMBER(N10),ROUND(N10/(MIN(F10,I10)*H10/F10)*100,2),"")</f>
+        <v/>
+      </c>
+      <c r="P10" s="207" t="n"/>
+      <c r="Q10" s="207" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="238" t="n"/>
-      <c r="C11" s="237" t="n"/>
-      <c r="D11" s="237" t="n"/>
-      <c r="E11" s="238" t="n"/>
-      <c r="F11" s="239" t="n"/>
-      <c r="G11" s="240" t="n"/>
-      <c r="H11" s="177" t="n"/>
-      <c r="I11" s="241" t="n"/>
-      <c r="J11" s="240" t="n"/>
-      <c r="K11" s="177" t="n"/>
-      <c r="L11" s="241" t="n"/>
-      <c r="M11" s="240">
-        <f>IF(AND(AND(ISNUMBER(G11),ISNUMBER(J11),ISNUMBER(I11),ISNUMBER(L11)),G11&gt;0,J11&gt;0,I11&lt;&gt;0),ROUND(MIN(G11,J11)*(L11/J11-I11/G11),8),"")</f>
-        <v/>
-      </c>
-      <c r="N11" s="241">
-        <f>IF(AND(AND(ISNUMBER(G11),ISNUMBER(J11),ISNUMBER(I11),ISNUMBER(L11)),G11&gt;0,J11&gt;0,I11&lt;&gt;0),ROUND((L11/J11)/(I11/G11)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="O11" s="240" t="n"/>
-      <c r="P11" s="177" t="n"/>
-      <c r="Q11" s="177" t="n"/>
+      <c r="B11" s="238" t="inlineStr">
+        <is>
+          <t>L-0015</t>
+        </is>
+      </c>
+      <c r="C11" s="237" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D11" s="238" t="inlineStr">
+        <is>
+          <t>Bybit</t>
+        </is>
+      </c>
+      <c r="E11" s="239" t="inlineStr">
+        <is>
+          <t>SOL/USDT</t>
+        </is>
+      </c>
+      <c r="F11" s="240" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="177" t="n">
+        <v>145</v>
+      </c>
+      <c r="H11" s="241" t="n">
+        <v>1450</v>
+      </c>
+      <c r="I11" s="240" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="177" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="K11" s="241" t="n">
+        <v>1505</v>
+      </c>
+      <c r="L11" s="240">
+        <f>IF(COUNT(F11,I11)=0,"",N(F11)-N(I11))</f>
+        <v/>
+      </c>
+      <c r="M11" s="241">
+        <f>IF(COUNT(H11,K11)=0,"",N(K11)-N(H11))</f>
+        <v/>
+      </c>
+      <c r="N11" s="240">
+        <f>IF(AND(ISNUMBER(F11),ISNUMBER(I11),ISNUMBER(H11),ISNUMBER(K11),F11&gt;0,I11&gt;0,H11&lt;&gt;0),ROUND(MIN(F11,I11)*(K11/I11-H11/F11),8),"")</f>
+        <v/>
+      </c>
+      <c r="O11" s="177">
+        <f>IF(ISNUMBER(N11),ROUND(N11/(MIN(F11,I11)*H11/F11)*100,2),"")</f>
+        <v/>
+      </c>
+      <c r="P11" s="207" t="n"/>
+      <c r="Q11" s="207" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="244" t="n"/>
       <c r="C12" s="243" t="n"/>
-      <c r="D12" s="243" t="n"/>
-      <c r="E12" s="244" t="n"/>
-      <c r="F12" s="245" t="n"/>
-      <c r="G12" s="246" t="n"/>
-      <c r="H12" s="183" t="n"/>
-      <c r="I12" s="247" t="n"/>
-      <c r="J12" s="246" t="n"/>
-      <c r="K12" s="183" t="n"/>
-      <c r="L12" s="247" t="n"/>
-      <c r="M12" s="246">
-        <f>IF(AND(AND(ISNUMBER(G12),ISNUMBER(J12),ISNUMBER(I12),ISNUMBER(L12)),G12&gt;0,J12&gt;0,I12&lt;&gt;0),ROUND(MIN(G12,J12)*(L12/J12-I12/G12),8),"")</f>
-        <v/>
-      </c>
-      <c r="N12" s="247">
-        <f>IF(AND(AND(ISNUMBER(G12),ISNUMBER(J12),ISNUMBER(I12),ISNUMBER(L12)),G12&gt;0,J12&gt;0,I12&lt;&gt;0),ROUND((L12/J12)/(I12/G12)*100-100,2),"")</f>
-        <v/>
-      </c>
-      <c r="O12" s="246" t="n"/>
-      <c r="P12" s="183" t="n"/>
-      <c r="Q12" s="183" t="n"/>
+      <c r="D12" s="244" t="n"/>
+      <c r="E12" s="245" t="n"/>
+      <c r="F12" s="246" t="n"/>
+      <c r="G12" s="183" t="n"/>
+      <c r="H12" s="247" t="n"/>
+      <c r="I12" s="246" t="n"/>
+      <c r="J12" s="183" t="n"/>
+      <c r="K12" s="247" t="n"/>
+      <c r="L12" s="246">
+        <f>IF(COUNT(F12,I12)=0,"",N(F12)-N(I12))</f>
+        <v/>
+      </c>
+      <c r="M12" s="247">
+        <f>IF(COUNT(H12,K12)=0,"",N(K12)-N(H12))</f>
+        <v/>
+      </c>
+      <c r="N12" s="246">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER(I12),ISNUMBER(H12),ISNUMBER(K12),F12&gt;0,I12&gt;0,H12&lt;&gt;0),ROUND(MIN(F12,I12)*(K12/I12-H12/F12),8),"")</f>
+        <v/>
+      </c>
+      <c r="O12" s="183">
+        <f>IF(ISNUMBER(N12),ROUND(N12/(MIN(F12,I12)*H12/F12)*100,2),"")</f>
+        <v/>
+      </c>
+      <c r="P12" s="207" t="n"/>
+      <c r="Q12" s="207" t="n"/>
+    </row>
+    <row r="13">
+      <c r="P13" s="207" t="n"/>
+      <c r="Q13" s="207" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="B4:Q12"/>
+  <autoFilter ref="B4:O12"/>
   <mergeCells count="1">
-    <mergeCell ref="B1:Q2"/>
+    <mergeCell ref="B1:O2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:Q200">
+  <conditionalFormatting sqref="B5:O200">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND($B5&lt;&gt;"",COUNTIF(Торговля!$B$5:$B$200,$B5)&gt;0)</formula>
+      <formula>AND($B5&lt;&gt;"",COUNTIF(Торговля!$B$5:$B$200,$B5)+COUNTIF(Лэндинг!$B$5:$B$200,$B5)&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5988,7 +6280,7 @@
     <col width="2.5" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -5997,7 +6289,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">

--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J8" s="211">
         <f>IF(AND(ISNUMBER(J7),ISNUMBER(J9),J7&lt;&gt;0,1-N(J19)/100&lt;&gt;0),J9/(J7*(1-N(J19)/100)),"")</f>
-        <v/>
+        <v>1.00200400801603</v>
       </c>
       <c r="K8" s="207" t="n"/>
       <c r="L8" s="207" t="n"/>
@@ -2030,9 +2030,9 @@
           <t>BTC</t>
         </is>
       </c>
-      <c r="D9" s="195">
+      <c r="D9" s="195" t="str">
         <f>IF(AND(TRIM(B9)&lt;&gt;"",TRIM(C9)&lt;&gt;""),UPPER(TRIM(B9))&amp;"/"&amp;UPPER(TRIM(C9)),"")</f>
-        <v/>
+        <v>ETH/BTC</v>
       </c>
       <c r="E9" s="57" t="n"/>
       <c r="G9" s="3" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="H9" s="211">
         <f>IF(AND(ISNUMBER(H7),ISNUMBER(H8),OR(H6="Buy",H6="Sell")),H7*H8*(1+IF(H6="Buy",1,-1)*N(J19)/100),"")</f>
-        <v/>
+        <v>31062</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="I19" s="269">
         <f>IF(AND(ISNUMBER(G19),ISNUMBER(H19),H19&lt;&gt;0,1-N(J19)/100&lt;&gt;0),G19/(H19*(1-N(J19)/100)),"")</f>
-        <v/>
+        <v>0.501002004008016</v>
       </c>
       <c r="J19" s="266" t="n">
         <v>0.2</v>
@@ -2355,7 +2355,7 @@
   </mergeCells>
   <dataValidations count="11">
     <dataValidation sqref="H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Добавить,Удалить"</formula1>
+      <formula1>"Добавить,Закрыть"</formula1>
     </dataValidation>
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Дата" error="Введите корректную дату (ГГГГ.ММ.ДД)." type="date" operator="greaterThan">
       <formula1>36526</formula1>
@@ -2422,6 +2422,15 @@
       </c>
     </row>
     <row r="2" ht="21" customHeight="1"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="E3" s="205" t="inlineStr">
+        <is>
+          <t>Счётчики ID</t>
+        </is>
+      </c>
+      <c r="F3" s="205"/>
+      <c r="G3" s="205"/>
+    </row>
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="205" t="inlineStr">
         <is>
@@ -2433,6 +2442,21 @@
           <t>Действие (Торговля)</t>
         </is>
       </c>
+      <c r="E4" s="205" t="inlineStr">
+        <is>
+          <t>Раздел</t>
+        </is>
+      </c>
+      <c r="F4" s="205" t="inlineStr">
+        <is>
+          <t>Буква</t>
+        </is>
+      </c>
+      <c r="G4" s="205" t="inlineStr">
+        <is>
+          <t>Последний номер</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="206" t="inlineStr">
@@ -2445,6 +2469,19 @@
           <t>Buy</t>
         </is>
       </c>
+      <c r="E5" s="206" t="inlineStr">
+        <is>
+          <t>Торговля</t>
+        </is>
+      </c>
+      <c r="F5" s="206" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G5" s="206">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="206" t="inlineStr">
@@ -2457,6 +2494,19 @@
           <t>Sell</t>
         </is>
       </c>
+      <c r="E6" s="206" t="inlineStr">
+        <is>
+          <t>Лэндинг</t>
+        </is>
+      </c>
+      <c r="F6" s="206" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G6" s="206">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="206" t="inlineStr">
@@ -2465,6 +2515,19 @@
         </is>
       </c>
       <c r="C7" s="207" t="n"/>
+      <c r="E7" s="206" t="inlineStr">
+        <is>
+          <t>Пулы</t>
+        </is>
+      </c>
+      <c r="F7" s="206" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G7" s="206">
+        <v>8</v>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="206" t="inlineStr">
@@ -2495,8 +2558,9 @@
       <c r="C11" s="207" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B1:H2"/>
+    <mergeCell ref="E3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -2626,7 +2690,7 @@
       </c>
       <c r="F5" s="240" t="n"/>
       <c r="G5" s="177" t="n"/>
-      <c r="H5" s="271">
+      <c r="H5" s="271" t="str">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER(G5)),F5*G5,"")</f>
         <v/>
       </c>
@@ -2638,19 +2702,19 @@
       </c>
       <c r="K5" s="271">
         <f>IF(AND(ISNUMBER(I5),ISNUMBER(J5)),I5*J5,"")</f>
-        <v/>
+        <v>1796.4</v>
       </c>
       <c r="L5" s="240">
         <f>IF(COUNT(F5,I5)=0,"",N(F5)-N(I5))</f>
-        <v/>
+        <v>-3</v>
       </c>
       <c r="M5" s="241">
         <f>IF(COUNT(H5,K5)=0,"",N(K5)-N(H5))</f>
-        <v/>
+        <v>1796.4</v>
       </c>
       <c r="N5" s="240">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER(G5),F5&gt;0,1-N(Ввод!$J$19)/100&gt;0),G5/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I5),ISNUMBER(J5),I5&gt;0),J5/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>597.604790419162</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -2680,25 +2744,25 @@
       </c>
       <c r="H6" s="271">
         <f>IF(AND(ISNUMBER(F6),ISNUMBER(G6)),F6*G6,"")</f>
-        <v/>
+        <v>6212.4</v>
       </c>
       <c r="I6" s="246" t="n"/>
       <c r="J6" s="183" t="n"/>
-      <c r="K6" s="271">
+      <c r="K6" s="271" t="str">
         <f>IF(AND(ISNUMBER(I6),ISNUMBER(J6)),I6*J6,"")</f>
         <v/>
       </c>
       <c r="L6" s="246">
         <f>IF(COUNT(F6,I6)=0,"",N(F6)-N(I6))</f>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="M6" s="247">
         <f>IF(COUNT(H6,K6)=0,"",N(K6)-N(H6))</f>
-        <v/>
+        <v>-6212.4</v>
       </c>
       <c r="N6" s="246">
         <f>IF(AND(ISNUMBER(F6),ISNUMBER(G6),F6&gt;0,1-N(Ввод!$J$19)/100&gt;0),G6/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I6),ISNUMBER(J6),I6&gt;0),J6/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>62248.496993988</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -2722,7 +2786,7 @@
       </c>
       <c r="F7" s="240" t="n"/>
       <c r="G7" s="177" t="n"/>
-      <c r="H7" s="271">
+      <c r="H7" s="271" t="str">
         <f>IF(AND(ISNUMBER(F7),ISNUMBER(G7)),F7*G7,"")</f>
         <v/>
       </c>
@@ -2734,19 +2798,19 @@
       </c>
       <c r="K7" s="271">
         <f>IF(AND(ISNUMBER(I7),ISNUMBER(J7)),I7*J7,"")</f>
-        <v/>
+        <v>0.0785925</v>
       </c>
       <c r="L7" s="240">
         <f>IF(COUNT(F7,I7)=0,"",N(F7)-N(I7))</f>
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="M7" s="241">
         <f>IF(COUNT(H7,K7)=0,"",N(K7)-N(H7))</f>
-        <v/>
+        <v>0.0785925</v>
       </c>
       <c r="N7" s="240">
         <f>IF(AND(ISNUMBER(F7),ISNUMBER(G7),F7&gt;0,1-N(Ввод!$J$19)/100&gt;0),G7/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I7),ISNUMBER(J7),I7&gt;0),J7/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>0.0522904191616766</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -2776,25 +2840,25 @@
       </c>
       <c r="H8" s="271">
         <f>IF(AND(ISNUMBER(F8),ISNUMBER(G8)),F8*G8,"")</f>
-        <v/>
+        <v>3206.4</v>
       </c>
       <c r="I8" s="246" t="n"/>
       <c r="J8" s="183" t="n"/>
-      <c r="K8" s="271">
+      <c r="K8" s="271" t="str">
         <f>IF(AND(ISNUMBER(I8),ISNUMBER(J8)),I8*J8,"")</f>
         <v/>
       </c>
       <c r="L8" s="246">
         <f>IF(COUNT(F8,I8)=0,"",N(F8)-N(I8))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M8" s="247">
         <f>IF(COUNT(H8,K8)=0,"",N(K8)-N(H8))</f>
-        <v/>
+        <v>-3206.4</v>
       </c>
       <c r="N8" s="246">
         <f>IF(AND(ISNUMBER(F8),ISNUMBER(G8),F8&gt;0,1-N(Ввод!$J$19)/100&gt;0),G8/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I8),ISNUMBER(J8),I8&gt;0),J8/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>3212.82565130261</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -2824,25 +2888,25 @@
       </c>
       <c r="H9" s="271">
         <f>IF(AND(ISNUMBER(F9),ISNUMBER(G9)),F9*G9,"")</f>
-        <v/>
+        <v>3823.632</v>
       </c>
       <c r="I9" s="240" t="n"/>
       <c r="J9" s="177" t="n"/>
-      <c r="K9" s="271">
+      <c r="K9" s="271" t="str">
         <f>IF(AND(ISNUMBER(I9),ISNUMBER(J9)),I9*J9,"")</f>
         <v/>
       </c>
       <c r="L9" s="240">
         <f>IF(COUNT(F9,I9)=0,"",N(F9)-N(I9))</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="M9" s="241">
         <f>IF(COUNT(H9,K9)=0,"",N(K9)-N(H9))</f>
-        <v/>
+        <v>-3823.632</v>
       </c>
       <c r="N9" s="240">
         <f>IF(AND(ISNUMBER(F9),ISNUMBER(G9),F9&gt;0,1-N(Ввод!$J$19)/100&gt;0),G9/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I9),ISNUMBER(J9),I9&gt;0),J9/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>3192.74549098196</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -2872,25 +2936,25 @@
       </c>
       <c r="H10" s="271">
         <f>IF(AND(ISNUMBER(F10),ISNUMBER(G10)),F10*G10,"")</f>
-        <v/>
+        <v>2605.2</v>
       </c>
       <c r="I10" s="246" t="n"/>
       <c r="J10" s="183" t="n"/>
-      <c r="K10" s="271">
+      <c r="K10" s="271" t="str">
         <f>IF(AND(ISNUMBER(I10),ISNUMBER(J10)),I10*J10,"")</f>
         <v/>
       </c>
       <c r="L10" s="246">
         <f>IF(COUNT(F10,I10)=0,"",N(F10)-N(I10))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="M10" s="247">
         <f>IF(COUNT(H10,K10)=0,"",N(K10)-N(H10))</f>
-        <v/>
+        <v>-2605.2</v>
       </c>
       <c r="N10" s="246">
         <f>IF(AND(ISNUMBER(F10),ISNUMBER(G10),F10&gt;0,1-N(Ввод!$J$19)/100&gt;0),G10/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I10),ISNUMBER(J10),I10&gt;0),J10/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>3263.02605210421</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -2914,7 +2978,7 @@
       </c>
       <c r="F11" s="240" t="n"/>
       <c r="G11" s="177" t="n"/>
-      <c r="H11" s="271">
+      <c r="H11" s="271" t="str">
         <f>IF(AND(ISNUMBER(F11),ISNUMBER(G11)),F11*G11,"")</f>
         <v/>
       </c>
@@ -2926,19 +2990,19 @@
       </c>
       <c r="K11" s="271">
         <f>IF(AND(ISNUMBER(I11),ISNUMBER(J11)),I11*J11,"")</f>
-        <v/>
+        <v>5089.8</v>
       </c>
       <c r="L11" s="240">
         <f>IF(COUNT(F11,I11)=0,"",N(F11)-N(I11))</f>
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="M11" s="241">
         <f>IF(COUNT(H11,K11)=0,"",N(K11)-N(H11))</f>
-        <v/>
+        <v>5089.8</v>
       </c>
       <c r="N11" s="240">
         <f>IF(AND(ISNUMBER(F11),ISNUMBER(G11),F11&gt;0,1-N(Ввод!$J$19)/100&gt;0),G11/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I11),ISNUMBER(J11),I11&gt;0),J11/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>3386.42714570858</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -2962,7 +3026,7 @@
       </c>
       <c r="F12" s="246" t="n"/>
       <c r="G12" s="183" t="n"/>
-      <c r="H12" s="271">
+      <c r="H12" s="271" t="str">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER(G12)),F12*G12,"")</f>
         <v/>
       </c>
@@ -2974,19 +3038,19 @@
       </c>
       <c r="K12" s="271">
         <f>IF(AND(ISNUMBER(I12),ISNUMBER(J12)),I12*J12,"")</f>
-        <v/>
+        <v>4491</v>
       </c>
       <c r="L12" s="246">
         <f>IF(COUNT(F12,I12)=0,"",N(F12)-N(I12))</f>
-        <v/>
+        <v>-30</v>
       </c>
       <c r="M12" s="247">
         <f>IF(COUNT(H12,K12)=0,"",N(K12)-N(H12))</f>
-        <v/>
+        <v>4491</v>
       </c>
       <c r="N12" s="246">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER(G12),F12&gt;0,1-N(Ввод!$J$19)/100&gt;0),G12/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I12),ISNUMBER(J12),I12&gt;0),J12/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>149.40119760479</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -3010,7 +3074,7 @@
       </c>
       <c r="F13" s="240" t="n"/>
       <c r="G13" s="177" t="n"/>
-      <c r="H13" s="271">
+      <c r="H13" s="271" t="str">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER(G13)),F13*G13,"")</f>
         <v/>
       </c>
@@ -3022,19 +3086,19 @@
       </c>
       <c r="K13" s="271">
         <f>IF(AND(ISNUMBER(I13),ISNUMBER(J13)),I13*J13,"")</f>
-        <v/>
+        <v>1516.96</v>
       </c>
       <c r="L13" s="240">
         <f>IF(COUNT(F13,I13)=0,"",N(F13)-N(I13))</f>
-        <v/>
+        <v>-10</v>
       </c>
       <c r="M13" s="241">
         <f>IF(COUNT(H13,K13)=0,"",N(K13)-N(H13))</f>
-        <v/>
+        <v>1516.96</v>
       </c>
       <c r="N13" s="240">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER(G13),F13&gt;0,1-N(Ввод!$J$19)/100&gt;0),G13/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I13),ISNUMBER(J13),I13&gt;0),J13/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>151.393213572854</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -3064,25 +3128,25 @@
       </c>
       <c r="H14" s="271">
         <f>IF(AND(ISNUMBER(F14),ISNUMBER(G14)),F14*G14,"")</f>
-        <v/>
+        <v>3657.3</v>
       </c>
       <c r="I14" s="246" t="n"/>
       <c r="J14" s="183" t="n"/>
-      <c r="K14" s="271">
+      <c r="K14" s="271" t="str">
         <f>IF(AND(ISNUMBER(I14),ISNUMBER(J14)),I14*J14,"")</f>
         <v/>
       </c>
       <c r="L14" s="246">
         <f>IF(COUNT(F14,I14)=0,"",N(F14)-N(I14))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="M14" s="247">
         <f>IF(COUNT(H14,K14)=0,"",N(K14)-N(H14))</f>
-        <v/>
+        <v>-3657.3</v>
       </c>
       <c r="N14" s="246">
         <f>IF(AND(ISNUMBER(F14),ISNUMBER(G14),F14&gt;0,1-N(Ввод!$J$19)/100&gt;0),G14/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I14),ISNUMBER(J14),I14&gt;0),J14/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>146.585170340681</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -3092,25 +3156,25 @@
       <c r="E15" s="239" t="n"/>
       <c r="F15" s="240" t="n"/>
       <c r="G15" s="177" t="n"/>
-      <c r="H15" s="271">
+      <c r="H15" s="271" t="str">
         <f>IF(AND(ISNUMBER(F15),ISNUMBER(G15)),F15*G15,"")</f>
         <v/>
       </c>
       <c r="I15" s="240" t="n"/>
       <c r="J15" s="177" t="n"/>
-      <c r="K15" s="271">
+      <c r="K15" s="271" t="str">
         <f>IF(AND(ISNUMBER(I15),ISNUMBER(J15)),I15*J15,"")</f>
         <v/>
       </c>
-      <c r="L15" s="240">
+      <c r="L15" s="240" t="str">
         <f>IF(COUNT(F15,I15)=0,"",N(F15)-N(I15))</f>
         <v/>
       </c>
-      <c r="M15" s="241">
+      <c r="M15" s="241" t="str">
         <f>IF(COUNT(H15,K15)=0,"",N(K15)-N(H15))</f>
         <v/>
       </c>
-      <c r="N15" s="240">
+      <c r="N15" s="240" t="str">
         <f>IF(AND(ISNUMBER(F15),ISNUMBER(G15),F15&gt;0,1-N(Ввод!$J$19)/100&gt;0),G15/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I15),ISNUMBER(J15),I15&gt;0),J15/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
@@ -3122,25 +3186,25 @@
       <c r="E16" s="245" t="n"/>
       <c r="F16" s="246" t="n"/>
       <c r="G16" s="183" t="n"/>
-      <c r="H16" s="271">
+      <c r="H16" s="271" t="str">
         <f>IF(AND(ISNUMBER(F16),ISNUMBER(G16)),F16*G16,"")</f>
         <v/>
       </c>
       <c r="I16" s="246" t="n"/>
       <c r="J16" s="183" t="n"/>
-      <c r="K16" s="271">
+      <c r="K16" s="271" t="str">
         <f>IF(AND(ISNUMBER(I16),ISNUMBER(J16)),I16*J16,"")</f>
         <v/>
       </c>
-      <c r="L16" s="246">
+      <c r="L16" s="246" t="str">
         <f>IF(COUNT(F16,I16)=0,"",N(F16)-N(I16))</f>
         <v/>
       </c>
-      <c r="M16" s="247">
+      <c r="M16" s="247" t="str">
         <f>IF(COUNT(H16,K16)=0,"",N(K16)-N(H16))</f>
         <v/>
       </c>
-      <c r="N16" s="246">
+      <c r="N16" s="246" t="str">
         <f>IF(AND(ISNUMBER(F16),ISNUMBER(G16),F16&gt;0,1-N(Ввод!$J$19)/100&gt;0),G16/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I16),ISNUMBER(J16),I16&gt;0),J16/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
@@ -3264,47 +3328,47 @@
       </c>
       <c r="C5" s="240">
         <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D5" s="177">
         <f>IF(C5="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B5)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B5)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C5)</f>
-        <v/>
+        <v>586.17</v>
       </c>
       <c r="E5" s="241">
         <f>IF(C5="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>1172.34</v>
       </c>
       <c r="F5" s="240">
         <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G5" s="177">
         <f>IF(F5="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B5)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B5)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F5)</f>
-        <v/>
+        <v>598.8</v>
       </c>
       <c r="H5" s="241">
         <f>IF(F5="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>2994</v>
       </c>
       <c r="I5" s="240">
         <f>IF($B5="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B5)+COUNTIFS(Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
-        <v/>
+        <v>-3</v>
       </c>
       <c r="J5" s="241">
         <f>IF($B5="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B5)+COUNTIFS(Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
-        <v/>
+        <v>1821.66</v>
       </c>
       <c r="K5" s="240">
         <f>IF(MIN(N(C5),N(F5))&lt;=0,"",ROUND(MIN(N(C5),N(F5))*(N(G5)-N(D5)),8))</f>
-        <v/>
+        <v>25.26</v>
       </c>
       <c r="L5" s="177">
         <f>IF(MIN(N(C5),N(F5))&lt;=0,"",IF(N(D5)=0,"",ROUND((N(G5)/N(D5)-1)*100,2)))</f>
-        <v/>
+        <v>2.15</v>
       </c>
       <c r="M5" s="177">
         <f>IF(OR(ROUND(N(C5)-N(F5),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C5)&gt;N(F5),(N(E5)-N(H5))/((N(C5)-N(F5))*(1-N(Ввод!$J$19)/100)),(N(H5)-N(E5))/((N(F5)-N(C5))*(1+N(Ввод!$J$19)/100))))</f>
-        <v/>
+        <v>606.007984031936</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -3315,47 +3379,47 @@
       </c>
       <c r="C6" s="246">
         <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="D6" s="183">
         <f>IF(C6="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B6)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B6)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C6)</f>
-        <v/>
+        <v>62190.8</v>
       </c>
       <c r="E6" s="247">
         <f>IF(C6="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>9328.62</v>
       </c>
       <c r="F6" s="246">
         <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>0.05</v>
       </c>
       <c r="G6" s="183">
         <f>IF(F6="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B6)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B6)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F6)</f>
-        <v/>
+        <v>62874</v>
       </c>
       <c r="H6" s="247">
         <f>IF(F6="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>3143.7</v>
       </c>
       <c r="I6" s="246">
         <f>IF($B6="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B6)+COUNTIFS(Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="J6" s="247">
         <f>IF($B6="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B6)+COUNTIFS(Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
-        <v/>
+        <v>-6184.92</v>
       </c>
       <c r="K6" s="246">
         <f>IF(MIN(N(C6),N(F6))&lt;=0,"",ROUND(MIN(N(C6),N(F6))*(N(G6)-N(D6)),8))</f>
-        <v/>
+        <v>34.16</v>
       </c>
       <c r="L6" s="183">
         <f>IF(MIN(N(C6),N(F6))&lt;=0,"",IF(N(D6)=0,"",ROUND((N(G6)/N(D6)-1)*100,2)))</f>
-        <v/>
+        <v>1.1</v>
       </c>
       <c r="M6" s="183">
         <f>IF(OR(ROUND(N(C6)-N(F6),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C6)&gt;N(F6),(N(E6)-N(H6))/((N(C6)-N(F6))*(1-N(Ввод!$J$19)/100)),(N(H6)-N(E6))/((N(F6)-N(C6))*(1+N(Ввод!$J$19)/100))))</f>
-        <v/>
+        <v>61973.1462925852</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -3364,49 +3428,49 @@
           <t>ETH/BTC</t>
         </is>
       </c>
-      <c r="C7" s="240">
+      <c r="C7" s="240" t="str">
         <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="D7" s="177">
+      <c r="D7" s="177" t="str">
         <f>IF(C7="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B7)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B7)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C7)</f>
         <v/>
       </c>
-      <c r="E7" s="241">
+      <c r="E7" s="241" t="str">
         <f>IF(C7="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
       <c r="F7" s="240">
         <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="G7" s="177">
         <f>IF(F7="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B7)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B7)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F7)</f>
-        <v/>
+        <v>0.052395</v>
       </c>
       <c r="H7" s="241">
         <f>IF(F7="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>0.0785925</v>
       </c>
       <c r="I7" s="240">
         <f>IF($B7="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B7)+COUNTIFS(Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="J7" s="241">
         <f>IF($B7="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B7)+COUNTIFS(Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
-        <v/>
-      </c>
-      <c r="K7" s="240">
+        <v>0.0785925</v>
+      </c>
+      <c r="K7" s="240" t="str">
         <f>IF(MIN(N(C7),N(F7))&lt;=0,"",ROUND(MIN(N(C7),N(F7))*(N(G7)-N(D7)),8))</f>
         <v/>
       </c>
-      <c r="L7" s="177">
+      <c r="L7" s="177" t="str">
         <f>IF(MIN(N(C7),N(F7))&lt;=0,"",IF(N(D7)=0,"",ROUND((N(G7)/N(D7)-1)*100,2)))</f>
         <v/>
       </c>
       <c r="M7" s="177">
         <f>IF(OR(ROUND(N(C7)-N(F7),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C7)&gt;N(F7),(N(E7)-N(H7))/((N(C7)-N(F7))*(1-N(Ввод!$J$19)/100)),(N(H7)-N(E7))/((N(F7)-N(C7))*(1+N(Ввод!$J$19)/100))))</f>
-        <v/>
+        <v>0.0522904191616766</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -3417,47 +3481,47 @@
       </c>
       <c r="C8" s="246">
         <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D8" s="183">
         <f>IF(C8="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B8)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B8)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C8)</f>
-        <v/>
+        <v>3210.408</v>
       </c>
       <c r="E8" s="247">
         <f>IF(C8="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>12841.632</v>
       </c>
       <c r="F8" s="246">
         <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="G8" s="183">
         <f>IF(F8="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B8)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B8)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F8)</f>
-        <v/>
+        <v>3373.24</v>
       </c>
       <c r="H8" s="247">
         <f>IF(F8="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>8433.1</v>
       </c>
       <c r="I8" s="246">
         <f>IF($B8="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B8)+COUNTIFS(Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="J8" s="247">
         <f>IF($B8="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B8)+COUNTIFS(Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
-        <v/>
+        <v>-4408.532</v>
       </c>
       <c r="K8" s="246">
         <f>IF(MIN(N(C8),N(F8))&lt;=0,"",ROUND(MIN(N(C8),N(F8))*(N(G8)-N(D8)),8))</f>
-        <v/>
+        <v>407.08</v>
       </c>
       <c r="L8" s="183">
         <f>IF(MIN(N(C8),N(F8))&lt;=0,"",IF(N(D8)=0,"",ROUND((N(G8)/N(D8)-1)*100,2)))</f>
-        <v/>
+        <v>5.07</v>
       </c>
       <c r="M8" s="183">
         <f>IF(OR(ROUND(N(C8)-N(F8),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C8)&gt;N(F8),(N(E8)-N(H8))/((N(C8)-N(F8))*(1-N(Ввод!$J$19)/100)),(N(H8)-N(E8))/((N(F8)-N(C8))*(1+N(Ввод!$J$19)/100))))</f>
-        <v/>
+        <v>2944.91115564462</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -3468,186 +3532,186 @@
       </c>
       <c r="C9" s="240">
         <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="D9" s="177">
         <f>IF(C9="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B9)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B9)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C9)</f>
-        <v/>
+        <v>145.846666666667</v>
       </c>
       <c r="E9" s="241">
         <f>IF(C9="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>6563.1</v>
       </c>
       <c r="F9" s="240">
         <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>60</v>
       </c>
       <c r="G9" s="177">
         <f>IF(F9="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B9)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B9)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F9)</f>
-        <v/>
+        <v>150.698</v>
       </c>
       <c r="H9" s="241">
         <f>IF(F9="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*"))</f>
-        <v/>
+        <v>9041.88</v>
       </c>
       <c r="I9" s="240">
         <f>IF($B9="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B9)+COUNTIFS(Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
-        <v/>
+        <v>-15</v>
       </c>
       <c r="J9" s="241">
         <f>IF($B9="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B9)+COUNTIFS(Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
-        <v/>
+        <v>2478.78</v>
       </c>
       <c r="K9" s="240">
         <f>IF(MIN(N(C9),N(F9))&lt;=0,"",ROUND(MIN(N(C9),N(F9))*(N(G9)-N(D9)),8))</f>
-        <v/>
+        <v>218.31</v>
       </c>
       <c r="L9" s="177">
         <f>IF(MIN(N(C9),N(F9))&lt;=0,"",IF(N(D9)=0,"",ROUND((N(G9)/N(D9)-1)*100,2)))</f>
-        <v/>
+        <v>3.33</v>
       </c>
       <c r="M9" s="177">
         <f>IF(OR(ROUND(N(C9)-N(F9),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C9)&gt;N(F9),(N(E9)-N(H9))/((N(C9)-N(F9))*(1-N(Ввод!$J$19)/100)),(N(H9)-N(E9))/((N(F9)-N(C9))*(1+N(Ввод!$J$19)/100))))</f>
-        <v/>
+        <v>164.922155688623</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="245" t="n"/>
-      <c r="C10" s="246">
+      <c r="C10" s="246" t="str">
         <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="D10" s="183">
+      <c r="D10" s="183" t="str">
         <f>IF(C10="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B10)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B10)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C10)</f>
         <v/>
       </c>
-      <c r="E10" s="247">
+      <c r="E10" s="247" t="str">
         <f>IF(C10="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="F10" s="246">
+      <c r="F10" s="246" t="str">
         <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="G10" s="183">
+      <c r="G10" s="183" t="str">
         <f>IF(F10="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B10)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B10)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F10)</f>
         <v/>
       </c>
-      <c r="H10" s="247">
+      <c r="H10" s="247" t="str">
         <f>IF(F10="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="I10" s="246">
+      <c r="I10" s="246" t="str">
         <f>IF($B10="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B10)+COUNTIFS(Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
-      <c r="J10" s="247">
+      <c r="J10" s="247" t="str">
         <f>IF($B10="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B10)+COUNTIFS(Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
-      <c r="K10" s="246">
+      <c r="K10" s="246" t="str">
         <f>IF(MIN(N(C10),N(F10))&lt;=0,"",ROUND(MIN(N(C10),N(F10))*(N(G10)-N(D10)),8))</f>
         <v/>
       </c>
-      <c r="L10" s="183">
+      <c r="L10" s="183" t="str">
         <f>IF(MIN(N(C10),N(F10))&lt;=0,"",IF(N(D10)=0,"",ROUND((N(G10)/N(D10)-1)*100,2)))</f>
         <v/>
       </c>
-      <c r="M10" s="183">
+      <c r="M10" s="183" t="str">
         <f>IF(OR(ROUND(N(C10)-N(F10),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C10)&gt;N(F10),(N(E10)-N(H10))/((N(C10)-N(F10))*(1-N(Ввод!$J$19)/100)),(N(H10)-N(E10))/((N(F10)-N(C10))*(1+N(Ввод!$J$19)/100))))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="239" t="n"/>
-      <c r="C11" s="240">
+      <c r="C11" s="240" t="str">
         <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="D11" s="177">
+      <c r="D11" s="177" t="str">
         <f>IF(C11="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B11)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B11)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C11)</f>
         <v/>
       </c>
-      <c r="E11" s="241">
+      <c r="E11" s="241" t="str">
         <f>IF(C11="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="F11" s="240">
+      <c r="F11" s="240" t="str">
         <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="G11" s="177">
+      <c r="G11" s="177" t="str">
         <f>IF(F11="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B11)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B11)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F11)</f>
         <v/>
       </c>
-      <c r="H11" s="241">
+      <c r="H11" s="241" t="str">
         <f>IF(F11="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="I11" s="240">
+      <c r="I11" s="240" t="str">
         <f>IF($B11="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B11)+COUNTIFS(Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
-      <c r="J11" s="241">
+      <c r="J11" s="241" t="str">
         <f>IF($B11="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B11)+COUNTIFS(Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
-      <c r="K11" s="240">
+      <c r="K11" s="240" t="str">
         <f>IF(MIN(N(C11),N(F11))&lt;=0,"",ROUND(MIN(N(C11),N(F11))*(N(G11)-N(D11)),8))</f>
         <v/>
       </c>
-      <c r="L11" s="177">
+      <c r="L11" s="177" t="str">
         <f>IF(MIN(N(C11),N(F11))&lt;=0,"",IF(N(D11)=0,"",ROUND((N(G11)/N(D11)-1)*100,2)))</f>
         <v/>
       </c>
-      <c r="M11" s="177">
+      <c r="M11" s="177" t="str">
         <f>IF(OR(ROUND(N(C11)-N(F11),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C11)&gt;N(F11),(N(E11)-N(H11))/((N(C11)-N(F11))*(1-N(Ввод!$J$19)/100)),(N(H11)-N(E11))/((N(F11)-N(C11))*(1+N(Ввод!$J$19)/100))))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="245" t="n"/>
-      <c r="C12" s="246">
+      <c r="C12" s="246" t="str">
         <f>IF(SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$F$5:$F$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="D12" s="183">
+      <c r="D12" s="183" t="str">
         <f>IF(C12="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B12)*Торговля!$F$5:$F$200*Торговля!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B12)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C12)</f>
         <v/>
       </c>
-      <c r="E12" s="247">
+      <c r="E12" s="247" t="str">
         <f>IF(C12="","",SUMIFS(Торговля!$H$5:$H$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="F12" s="246">
+      <c r="F12" s="246" t="str">
         <f>IF(SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*")=0,"",SUMIFS(Торговля!$I$5:$I$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="G12" s="183">
+      <c r="G12" s="183" t="str">
         <f>IF(F12="","",(SUMPRODUCT((Торговля!$E$5:$E$200=$B12)*Торговля!$I$5:$I$200*Торговля!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B12)*(LEFT(Закрытые!$B$5:$B$200,2)="T-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F12)</f>
         <v/>
       </c>
-      <c r="H12" s="247">
+      <c r="H12" s="247" t="str">
         <f>IF(F12="","",SUMIFS(Торговля!$K$5:$K$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*"))</f>
         <v/>
       </c>
-      <c r="I12" s="246">
+      <c r="I12" s="246" t="str">
         <f>IF($B12="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B12)+COUNTIFS(Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$L$5:$L$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
-      <c r="J12" s="247">
+      <c r="J12" s="247" t="str">
         <f>IF($B12="","",IF(COUNTIFS(Торговля!$E$5:$E$200,$B12)+COUNTIFS(Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*")=0,"",ROUND(SUMIFS(Торговля!$M$5:$M$200,Торговля!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"T-*"),8)))</f>
         <v/>
       </c>
-      <c r="K12" s="246">
+      <c r="K12" s="246" t="str">
         <f>IF(MIN(N(C12),N(F12))&lt;=0,"",ROUND(MIN(N(C12),N(F12))*(N(G12)-N(D12)),8))</f>
         <v/>
       </c>
-      <c r="L12" s="183">
+      <c r="L12" s="183" t="str">
         <f>IF(MIN(N(C12),N(F12))&lt;=0,"",IF(N(D12)=0,"",ROUND((N(G12)/N(D12)-1)*100,2)))</f>
         <v/>
       </c>
-      <c r="M12" s="183">
+      <c r="M12" s="183" t="str">
         <f>IF(OR(ROUND(N(C12)-N(F12),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C12)&gt;N(F12),(N(E12)-N(H12))/((N(C12)-N(F12))*(1-N(Ввод!$J$19)/100)),(N(H12)-N(E12))/((N(F12)-N(C12))*(1+N(Ввод!$J$19)/100))))</f>
         <v/>
       </c>
@@ -3785,7 +3849,7 @@
       </c>
       <c r="F5" s="240" t="n"/>
       <c r="G5" s="177" t="n"/>
-      <c r="H5" s="271">
+      <c r="H5" s="271" t="str">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER(G5)),F5*G5,"")</f>
         <v/>
       </c>
@@ -3797,19 +3861,19 @@
       </c>
       <c r="K5" s="271">
         <f>IF(AND(ISNUMBER(I5),ISNUMBER(J5)),I5*J5,"")</f>
-        <v/>
+        <v>1796.4</v>
       </c>
       <c r="L5" s="240">
         <f>IF(COUNT(F5,I5)=0,"",N(F5)-N(I5))</f>
-        <v/>
+        <v>-3</v>
       </c>
       <c r="M5" s="241">
         <f>IF(COUNT(H5,K5)=0,"",N(K5)-N(H5))</f>
-        <v/>
+        <v>1796.4</v>
       </c>
       <c r="N5" s="240">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER(G5),F5&gt;0,1-N(Ввод!$J$19)/100&gt;0),G5/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I5),ISNUMBER(J5),I5&gt;0),J5/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>597.604790419162</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -3839,25 +3903,25 @@
       </c>
       <c r="H6" s="271">
         <f>IF(AND(ISNUMBER(F6),ISNUMBER(G6)),F6*G6,"")</f>
-        <v/>
+        <v>6212.4</v>
       </c>
       <c r="I6" s="246" t="n"/>
       <c r="J6" s="183" t="n"/>
-      <c r="K6" s="271">
+      <c r="K6" s="271" t="str">
         <f>IF(AND(ISNUMBER(I6),ISNUMBER(J6)),I6*J6,"")</f>
         <v/>
       </c>
       <c r="L6" s="246">
         <f>IF(COUNT(F6,I6)=0,"",N(F6)-N(I6))</f>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="M6" s="247">
         <f>IF(COUNT(H6,K6)=0,"",N(K6)-N(H6))</f>
-        <v/>
+        <v>-6212.4</v>
       </c>
       <c r="N6" s="246">
         <f>IF(AND(ISNUMBER(F6),ISNUMBER(G6),F6&gt;0,1-N(Ввод!$J$19)/100&gt;0),G6/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I6),ISNUMBER(J6),I6&gt;0),J6/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>62248.496993988</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -3881,7 +3945,7 @@
       </c>
       <c r="F7" s="240" t="n"/>
       <c r="G7" s="177" t="n"/>
-      <c r="H7" s="271">
+      <c r="H7" s="271" t="str">
         <f>IF(AND(ISNUMBER(F7),ISNUMBER(G7)),F7*G7,"")</f>
         <v/>
       </c>
@@ -3893,19 +3957,19 @@
       </c>
       <c r="K7" s="271">
         <f>IF(AND(ISNUMBER(I7),ISNUMBER(J7)),I7*J7,"")</f>
-        <v/>
+        <v>0.0785925</v>
       </c>
       <c r="L7" s="240">
         <f>IF(COUNT(F7,I7)=0,"",N(F7)-N(I7))</f>
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="M7" s="241">
         <f>IF(COUNT(H7,K7)=0,"",N(K7)-N(H7))</f>
-        <v/>
+        <v>0.0785925</v>
       </c>
       <c r="N7" s="240">
         <f>IF(AND(ISNUMBER(F7),ISNUMBER(G7),F7&gt;0,1-N(Ввод!$J$19)/100&gt;0),G7/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I7),ISNUMBER(J7),I7&gt;0),J7/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>0.0522904191616766</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -3935,25 +3999,25 @@
       </c>
       <c r="H8" s="271">
         <f>IF(AND(ISNUMBER(F8),ISNUMBER(G8)),F8*G8,"")</f>
-        <v/>
+        <v>3206.4</v>
       </c>
       <c r="I8" s="246" t="n"/>
       <c r="J8" s="183" t="n"/>
-      <c r="K8" s="271">
+      <c r="K8" s="271" t="str">
         <f>IF(AND(ISNUMBER(I8),ISNUMBER(J8)),I8*J8,"")</f>
         <v/>
       </c>
       <c r="L8" s="246">
         <f>IF(COUNT(F8,I8)=0,"",N(F8)-N(I8))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M8" s="247">
         <f>IF(COUNT(H8,K8)=0,"",N(K8)-N(H8))</f>
-        <v/>
+        <v>-3206.4</v>
       </c>
       <c r="N8" s="246">
         <f>IF(AND(ISNUMBER(F8),ISNUMBER(G8),F8&gt;0,1-N(Ввод!$J$19)/100&gt;0),G8/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I8),ISNUMBER(J8),I8&gt;0),J8/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>3212.82565130261</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -3983,25 +4047,25 @@
       </c>
       <c r="H9" s="271">
         <f>IF(AND(ISNUMBER(F9),ISNUMBER(G9)),F9*G9,"")</f>
-        <v/>
+        <v>3823.632</v>
       </c>
       <c r="I9" s="240" t="n"/>
       <c r="J9" s="177" t="n"/>
-      <c r="K9" s="271">
+      <c r="K9" s="271" t="str">
         <f>IF(AND(ISNUMBER(I9),ISNUMBER(J9)),I9*J9,"")</f>
         <v/>
       </c>
       <c r="L9" s="240">
         <f>IF(COUNT(F9,I9)=0,"",N(F9)-N(I9))</f>
-        <v/>
+        <v>1.2</v>
       </c>
       <c r="M9" s="241">
         <f>IF(COUNT(H9,K9)=0,"",N(K9)-N(H9))</f>
-        <v/>
+        <v>-3823.632</v>
       </c>
       <c r="N9" s="240">
         <f>IF(AND(ISNUMBER(F9),ISNUMBER(G9),F9&gt;0,1-N(Ввод!$J$19)/100&gt;0),G9/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I9),ISNUMBER(J9),I9&gt;0),J9/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>3192.74549098196</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -4031,25 +4095,25 @@
       </c>
       <c r="H10" s="271">
         <f>IF(AND(ISNUMBER(F10),ISNUMBER(G10)),F10*G10,"")</f>
-        <v/>
+        <v>2605.2</v>
       </c>
       <c r="I10" s="246" t="n"/>
       <c r="J10" s="183" t="n"/>
-      <c r="K10" s="271">
+      <c r="K10" s="271" t="str">
         <f>IF(AND(ISNUMBER(I10),ISNUMBER(J10)),I10*J10,"")</f>
         <v/>
       </c>
       <c r="L10" s="246">
         <f>IF(COUNT(F10,I10)=0,"",N(F10)-N(I10))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="M10" s="247">
         <f>IF(COUNT(H10,K10)=0,"",N(K10)-N(H10))</f>
-        <v/>
+        <v>-2605.2</v>
       </c>
       <c r="N10" s="246">
         <f>IF(AND(ISNUMBER(F10),ISNUMBER(G10),F10&gt;0,1-N(Ввод!$J$19)/100&gt;0),G10/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I10),ISNUMBER(J10),I10&gt;0),J10/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>3263.02605210421</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -4073,7 +4137,7 @@
       </c>
       <c r="F11" s="240" t="n"/>
       <c r="G11" s="177" t="n"/>
-      <c r="H11" s="271">
+      <c r="H11" s="271" t="str">
         <f>IF(AND(ISNUMBER(F11),ISNUMBER(G11)),F11*G11,"")</f>
         <v/>
       </c>
@@ -4085,19 +4149,19 @@
       </c>
       <c r="K11" s="271">
         <f>IF(AND(ISNUMBER(I11),ISNUMBER(J11)),I11*J11,"")</f>
-        <v/>
+        <v>5089.8</v>
       </c>
       <c r="L11" s="240">
         <f>IF(COUNT(F11,I11)=0,"",N(F11)-N(I11))</f>
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="M11" s="241">
         <f>IF(COUNT(H11,K11)=0,"",N(K11)-N(H11))</f>
-        <v/>
+        <v>5089.8</v>
       </c>
       <c r="N11" s="240">
         <f>IF(AND(ISNUMBER(F11),ISNUMBER(G11),F11&gt;0,1-N(Ввод!$J$19)/100&gt;0),G11/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I11),ISNUMBER(J11),I11&gt;0),J11/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>3386.42714570858</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -4121,7 +4185,7 @@
       </c>
       <c r="F12" s="246" t="n"/>
       <c r="G12" s="183" t="n"/>
-      <c r="H12" s="271">
+      <c r="H12" s="271" t="str">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER(G12)),F12*G12,"")</f>
         <v/>
       </c>
@@ -4133,19 +4197,19 @@
       </c>
       <c r="K12" s="271">
         <f>IF(AND(ISNUMBER(I12),ISNUMBER(J12)),I12*J12,"")</f>
-        <v/>
+        <v>4491</v>
       </c>
       <c r="L12" s="246">
         <f>IF(COUNT(F12,I12)=0,"",N(F12)-N(I12))</f>
-        <v/>
+        <v>-30</v>
       </c>
       <c r="M12" s="247">
         <f>IF(COUNT(H12,K12)=0,"",N(K12)-N(H12))</f>
-        <v/>
+        <v>4491</v>
       </c>
       <c r="N12" s="246">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER(G12),F12&gt;0,1-N(Ввод!$J$19)/100&gt;0),G12/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I12),ISNUMBER(J12),I12&gt;0),J12/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>149.40119760479</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
@@ -4169,7 +4233,7 @@
       </c>
       <c r="F13" s="240" t="n"/>
       <c r="G13" s="177" t="n"/>
-      <c r="H13" s="271">
+      <c r="H13" s="271" t="str">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER(G13)),F13*G13,"")</f>
         <v/>
       </c>
@@ -4181,19 +4245,19 @@
       </c>
       <c r="K13" s="271">
         <f>IF(AND(ISNUMBER(I13),ISNUMBER(J13)),I13*J13,"")</f>
-        <v/>
+        <v>1516.96</v>
       </c>
       <c r="L13" s="240">
         <f>IF(COUNT(F13,I13)=0,"",N(F13)-N(I13))</f>
-        <v/>
+        <v>-10</v>
       </c>
       <c r="M13" s="241">
         <f>IF(COUNT(H13,K13)=0,"",N(K13)-N(H13))</f>
-        <v/>
+        <v>1516.96</v>
       </c>
       <c r="N13" s="240">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER(G13),F13&gt;0,1-N(Ввод!$J$19)/100&gt;0),G13/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I13),ISNUMBER(J13),I13&gt;0),J13/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>151.393213572854</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -4223,25 +4287,25 @@
       </c>
       <c r="H14" s="271">
         <f>IF(AND(ISNUMBER(F14),ISNUMBER(G14)),F14*G14,"")</f>
-        <v/>
+        <v>3657.3</v>
       </c>
       <c r="I14" s="246" t="n"/>
       <c r="J14" s="183" t="n"/>
-      <c r="K14" s="271">
+      <c r="K14" s="271" t="str">
         <f>IF(AND(ISNUMBER(I14),ISNUMBER(J14)),I14*J14,"")</f>
         <v/>
       </c>
       <c r="L14" s="246">
         <f>IF(COUNT(F14,I14)=0,"",N(F14)-N(I14))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="M14" s="247">
         <f>IF(COUNT(H14,K14)=0,"",N(K14)-N(H14))</f>
-        <v/>
+        <v>-3657.3</v>
       </c>
       <c r="N14" s="246">
         <f>IF(AND(ISNUMBER(F14),ISNUMBER(G14),F14&gt;0,1-N(Ввод!$J$19)/100&gt;0),G14/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I14),ISNUMBER(J14),I14&gt;0),J14/(1+N(Ввод!$J$19)/100),""))</f>
-        <v/>
+        <v>146.585170340681</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -4251,25 +4315,25 @@
       <c r="E15" s="239" t="n"/>
       <c r="F15" s="240" t="n"/>
       <c r="G15" s="177" t="n"/>
-      <c r="H15" s="271">
+      <c r="H15" s="271" t="str">
         <f>IF(AND(ISNUMBER(F15),ISNUMBER(G15)),F15*G15,"")</f>
         <v/>
       </c>
       <c r="I15" s="240" t="n"/>
       <c r="J15" s="177" t="n"/>
-      <c r="K15" s="271">
+      <c r="K15" s="271" t="str">
         <f>IF(AND(ISNUMBER(I15),ISNUMBER(J15)),I15*J15,"")</f>
         <v/>
       </c>
-      <c r="L15" s="240">
+      <c r="L15" s="240" t="str">
         <f>IF(COUNT(F15,I15)=0,"",N(F15)-N(I15))</f>
         <v/>
       </c>
-      <c r="M15" s="241">
+      <c r="M15" s="241" t="str">
         <f>IF(COUNT(H15,K15)=0,"",N(K15)-N(H15))</f>
         <v/>
       </c>
-      <c r="N15" s="240">
+      <c r="N15" s="240" t="str">
         <f>IF(AND(ISNUMBER(F15),ISNUMBER(G15),F15&gt;0,1-N(Ввод!$J$19)/100&gt;0),G15/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I15),ISNUMBER(J15),I15&gt;0),J15/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
@@ -4281,25 +4345,25 @@
       <c r="E16" s="245" t="n"/>
       <c r="F16" s="246" t="n"/>
       <c r="G16" s="183" t="n"/>
-      <c r="H16" s="271">
+      <c r="H16" s="271" t="str">
         <f>IF(AND(ISNUMBER(F16),ISNUMBER(G16)),F16*G16,"")</f>
         <v/>
       </c>
       <c r="I16" s="246" t="n"/>
       <c r="J16" s="183" t="n"/>
-      <c r="K16" s="271">
+      <c r="K16" s="271" t="str">
         <f>IF(AND(ISNUMBER(I16),ISNUMBER(J16)),I16*J16,"")</f>
         <v/>
       </c>
-      <c r="L16" s="246">
+      <c r="L16" s="246" t="str">
         <f>IF(COUNT(F16,I16)=0,"",N(F16)-N(I16))</f>
         <v/>
       </c>
-      <c r="M16" s="247">
+      <c r="M16" s="247" t="str">
         <f>IF(COUNT(H16,K16)=0,"",N(K16)-N(H16))</f>
         <v/>
       </c>
-      <c r="N16" s="246">
+      <c r="N16" s="246" t="str">
         <f>IF(AND(ISNUMBER(F16),ISNUMBER(G16),F16&gt;0,1-N(Ввод!$J$19)/100&gt;0),G16/(1-N(Ввод!$J$19)/100),IF(AND(ISNUMBER(I16),ISNUMBER(J16),I16&gt;0),J16/(1+N(Ввод!$J$19)/100),""))</f>
         <v/>
       </c>
@@ -4423,47 +4487,47 @@
       </c>
       <c r="C5" s="240">
         <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="D5" s="177">
         <f>IF(C5="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B5)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B5)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C5)</f>
-        <v/>
+        <v>585</v>
       </c>
       <c r="E5" s="241">
         <f>IF(C5="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>877.5</v>
       </c>
       <c r="F5" s="240">
         <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>4.5</v>
       </c>
       <c r="G5" s="177">
         <f>IF(F5="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B5)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B5)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F5)</f>
-        <v/>
+        <v>598.2</v>
       </c>
       <c r="H5" s="241">
         <f>IF(F5="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>2691.9</v>
       </c>
       <c r="I5" s="240">
         <f>IF($B5="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B5)+COUNTIFS(Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
-        <v/>
+        <v>-3</v>
       </c>
       <c r="J5" s="241">
         <f>IF($B5="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B5)+COUNTIFS(Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B5)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B5,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
-        <v/>
+        <v>1814.4</v>
       </c>
       <c r="K5" s="240">
         <f>IF(MIN(N(C5),N(F5))&lt;=0,"",ROUND(MIN(N(C5),N(F5))*(N(G5)-N(D5)),8))</f>
-        <v/>
+        <v>19.8</v>
       </c>
       <c r="L5" s="177">
         <f>IF(MIN(N(C5),N(F5))&lt;=0,"",IF(N(D5)=0,"",ROUND((N(G5)/N(D5)-1)*100,2)))</f>
-        <v/>
+        <v>2.26</v>
       </c>
       <c r="M5" s="177">
         <f>IF(OR(ROUND(N(C5)-N(F5),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C5)&gt;N(F5),(N(E5)-N(H5))/((N(C5)-N(F5))*(1-N(Ввод!$J$19)/100)),(N(H5)-N(E5))/((N(F5)-N(C5))*(1+N(Ввод!$J$19)/100))))</f>
-        <v/>
+        <v>603.592814371257</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -4474,47 +4538,47 @@
       </c>
       <c r="C6" s="246">
         <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="D6" s="183">
         <f>IF(C6="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B6)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B6)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C6)</f>
-        <v/>
+        <v>62124</v>
       </c>
       <c r="E6" s="247">
         <f>IF(C6="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
-      </c>
-      <c r="F6" s="246">
+        <v>6212.4</v>
+      </c>
+      <c r="F6" s="246" t="str">
         <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="G6" s="183">
+      <c r="G6" s="183" t="str">
         <f>IF(F6="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B6)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B6)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F6)</f>
         <v/>
       </c>
-      <c r="H6" s="247">
+      <c r="H6" s="247" t="str">
         <f>IF(F6="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="I6" s="246">
         <f>IF($B6="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B6)+COUNTIFS(Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
-        <v/>
+        <v>0.1</v>
       </c>
       <c r="J6" s="247">
         <f>IF($B6="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B6)+COUNTIFS(Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B6)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B6,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
-        <v/>
-      </c>
-      <c r="K6" s="246">
+        <v>-6212.4</v>
+      </c>
+      <c r="K6" s="246" t="str">
         <f>IF(MIN(N(C6),N(F6))&lt;=0,"",ROUND(MIN(N(C6),N(F6))*(N(G6)-N(D6)),8))</f>
         <v/>
       </c>
-      <c r="L6" s="183">
+      <c r="L6" s="183" t="str">
         <f>IF(MIN(N(C6),N(F6))&lt;=0,"",IF(N(D6)=0,"",ROUND((N(G6)/N(D6)-1)*100,2)))</f>
         <v/>
       </c>
       <c r="M6" s="183">
         <f>IF(OR(ROUND(N(C6)-N(F6),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C6)&gt;N(F6),(N(E6)-N(H6))/((N(C6)-N(F6))*(1-N(Ввод!$J$19)/100)),(N(H6)-N(E6))/((N(F6)-N(C6))*(1+N(Ввод!$J$19)/100))))</f>
-        <v/>
+        <v>62248.496993988</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -4523,49 +4587,49 @@
           <t>ETH/BTC</t>
         </is>
       </c>
-      <c r="C7" s="240">
+      <c r="C7" s="240" t="str">
         <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="D7" s="177">
+      <c r="D7" s="177" t="str">
         <f>IF(C7="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B7)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B7)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C7)</f>
         <v/>
       </c>
-      <c r="E7" s="241">
+      <c r="E7" s="241" t="str">
         <f>IF(C7="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
       <c r="F7" s="240">
         <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="G7" s="177">
         <f>IF(F7="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B7)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B7)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F7)</f>
-        <v/>
+        <v>0.052395</v>
       </c>
       <c r="H7" s="241">
         <f>IF(F7="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>0.0785925</v>
       </c>
       <c r="I7" s="240">
         <f>IF($B7="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B7)+COUNTIFS(Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="J7" s="241">
         <f>IF($B7="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B7)+COUNTIFS(Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B7)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B7,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
-        <v/>
-      </c>
-      <c r="K7" s="240">
+        <v>0.0785925</v>
+      </c>
+      <c r="K7" s="240" t="str">
         <f>IF(MIN(N(C7),N(F7))&lt;=0,"",ROUND(MIN(N(C7),N(F7))*(N(G7)-N(D7)),8))</f>
         <v/>
       </c>
-      <c r="L7" s="177">
+      <c r="L7" s="177" t="str">
         <f>IF(MIN(N(C7),N(F7))&lt;=0,"",IF(N(D7)=0,"",ROUND((N(G7)/N(D7)-1)*100,2)))</f>
         <v/>
       </c>
       <c r="M7" s="177">
         <f>IF(OR(ROUND(N(C7)-N(F7),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C7)&gt;N(F7),(N(E7)-N(H7))/((N(C7)-N(F7))*(1-N(Ввод!$J$19)/100)),(N(H7)-N(E7))/((N(F7)-N(C7))*(1+N(Ввод!$J$19)/100))))</f>
-        <v/>
+        <v>0.0522904191616766</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -4576,47 +4640,47 @@
       </c>
       <c r="C8" s="246">
         <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>3.5</v>
       </c>
       <c r="D8" s="183">
         <f>IF(C8="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B8)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B8)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C8)</f>
-        <v/>
+        <v>3211.49485714286</v>
       </c>
       <c r="E8" s="247">
         <f>IF(C8="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>11240.232</v>
       </c>
       <c r="F8" s="246">
         <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G8" s="183">
         <f>IF(F8="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B8)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B8)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F8)</f>
-        <v/>
+        <v>3379.9</v>
       </c>
       <c r="H8" s="247">
         <f>IF(F8="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>6759.8</v>
       </c>
       <c r="I8" s="246">
         <f>IF($B8="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B8)+COUNTIFS(Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="J8" s="247">
         <f>IF($B8="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B8)+COUNTIFS(Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B8)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B8,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
-        <v/>
+        <v>-4480.432</v>
       </c>
       <c r="K8" s="246">
         <f>IF(MIN(N(C8),N(F8))&lt;=0,"",ROUND(MIN(N(C8),N(F8))*(N(G8)-N(D8)),8))</f>
-        <v/>
+        <v>336.81028571</v>
       </c>
       <c r="L8" s="183">
         <f>IF(MIN(N(C8),N(F8))&lt;=0,"",IF(N(D8)=0,"",ROUND((N(G8)/N(D8)-1)*100,2)))</f>
-        <v/>
+        <v>5.24</v>
       </c>
       <c r="M8" s="183">
         <f>IF(OR(ROUND(N(C8)-N(F8),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C8)&gt;N(F8),(N(E8)-N(H8))/((N(C8)-N(F8))*(1-N(Ввод!$J$19)/100)),(N(H8)-N(E8))/((N(F8)-N(C8))*(1+N(Ввод!$J$19)/100))))</f>
-        <v/>
+        <v>2992.94054776219</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -4627,186 +4691,186 @@
       </c>
       <c r="C9" s="240">
         <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>35</v>
       </c>
       <c r="D9" s="177">
         <f>IF(C9="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B9)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B9)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C9)</f>
-        <v/>
+        <v>145.922857142857</v>
       </c>
       <c r="E9" s="241">
         <f>IF(C9="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>5107.3</v>
       </c>
       <c r="F9" s="240">
         <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="G9" s="177">
         <f>IF(F9="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B9)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B9)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F9)</f>
-        <v/>
+        <v>150.2592</v>
       </c>
       <c r="H9" s="241">
         <f>IF(F9="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*"))</f>
-        <v/>
+        <v>7512.96</v>
       </c>
       <c r="I9" s="240">
         <f>IF($B9="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B9)+COUNTIFS(Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
-        <v/>
+        <v>-15</v>
       </c>
       <c r="J9" s="241">
         <f>IF($B9="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B9)+COUNTIFS(Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B9)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B9,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
-        <v/>
+        <v>2405.66</v>
       </c>
       <c r="K9" s="240">
         <f>IF(MIN(N(C9),N(F9))&lt;=0,"",ROUND(MIN(N(C9),N(F9))*(N(G9)-N(D9)),8))</f>
-        <v/>
+        <v>151.772</v>
       </c>
       <c r="L9" s="177">
         <f>IF(MIN(N(C9),N(F9))&lt;=0,"",IF(N(D9)=0,"",ROUND((N(G9)/N(D9)-1)*100,2)))</f>
-        <v/>
+        <v>2.97</v>
       </c>
       <c r="M9" s="177">
         <f>IF(OR(ROUND(N(C9)-N(F9),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C9)&gt;N(F9),(N(E9)-N(H9))/((N(C9)-N(F9))*(1-N(Ввод!$J$19)/100)),(N(H9)-N(E9))/((N(F9)-N(C9))*(1+N(Ввод!$J$19)/100))))</f>
-        <v/>
+        <v>160.057218895542</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="245" t="n"/>
-      <c r="C10" s="246">
+      <c r="C10" s="246" t="str">
         <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="D10" s="183">
+      <c r="D10" s="183" t="str">
         <f>IF(C10="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B10)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B10)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C10)</f>
         <v/>
       </c>
-      <c r="E10" s="247">
+      <c r="E10" s="247" t="str">
         <f>IF(C10="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="F10" s="246">
+      <c r="F10" s="246" t="str">
         <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="G10" s="183">
+      <c r="G10" s="183" t="str">
         <f>IF(F10="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B10)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B10)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F10)</f>
         <v/>
       </c>
-      <c r="H10" s="247">
+      <c r="H10" s="247" t="str">
         <f>IF(F10="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="I10" s="246">
+      <c r="I10" s="246" t="str">
         <f>IF($B10="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B10)+COUNTIFS(Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
         <v/>
       </c>
-      <c r="J10" s="247">
+      <c r="J10" s="247" t="str">
         <f>IF($B10="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B10)+COUNTIFS(Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B10)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B10,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
         <v/>
       </c>
-      <c r="K10" s="246">
+      <c r="K10" s="246" t="str">
         <f>IF(MIN(N(C10),N(F10))&lt;=0,"",ROUND(MIN(N(C10),N(F10))*(N(G10)-N(D10)),8))</f>
         <v/>
       </c>
-      <c r="L10" s="183">
+      <c r="L10" s="183" t="str">
         <f>IF(MIN(N(C10),N(F10))&lt;=0,"",IF(N(D10)=0,"",ROUND((N(G10)/N(D10)-1)*100,2)))</f>
         <v/>
       </c>
-      <c r="M10" s="183">
+      <c r="M10" s="183" t="str">
         <f>IF(OR(ROUND(N(C10)-N(F10),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C10)&gt;N(F10),(N(E10)-N(H10))/((N(C10)-N(F10))*(1-N(Ввод!$J$19)/100)),(N(H10)-N(E10))/((N(F10)-N(C10))*(1+N(Ввод!$J$19)/100))))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="239" t="n"/>
-      <c r="C11" s="240">
+      <c r="C11" s="240" t="str">
         <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="D11" s="177">
+      <c r="D11" s="177" t="str">
         <f>IF(C11="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B11)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B11)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C11)</f>
         <v/>
       </c>
-      <c r="E11" s="241">
+      <c r="E11" s="241" t="str">
         <f>IF(C11="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="F11" s="240">
+      <c r="F11" s="240" t="str">
         <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="G11" s="177">
+      <c r="G11" s="177" t="str">
         <f>IF(F11="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B11)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B11)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F11)</f>
         <v/>
       </c>
-      <c r="H11" s="241">
+      <c r="H11" s="241" t="str">
         <f>IF(F11="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="I11" s="240">
+      <c r="I11" s="240" t="str">
         <f>IF($B11="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B11)+COUNTIFS(Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
         <v/>
       </c>
-      <c r="J11" s="241">
+      <c r="J11" s="241" t="str">
         <f>IF($B11="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B11)+COUNTIFS(Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B11)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B11,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
         <v/>
       </c>
-      <c r="K11" s="240">
+      <c r="K11" s="240" t="str">
         <f>IF(MIN(N(C11),N(F11))&lt;=0,"",ROUND(MIN(N(C11),N(F11))*(N(G11)-N(D11)),8))</f>
         <v/>
       </c>
-      <c r="L11" s="177">
+      <c r="L11" s="177" t="str">
         <f>IF(MIN(N(C11),N(F11))&lt;=0,"",IF(N(D11)=0,"",ROUND((N(G11)/N(D11)-1)*100,2)))</f>
         <v/>
       </c>
-      <c r="M11" s="177">
+      <c r="M11" s="177" t="str">
         <f>IF(OR(ROUND(N(C11)-N(F11),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C11)&gt;N(F11),(N(E11)-N(H11))/((N(C11)-N(F11))*(1-N(Ввод!$J$19)/100)),(N(H11)-N(E11))/((N(F11)-N(C11))*(1+N(Ввод!$J$19)/100))))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="245" t="n"/>
-      <c r="C12" s="246">
+      <c r="C12" s="246" t="str">
         <f>IF(SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$F$5:$F$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$F$5:$F$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="D12" s="183">
+      <c r="D12" s="183" t="str">
         <f>IF(C12="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B12)*Лэндинг!$F$5:$F$200*Лэндинг!$G$5:$G$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B12)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$F$5:$F$200*Закрытые!$G$5:$G$200))/C12)</f>
         <v/>
       </c>
-      <c r="E12" s="247">
+      <c r="E12" s="247" t="str">
         <f>IF(C12="","",SUMIFS(Лэндинг!$H$5:$H$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$H$5:$H$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="F12" s="246">
+      <c r="F12" s="246" t="str">
         <f>IF(SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*")=0,"",SUMIFS(Лэндинг!$I$5:$I$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$I$5:$I$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="G12" s="183">
+      <c r="G12" s="183" t="str">
         <f>IF(F12="","",(SUMPRODUCT((Лэндинг!$E$5:$E$200=$B12)*Лэндинг!$I$5:$I$200*Лэндинг!$J$5:$J$200)+SUMPRODUCT((Закрытые!$E$5:$E$200=$B12)*(LEFT(Закрытые!$B$5:$B$200,2)="L-")*Закрытые!$I$5:$I$200*Закрытые!$J$5:$J$200))/F12)</f>
         <v/>
       </c>
-      <c r="H12" s="247">
+      <c r="H12" s="247" t="str">
         <f>IF(F12="","",SUMIFS(Лэндинг!$K$5:$K$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$K$5:$K$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*"))</f>
         <v/>
       </c>
-      <c r="I12" s="246">
+      <c r="I12" s="246" t="str">
         <f>IF($B12="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B12)+COUNTIFS(Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$L$5:$L$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$L$5:$L$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
         <v/>
       </c>
-      <c r="J12" s="247">
+      <c r="J12" s="247" t="str">
         <f>IF($B12="","",IF(COUNTIFS(Лэндинг!$E$5:$E$200,$B12)+COUNTIFS(Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*")=0,"",ROUND(SUMIFS(Лэндинг!$M$5:$M$200,Лэндинг!$E$5:$E$200,$B12)+SUMIFS(Закрытые!$M$5:$M$200,Закрытые!$E$5:$E$200,$B12,Закрытые!$B$5:$B$200,"L-*"),8)))</f>
         <v/>
       </c>
-      <c r="K12" s="246">
+      <c r="K12" s="246" t="str">
         <f>IF(MIN(N(C12),N(F12))&lt;=0,"",ROUND(MIN(N(C12),N(F12))*(N(G12)-N(D12)),8))</f>
         <v/>
       </c>
-      <c r="L12" s="183">
+      <c r="L12" s="183" t="str">
         <f>IF(MIN(N(C12),N(F12))&lt;=0,"",IF(N(D12)=0,"",ROUND((N(G12)/N(D12)-1)*100,2)))</f>
         <v/>
       </c>
-      <c r="M12" s="183">
+      <c r="M12" s="183" t="str">
         <f>IF(OR(ROUND(N(C12)-N(F12),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C12)&gt;N(F12),(N(E12)-N(H12))/((N(C12)-N(F12))*(1-N(Ввод!$J$19)/100)),(N(H12)-N(E12))/((N(F12)-N(C12))*(1+N(Ввод!$J$19)/100))))</f>
         <v/>
       </c>
@@ -4949,11 +5013,11 @@
       </c>
       <c r="J5" s="240">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER(H5)),ROUND(H5-F5,8),"")</f>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="K5" s="241">
         <f>IF(AND(ISNUMBER(G5),ISNUMBER(I5)),ROUND(I5-G5,8),"")</f>
-        <v/>
+        <v>-60</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -4983,11 +5047,11 @@
       </c>
       <c r="H6" s="246" t="n"/>
       <c r="I6" s="247" t="n"/>
-      <c r="J6" s="246">
+      <c r="J6" s="246" t="str">
         <f>IF(AND(ISNUMBER(F6),ISNUMBER(H6)),ROUND(H6-F6,8),"")</f>
         <v/>
       </c>
-      <c r="K6" s="247">
+      <c r="K6" s="247" t="str">
         <f>IF(AND(ISNUMBER(G6),ISNUMBER(I6)),ROUND(I6-G6,8),"")</f>
         <v/>
       </c>
@@ -5025,11 +5089,11 @@
       </c>
       <c r="J7" s="240">
         <f>IF(AND(ISNUMBER(F7),ISNUMBER(H7)),ROUND(H7-F7,8),"")</f>
-        <v/>
+        <v>-0.04</v>
       </c>
       <c r="K7" s="241">
         <f>IF(AND(ISNUMBER(G7),ISNUMBER(I7)),ROUND(I7-G7,8),"")</f>
-        <v/>
+        <v>0.0052</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -5059,11 +5123,11 @@
       </c>
       <c r="H8" s="246" t="n"/>
       <c r="I8" s="247" t="n"/>
-      <c r="J8" s="246">
+      <c r="J8" s="246" t="str">
         <f>IF(AND(ISNUMBER(F8),ISNUMBER(H8)),ROUND(H8-F8,8),"")</f>
         <v/>
       </c>
-      <c r="K8" s="247">
+      <c r="K8" s="247" t="str">
         <f>IF(AND(ISNUMBER(G8),ISNUMBER(I8)),ROUND(I8-G8,8),"")</f>
         <v/>
       </c>
@@ -5095,11 +5159,11 @@
       </c>
       <c r="H9" s="240" t="n"/>
       <c r="I9" s="241" t="n"/>
-      <c r="J9" s="240">
+      <c r="J9" s="240" t="str">
         <f>IF(AND(ISNUMBER(F9),ISNUMBER(H9)),ROUND(H9-F9,8),"")</f>
         <v/>
       </c>
-      <c r="K9" s="241">
+      <c r="K9" s="241" t="str">
         <f>IF(AND(ISNUMBER(G9),ISNUMBER(I9)),ROUND(I9-G9,8),"")</f>
         <v/>
       </c>
@@ -5137,11 +5201,11 @@
       </c>
       <c r="J10" s="246">
         <f>IF(AND(ISNUMBER(F10),ISNUMBER(H10)),ROUND(H10-F10,8),"")</f>
-        <v/>
+        <v>-1.5</v>
       </c>
       <c r="K10" s="247">
         <f>IF(AND(ISNUMBER(G10),ISNUMBER(I10)),ROUND(I10-G10,8),"")</f>
-        <v/>
+        <v>210</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -5177,11 +5241,11 @@
       </c>
       <c r="J11" s="240">
         <f>IF(AND(ISNUMBER(F11),ISNUMBER(H11)),ROUND(H11-F11,8),"")</f>
-        <v/>
+        <v>0.6</v>
       </c>
       <c r="K11" s="241">
         <f>IF(AND(ISNUMBER(G11),ISNUMBER(I11)),ROUND(I11-G11,8),"")</f>
-        <v/>
+        <v>-52</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -5211,11 +5275,11 @@
       </c>
       <c r="H12" s="246" t="n"/>
       <c r="I12" s="247" t="n"/>
-      <c r="J12" s="246">
+      <c r="J12" s="246" t="str">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER(H12)),ROUND(H12-F12,8),"")</f>
         <v/>
       </c>
-      <c r="K12" s="247">
+      <c r="K12" s="247" t="str">
         <f>IF(AND(ISNUMBER(G12),ISNUMBER(I12)),ROUND(I12-G12,8),"")</f>
         <v/>
       </c>
@@ -5340,43 +5404,43 @@
       </c>
       <c r="C5" s="240">
         <f>IF($B5="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B5,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B5),8)))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="D5" s="241">
         <f>IF($B5="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B5,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B5),8)))</f>
-        <v/>
+        <v>2360</v>
       </c>
       <c r="E5" s="240">
         <f>IF($B5="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B5,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B5),8)))</f>
-        <v/>
+        <v>4.2</v>
       </c>
       <c r="F5" s="241">
         <f>IF($B5="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B5,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B5),8)))</f>
-        <v/>
+        <v>2300</v>
       </c>
       <c r="G5" s="240">
         <f>IF($B5="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B5,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B5),8)))</f>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="H5" s="241">
         <f>IF($B5="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B5,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B5),8)))</f>
-        <v/>
-      </c>
-      <c r="I5" s="236">
+        <v>-60</v>
+      </c>
+      <c r="I5" s="236" t="str">
         <f>IF(AND(ISNUMBER(G5),ISNUMBER(H5)),IF(AND(G5&gt;0,H5&lt;0),"Buy",IF(AND(G5&lt;0,H5&gt;0),"Sell","")),"")</f>
-        <v/>
+        <v>Buy</v>
       </c>
       <c r="J5" s="177">
         <f>IF(I5="Buy",G5,IF(I5="Sell",-G5,""))</f>
-        <v/>
+        <v>0.2</v>
       </c>
       <c r="K5" s="177">
         <f>IF(AND(ISNUMBER(J5),ISNUMBER(L5),N(J5)&lt;&gt;0),ROUND(L5/J5,8),"")</f>
-        <v/>
+        <v>300</v>
       </c>
       <c r="L5" s="177">
         <f>IF(I5="Buy",-H5,IF(I5="Sell",H5,""))</f>
-        <v/>
+        <v>60</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -5387,41 +5451,41 @@
       </c>
       <c r="C6" s="246">
         <f>IF($B6="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B6,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B6),8)))</f>
-        <v/>
+        <v>0.05</v>
       </c>
       <c r="D6" s="247">
         <f>IF($B6="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B6,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B6),8)))</f>
-        <v/>
-      </c>
-      <c r="E6" s="246">
+        <v>3125</v>
+      </c>
+      <c r="E6" s="246" t="str">
         <f>IF($B6="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B6,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B6),8)))</f>
         <v/>
       </c>
-      <c r="F6" s="247">
+      <c r="F6" s="247" t="str">
         <f>IF($B6="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B6,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B6),8)))</f>
         <v/>
       </c>
-      <c r="G6" s="246">
+      <c r="G6" s="246" t="str">
         <f>IF($B6="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B6,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B6),8)))</f>
         <v/>
       </c>
-      <c r="H6" s="247">
+      <c r="H6" s="247" t="str">
         <f>IF($B6="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B6,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B6),8)))</f>
         <v/>
       </c>
-      <c r="I6" s="242">
+      <c r="I6" s="242" t="str">
         <f>IF(AND(ISNUMBER(G6),ISNUMBER(H6)),IF(AND(G6&gt;0,H6&lt;0),"Buy",IF(AND(G6&lt;0,H6&gt;0),"Sell","")),"")</f>
         <v/>
       </c>
-      <c r="J6" s="183">
+      <c r="J6" s="183" t="str">
         <f>IF(I6="Buy",G6,IF(I6="Sell",-G6,""))</f>
         <v/>
       </c>
-      <c r="K6" s="183">
+      <c r="K6" s="183" t="str">
         <f>IF(AND(ISNUMBER(J6),ISNUMBER(L6),N(J6)&lt;&gt;0),ROUND(L6/J6,8),"")</f>
         <v/>
       </c>
-      <c r="L6" s="183">
+      <c r="L6" s="183" t="str">
         <f>IF(I6="Buy",-H6,IF(I6="Sell",H6,""))</f>
         <v/>
       </c>
@@ -5434,43 +5498,43 @@
       </c>
       <c r="C7" s="240">
         <f>IF($B7="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B7,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B7),8)))</f>
-        <v/>
+        <v>3.2</v>
       </c>
       <c r="D7" s="241">
         <f>IF($B7="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B7,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B7),8)))</f>
-        <v/>
+        <v>0.1664</v>
       </c>
       <c r="E7" s="240">
         <f>IF($B7="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B7,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B7),8)))</f>
-        <v/>
+        <v>1.96</v>
       </c>
       <c r="F7" s="241">
         <f>IF($B7="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B7,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B7),8)))</f>
-        <v/>
+        <v>0.1092</v>
       </c>
       <c r="G7" s="240">
         <f>IF($B7="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B7,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B7),8)))</f>
-        <v/>
+        <v>-0.04</v>
       </c>
       <c r="H7" s="241">
         <f>IF($B7="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B7,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B7),8)))</f>
-        <v/>
-      </c>
-      <c r="I7" s="236">
+        <v>0.0052</v>
+      </c>
+      <c r="I7" s="236" t="str">
         <f>IF(AND(ISNUMBER(G7),ISNUMBER(H7)),IF(AND(G7&gt;0,H7&lt;0),"Buy",IF(AND(G7&lt;0,H7&gt;0),"Sell","")),"")</f>
-        <v/>
+        <v>Sell</v>
       </c>
       <c r="J7" s="177">
         <f>IF(I7="Buy",G7,IF(I7="Sell",-G7,""))</f>
-        <v/>
+        <v>0.04</v>
       </c>
       <c r="K7" s="177">
         <f>IF(AND(ISNUMBER(J7),ISNUMBER(L7),N(J7)&lt;&gt;0),ROUND(L7/J7,8),"")</f>
-        <v/>
+        <v>0.13</v>
       </c>
       <c r="L7" s="177">
         <f>IF(I7="Buy",-H7,IF(I7="Sell",H7,""))</f>
-        <v/>
+        <v>0.0052</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -5481,41 +5545,41 @@
       </c>
       <c r="C8" s="246">
         <f>IF($B8="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B8,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B8),8)))</f>
-        <v/>
+        <v>1.5</v>
       </c>
       <c r="D8" s="247">
         <f>IF($B8="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B8,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B8),8)))</f>
-        <v/>
-      </c>
-      <c r="E8" s="246">
+        <v>4800</v>
+      </c>
+      <c r="E8" s="246" t="str">
         <f>IF($B8="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B8,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B8),8)))</f>
         <v/>
       </c>
-      <c r="F8" s="247">
+      <c r="F8" s="247" t="str">
         <f>IF($B8="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B8,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B8),8)))</f>
         <v/>
       </c>
-      <c r="G8" s="246">
+      <c r="G8" s="246" t="str">
         <f>IF($B8="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B8,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B8),8)))</f>
         <v/>
       </c>
-      <c r="H8" s="247">
+      <c r="H8" s="247" t="str">
         <f>IF($B8="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B8,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B8),8)))</f>
         <v/>
       </c>
-      <c r="I8" s="242">
+      <c r="I8" s="242" t="str">
         <f>IF(AND(ISNUMBER(G8),ISNUMBER(H8)),IF(AND(G8&gt;0,H8&lt;0),"Buy",IF(AND(G8&lt;0,H8&gt;0),"Sell","")),"")</f>
         <v/>
       </c>
-      <c r="J8" s="183">
+      <c r="J8" s="183" t="str">
         <f>IF(I8="Buy",G8,IF(I8="Sell",-G8,""))</f>
         <v/>
       </c>
-      <c r="K8" s="183">
+      <c r="K8" s="183" t="str">
         <f>IF(AND(ISNUMBER(J8),ISNUMBER(L8),N(J8)&lt;&gt;0),ROUND(L8/J8,8),"")</f>
         <v/>
       </c>
-      <c r="L8" s="183">
+      <c r="L8" s="183" t="str">
         <f>IF(I8="Buy",-H8,IF(I8="Sell",H8,""))</f>
         <v/>
       </c>
@@ -5528,170 +5592,170 @@
       </c>
       <c r="C9" s="240">
         <f>IF($B9="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B9,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B9),8)))</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="D9" s="241">
         <f>IF($B9="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B9,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B9),8)))</f>
-        <v/>
+        <v>9715</v>
       </c>
       <c r="E9" s="240">
         <f>IF($B9="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B9,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B9),8)))</f>
-        <v/>
+        <v>41.1</v>
       </c>
       <c r="F9" s="241">
         <f>IF($B9="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B9,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B9),8)))</f>
-        <v/>
+        <v>6248</v>
       </c>
       <c r="G9" s="240">
         <f>IF($B9="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B9,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B9),8)))</f>
-        <v/>
+        <v>-0.9</v>
       </c>
       <c r="H9" s="241">
         <f>IF($B9="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B9,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B9),8)))</f>
-        <v/>
-      </c>
-      <c r="I9" s="236">
+        <v>158</v>
+      </c>
+      <c r="I9" s="236" t="str">
         <f>IF(AND(ISNUMBER(G9),ISNUMBER(H9)),IF(AND(G9&gt;0,H9&lt;0),"Buy",IF(AND(G9&lt;0,H9&gt;0),"Sell","")),"")</f>
-        <v/>
+        <v>Sell</v>
       </c>
       <c r="J9" s="177">
         <f>IF(I9="Buy",G9,IF(I9="Sell",-G9,""))</f>
-        <v/>
+        <v>0.9</v>
       </c>
       <c r="K9" s="177">
         <f>IF(AND(ISNUMBER(J9),ISNUMBER(L9),N(J9)&lt;&gt;0),ROUND(L9/J9,8),"")</f>
-        <v/>
+        <v>175.55555556</v>
       </c>
       <c r="L9" s="177">
         <f>IF(I9="Buy",-H9,IF(I9="Sell",H9,""))</f>
-        <v/>
+        <v>158</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="245" t="n"/>
-      <c r="C10" s="246">
+      <c r="C10" s="246" t="str">
         <f>IF($B10="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B10,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B10),8)))</f>
         <v/>
       </c>
-      <c r="D10" s="247">
+      <c r="D10" s="247" t="str">
         <f>IF($B10="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B10,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B10),8)))</f>
         <v/>
       </c>
-      <c r="E10" s="246">
+      <c r="E10" s="246" t="str">
         <f>IF($B10="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B10,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B10),8)))</f>
         <v/>
       </c>
-      <c r="F10" s="247">
+      <c r="F10" s="247" t="str">
         <f>IF($B10="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B10,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B10),8)))</f>
         <v/>
       </c>
-      <c r="G10" s="246">
+      <c r="G10" s="246" t="str">
         <f>IF($B10="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B10,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B10),8)))</f>
         <v/>
       </c>
-      <c r="H10" s="247">
+      <c r="H10" s="247" t="str">
         <f>IF($B10="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B10,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B10),8)))</f>
         <v/>
       </c>
-      <c r="I10" s="242">
+      <c r="I10" s="242" t="str">
         <f>IF(AND(ISNUMBER(G10),ISNUMBER(H10)),IF(AND(G10&gt;0,H10&lt;0),"Buy",IF(AND(G10&lt;0,H10&gt;0),"Sell","")),"")</f>
         <v/>
       </c>
-      <c r="J10" s="183">
+      <c r="J10" s="183" t="str">
         <f>IF(I10="Buy",G10,IF(I10="Sell",-G10,""))</f>
         <v/>
       </c>
-      <c r="K10" s="183">
+      <c r="K10" s="183" t="str">
         <f>IF(AND(ISNUMBER(J10),ISNUMBER(L10),N(J10)&lt;&gt;0),ROUND(L10/J10,8),"")</f>
         <v/>
       </c>
-      <c r="L10" s="183">
+      <c r="L10" s="183" t="str">
         <f>IF(I10="Buy",-H10,IF(I10="Sell",H10,""))</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="239" t="n"/>
-      <c r="C11" s="240">
+      <c r="C11" s="240" t="str">
         <f>IF($B11="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B11,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B11),8)))</f>
         <v/>
       </c>
-      <c r="D11" s="241">
+      <c r="D11" s="241" t="str">
         <f>IF($B11="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B11,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B11),8)))</f>
         <v/>
       </c>
-      <c r="E11" s="240">
+      <c r="E11" s="240" t="str">
         <f>IF($B11="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B11,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B11),8)))</f>
         <v/>
       </c>
-      <c r="F11" s="241">
+      <c r="F11" s="241" t="str">
         <f>IF($B11="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B11,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B11),8)))</f>
         <v/>
       </c>
-      <c r="G11" s="240">
+      <c r="G11" s="240" t="str">
         <f>IF($B11="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B11,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B11),8)))</f>
         <v/>
       </c>
-      <c r="H11" s="241">
+      <c r="H11" s="241" t="str">
         <f>IF($B11="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B11,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B11),8)))</f>
         <v/>
       </c>
-      <c r="I11" s="236">
+      <c r="I11" s="236" t="str">
         <f>IF(AND(ISNUMBER(G11),ISNUMBER(H11)),IF(AND(G11&gt;0,H11&lt;0),"Buy",IF(AND(G11&lt;0,H11&gt;0),"Sell","")),"")</f>
         <v/>
       </c>
-      <c r="J11" s="177">
+      <c r="J11" s="177" t="str">
         <f>IF(I11="Buy",G11,IF(I11="Sell",-G11,""))</f>
         <v/>
       </c>
-      <c r="K11" s="177">
+      <c r="K11" s="177" t="str">
         <f>IF(AND(ISNUMBER(J11),ISNUMBER(L11),N(J11)&lt;&gt;0),ROUND(L11/J11,8),"")</f>
         <v/>
       </c>
-      <c r="L11" s="177">
+      <c r="L11" s="177" t="str">
         <f>IF(I11="Buy",-H11,IF(I11="Sell",H11,""))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="245" t="n"/>
-      <c r="C12" s="246">
+      <c r="C12" s="246" t="str">
         <f>IF($B12="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B12,Пул!$F$5:$F$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$F$5:$F$200,Пул!$E$5:$E$200,$B12),8)))</f>
         <v/>
       </c>
-      <c r="D12" s="247">
+      <c r="D12" s="247" t="str">
         <f>IF($B12="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B12,Пул!$G$5:$G$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$G$5:$G$200,Пул!$E$5:$E$200,$B12),8)))</f>
         <v/>
       </c>
-      <c r="E12" s="246">
+      <c r="E12" s="246" t="str">
         <f>IF($B12="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B12,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$H$5:$H$200,Пул!$E$5:$E$200,$B12),8)))</f>
         <v/>
       </c>
-      <c r="F12" s="247">
+      <c r="F12" s="247" t="str">
         <f>IF($B12="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B12,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$I$5:$I$200,Пул!$E$5:$E$200,$B12),8)))</f>
         <v/>
       </c>
-      <c r="G12" s="246">
+      <c r="G12" s="246" t="str">
         <f>IF($B12="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B12,Пул!$H$5:$H$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$J$5:$J$200,Пул!$E$5:$E$200,$B12),8)))</f>
         <v/>
       </c>
-      <c r="H12" s="247">
+      <c r="H12" s="247" t="str">
         <f>IF($B12="","",IF(COUNTIFS(Пул!$E$5:$E$200,$B12,Пул!$I$5:$I$200,"&lt;&gt;")=0,"",ROUND(SUMIFS(Пул!$K$5:$K$200,Пул!$E$5:$E$200,$B12),8)))</f>
         <v/>
       </c>
-      <c r="I12" s="242">
+      <c r="I12" s="242" t="str">
         <f>IF(AND(ISNUMBER(G12),ISNUMBER(H12)),IF(AND(G12&gt;0,H12&lt;0),"Buy",IF(AND(G12&lt;0,H12&gt;0),"Sell","")),"")</f>
         <v/>
       </c>
-      <c r="J12" s="183">
+      <c r="J12" s="183" t="str">
         <f>IF(I12="Buy",G12,IF(I12="Sell",-G12,""))</f>
         <v/>
       </c>
-      <c r="K12" s="183">
+      <c r="K12" s="183" t="str">
         <f>IF(AND(ISNUMBER(J12),ISNUMBER(L12),N(J12)&lt;&gt;0),ROUND(L12/J12,8),"")</f>
         <v/>
       </c>
-      <c r="L12" s="183">
+      <c r="L12" s="183" t="str">
         <f>IF(I12="Buy",-H12,IF(I12="Sell",H12,""))</f>
         <v/>
       </c>
@@ -5865,19 +5929,19 @@
       </c>
       <c r="L5" s="240">
         <f>IF(COUNT(F5,I5)=0,"",N(F5)-N(I5))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M5" s="241">
         <f>IF(COUNT(H5,K5)=0,"",N(K5)-N(H5))</f>
-        <v/>
+        <v>25.26</v>
       </c>
       <c r="N5" s="240">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER(I5),ISNUMBER(H5),ISNUMBER(K5),F5&gt;0,I5&gt;0,H5&lt;&gt;0),ROUND(MIN(F5,I5)*(K5/I5-H5/F5),8),"")</f>
-        <v/>
+        <v>25.26</v>
       </c>
       <c r="O5" s="177">
         <f>IF(ISNUMBER(N5),ROUND(N5/(MIN(F5,I5)*H5/F5)*100,2),"")</f>
-        <v/>
+        <v>2.15</v>
       </c>
       <c r="P5" s="207" t="n"/>
       <c r="Q5" s="207" t="n"/>
@@ -5921,19 +5985,19 @@
       </c>
       <c r="L6" s="246">
         <f>IF(COUNT(F6,I6)=0,"",N(F6)-N(I6))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M6" s="247">
         <f>IF(COUNT(H6,K6)=0,"",N(K6)-N(H6))</f>
-        <v/>
+        <v>27.48</v>
       </c>
       <c r="N6" s="246">
         <f>IF(AND(ISNUMBER(F6),ISNUMBER(I6),ISNUMBER(H6),ISNUMBER(K6),F6&gt;0,I6&gt;0,H6&lt;&gt;0),ROUND(MIN(F6,I6)*(K6/I6-H6/F6),8),"")</f>
-        <v/>
+        <v>27.48</v>
       </c>
       <c r="O6" s="183">
         <f>IF(ISNUMBER(N6),ROUND(N6/(MIN(F6,I6)*H6/F6)*100,2),"")</f>
-        <v/>
+        <v>0.88</v>
       </c>
       <c r="P6" s="207" t="n"/>
       <c r="Q6" s="207" t="n"/>
@@ -5977,19 +6041,19 @@
       </c>
       <c r="L7" s="240">
         <f>IF(COUNT(F7,I7)=0,"",N(F7)-N(I7))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M7" s="241">
         <f>IF(COUNT(H7,K7)=0,"",N(K7)-N(H7))</f>
-        <v/>
+        <v>136.9</v>
       </c>
       <c r="N7" s="240">
         <f>IF(AND(ISNUMBER(F7),ISNUMBER(I7),ISNUMBER(H7),ISNUMBER(K7),F7&gt;0,I7&gt;0,H7&lt;&gt;0),ROUND(MIN(F7,I7)*(K7/I7-H7/F7),8),"")</f>
-        <v/>
+        <v>136.9</v>
       </c>
       <c r="O7" s="177">
         <f>IF(ISNUMBER(N7),ROUND(N7/(MIN(F7,I7)*H7/F7)*100,2),"")</f>
-        <v/>
+        <v>4.27</v>
       </c>
       <c r="P7" s="207" t="n"/>
       <c r="Q7" s="207" t="n"/>
@@ -6033,19 +6097,19 @@
       </c>
       <c r="L8" s="246">
         <f>IF(COUNT(F8,I8)=0,"",N(F8)-N(I8))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M8" s="247">
         <f>IF(COUNT(H8,K8)=0,"",N(K8)-N(H8))</f>
-        <v/>
+        <v>128.12</v>
       </c>
       <c r="N8" s="246">
         <f>IF(AND(ISNUMBER(F8),ISNUMBER(I8),ISNUMBER(H8),ISNUMBER(K8),F8&gt;0,I8&gt;0,H8&lt;&gt;0),ROUND(MIN(F8,I8)*(K8/I8-H8/F8),8),"")</f>
-        <v/>
+        <v>128.12</v>
       </c>
       <c r="O8" s="183">
         <f>IF(ISNUMBER(N8),ROUND(N8/(MIN(F8,I8)*H8/F8)*100,2),"")</f>
-        <v/>
+        <v>4.41</v>
       </c>
       <c r="P8" s="207" t="n"/>
       <c r="Q8" s="207" t="n"/>
@@ -6089,19 +6153,19 @@
       </c>
       <c r="L9" s="240">
         <f>IF(COUNT(F9,I9)=0,"",N(F9)-N(I9))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M9" s="241">
         <f>IF(COUNT(H9,K9)=0,"",N(K9)-N(H9))</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="N9" s="240">
         <f>IF(AND(ISNUMBER(F9),ISNUMBER(I9),ISNUMBER(H9),ISNUMBER(K9),F9&gt;0,I9&gt;0,H9&lt;&gt;0),ROUND(MIN(F9,I9)*(K9/I9-H9/F9),8),"")</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="O9" s="177">
         <f>IF(ISNUMBER(N9),ROUND(N9/(MIN(F9,I9)*H9/F9)*100,2),"")</f>
-        <v/>
+        <v>2.05</v>
       </c>
       <c r="P9" s="207" t="n"/>
       <c r="Q9" s="207" t="n"/>
@@ -6145,19 +6209,19 @@
       </c>
       <c r="L10" s="246">
         <f>IF(COUNT(F10,I10)=0,"",N(F10)-N(I10))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M10" s="247">
         <f>IF(COUNT(H10,K10)=0,"",N(K10)-N(H10))</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="N10" s="246">
         <f>IF(AND(ISNUMBER(F10),ISNUMBER(I10),ISNUMBER(H10),ISNUMBER(K10),F10&gt;0,I10&gt;0,H10&lt;&gt;0),ROUND(MIN(F10,I10)*(K10/I10-H10/F10),8),"")</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="O10" s="183">
         <f>IF(ISNUMBER(N10),ROUND(N10/(MIN(F10,I10)*H10/F10)*100,2),"")</f>
-        <v/>
+        <v>4.05</v>
       </c>
       <c r="P10" s="207" t="n"/>
       <c r="Q10" s="207" t="n"/>
@@ -6201,19 +6265,19 @@
       </c>
       <c r="L11" s="240">
         <f>IF(COUNT(F11,I11)=0,"",N(F11)-N(I11))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M11" s="241">
         <f>IF(COUNT(H11,K11)=0,"",N(K11)-N(H11))</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="N11" s="240">
         <f>IF(AND(ISNUMBER(F11),ISNUMBER(I11),ISNUMBER(H11),ISNUMBER(K11),F11&gt;0,I11&gt;0,H11&lt;&gt;0),ROUND(MIN(F11,I11)*(K11/I11-H11/F11),8),"")</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="O11" s="177">
         <f>IF(ISNUMBER(N11),ROUND(N11/(MIN(F11,I11)*H11/F11)*100,2),"")</f>
-        <v/>
+        <v>3.79</v>
       </c>
       <c r="P11" s="207" t="n"/>
       <c r="Q11" s="207" t="n"/>
@@ -6229,19 +6293,19 @@
       <c r="I12" s="246" t="n"/>
       <c r="J12" s="183" t="n"/>
       <c r="K12" s="247" t="n"/>
-      <c r="L12" s="246">
+      <c r="L12" s="246" t="str">
         <f>IF(COUNT(F12,I12)=0,"",N(F12)-N(I12))</f>
         <v/>
       </c>
-      <c r="M12" s="247">
+      <c r="M12" s="247" t="str">
         <f>IF(COUNT(H12,K12)=0,"",N(K12)-N(H12))</f>
         <v/>
       </c>
-      <c r="N12" s="246">
+      <c r="N12" s="246" t="str">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER(I12),ISNUMBER(H12),ISNUMBER(K12),F12&gt;0,I12&gt;0,H12&lt;&gt;0),ROUND(MIN(F12,I12)*(K12/I12-H12/F12),8),"")</f>
         <v/>
       </c>
-      <c r="O12" s="183">
+      <c r="O12" s="183" t="str">
         <f>IF(ISNUMBER(N12),ROUND(N12/(MIN(F12,I12)*H12/F12)*100,2),"")</f>
         <v/>
       </c>
@@ -6389,11 +6453,11 @@
       </c>
       <c r="I5" s="240">
         <f>IF(AND(AND(ISNUMBER(C5),ISNUMBER(F5),ISNUMBER(E5),ISNUMBER(H5)),C5&gt;0,F5&gt;0,E5&lt;&gt;0),ROUND(MIN(C5,F5)*(H5/F5-E5/C5),8),"")</f>
-        <v/>
+        <v>0.00065</v>
       </c>
       <c r="J5" s="241">
         <f>IF(AND(AND(ISNUMBER(C5),ISNUMBER(F5),ISNUMBER(E5),ISNUMBER(H5)),C5&gt;0,F5&gt;0,E5&lt;&gt;0),ROUND((H5/F5)/(E5/C5)*100-100,2),"")</f>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="K5" s="240" t="n">
         <v>0.00063</v>
@@ -6431,11 +6495,11 @@
       </c>
       <c r="I6" s="246">
         <f>IF(AND(AND(ISNUMBER(C6),ISNUMBER(F6),ISNUMBER(E6),ISNUMBER(H6)),C6&gt;0,F6&gt;0,E6&lt;&gt;0),ROUND(MIN(C6,F6)*(H6/F6-E6/C6),8),"")</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="J6" s="247">
         <f>IF(AND(AND(ISNUMBER(C6),ISNUMBER(F6),ISNUMBER(E6),ISNUMBER(H6)),C6&gt;0,F6&gt;0,E6&lt;&gt;0),ROUND((H6/F6)/(E6/C6)*100-100,2),"")</f>
-        <v/>
+        <v>3.23</v>
       </c>
       <c r="K6" s="246" t="n">
         <v>485</v>
@@ -6473,11 +6537,11 @@
       </c>
       <c r="I7" s="240">
         <f>IF(AND(AND(ISNUMBER(C7),ISNUMBER(F7),ISNUMBER(E7),ISNUMBER(H7)),C7&gt;0,F7&gt;0,E7&lt;&gt;0),ROUND(MIN(C7,F7)*(H7/F7-E7/C7),8),"")</f>
-        <v/>
+        <v>-120</v>
       </c>
       <c r="J7" s="241">
         <f>IF(AND(AND(ISNUMBER(C7),ISNUMBER(F7),ISNUMBER(E7),ISNUMBER(H7)),C7&gt;0,F7&gt;0,E7&lt;&gt;0),ROUND((H7/F7)/(E7/C7)*100-100,2),"")</f>
-        <v/>
+        <v>-4.14</v>
       </c>
       <c r="K7" s="240" t="n">
         <v>-125</v>
@@ -6515,11 +6579,11 @@
       </c>
       <c r="I8" s="246">
         <f>IF(AND(AND(ISNUMBER(C8),ISNUMBER(F8),ISNUMBER(E8),ISNUMBER(H8)),C8&gt;0,F8&gt;0,E8&lt;&gt;0),ROUND(MIN(C8,F8)*(H8/F8-E8/C8),8),"")</f>
-        <v/>
+        <v>180</v>
       </c>
       <c r="J8" s="247">
         <f>IF(AND(AND(ISNUMBER(C8),ISNUMBER(F8),ISNUMBER(E8),ISNUMBER(H8)),C8&gt;0,F8&gt;0,E8&lt;&gt;0),ROUND((H8/F8)/(E8/C8)*100-100,2),"")</f>
-        <v/>
+        <v>4.69</v>
       </c>
       <c r="K8" s="246" t="n">
         <v>175</v>
@@ -6557,11 +6621,11 @@
       </c>
       <c r="I9" s="240">
         <f>IF(AND(AND(ISNUMBER(C9),ISNUMBER(F9),ISNUMBER(E9),ISNUMBER(H9)),C9&gt;0,F9&gt;0,E9&lt;&gt;0),ROUND(MIN(C9,F9)*(H9/F9-E9/C9),8),"")</f>
-        <v/>
+        <v>-75</v>
       </c>
       <c r="J9" s="241">
         <f>IF(AND(AND(ISNUMBER(C9),ISNUMBER(F9),ISNUMBER(E9),ISNUMBER(H9)),C9&gt;0,F9&gt;0,E9&lt;&gt;0),ROUND((H9/F9)/(E9/C9)*100-100,2),"")</f>
-        <v/>
+        <v>-2.54</v>
       </c>
       <c r="K9" s="240" t="n">
         <v>-80</v>
@@ -6599,11 +6663,11 @@
       </c>
       <c r="I10" s="246">
         <f>IF(AND(AND(ISNUMBER(C10),ISNUMBER(F10),ISNUMBER(E10),ISNUMBER(H10)),C10&gt;0,F10&gt;0,E10&lt;&gt;0),ROUND(MIN(C10,F10)*(H10/F10-E10/C10),8),"")</f>
-        <v/>
+        <v>60</v>
       </c>
       <c r="J10" s="247">
         <f>IF(AND(AND(ISNUMBER(C10),ISNUMBER(F10),ISNUMBER(E10),ISNUMBER(H10)),C10&gt;0,F10&gt;0,E10&lt;&gt;0),ROUND((H10/F10)/(E10/C10)*100-100,2),"")</f>
-        <v/>
+        <v>0.96</v>
       </c>
       <c r="K10" s="246" t="n">
         <v>55</v>
@@ -6641,11 +6705,11 @@
       </c>
       <c r="I11" s="240">
         <f>IF(AND(AND(ISNUMBER(C11),ISNUMBER(F11),ISNUMBER(E11),ISNUMBER(H11)),C11&gt;0,F11&gt;0,E11&lt;&gt;0),ROUND(MIN(C11,F11)*(H11/F11-E11/C11),8),"")</f>
-        <v/>
+        <v>0.00096</v>
       </c>
       <c r="J11" s="241">
         <f>IF(AND(AND(ISNUMBER(C11),ISNUMBER(F11),ISNUMBER(E11),ISNUMBER(H11)),C11&gt;0,F11&gt;0,E11&lt;&gt;0),ROUND((H11/F11)/(E11/C11)*100-100,2),"")</f>
-        <v/>
+        <v>2.32</v>
       </c>
       <c r="K11" s="240" t="n">
         <v>0.00092</v>
@@ -6683,11 +6747,11 @@
       </c>
       <c r="I12" s="246">
         <f>IF(AND(AND(ISNUMBER(C12),ISNUMBER(F12),ISNUMBER(E12),ISNUMBER(H12)),C12&gt;0,F12&gt;0,E12&lt;&gt;0),ROUND(MIN(C12,F12)*(H12/F12-E12/C12),8),"")</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="J12" s="247">
         <f>IF(AND(AND(ISNUMBER(C12),ISNUMBER(F12),ISNUMBER(E12),ISNUMBER(H12)),C12&gt;0,F12&gt;0,E12&lt;&gt;0),ROUND((H12/F12)/(E12/C12)*100-100,2),"")</f>
-        <v/>
+        <v>3.52</v>
       </c>
       <c r="K12" s="246" t="n">
         <v>70</v>

--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -1482,7 +1482,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1496,6 +1496,22 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFDE9D9"/>
           <bgColor rgb="FFFDE9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFDF3"/>
+          <bgColor rgb="FFFFFDF3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11739,6 +11755,14 @@
       <formula>AND($B5&lt;&gt;"",COUNTIF(Закрытые!$B$5:$B$300,$B5)&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B5:G300 I5:J300 L5:N300">
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="3">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
@@ -21416,6 +21440,14 @@
   <conditionalFormatting sqref="B5:N300">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($B5&lt;&gt;"",COUNTIF(Закрытые!$B$5:$B$300,$B5)&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:G300 I5:J300 L5:N300">
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="3">
+      <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31426,6 +31458,14 @@
       <formula>AND($B5&lt;&gt;"",COUNTIF(Торговля!$B$5:$B$300,$B5)+COUNTIF(Лэндинг!$B$5:$B$300,$B5)&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B5:O300">
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="3">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>

--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -31570,43 +31570,52 @@
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="239" t="inlineStr">
         <is>
-          <t>ETH/BTC</t>
+          <t>BNB/USDT</t>
         </is>
       </c>
-      <c r="C5" s="240" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D5" s="177" t="n">
-        <v>0.0521</v>
-      </c>
-      <c r="E5" s="241" t="n">
-        <v>0.02605</v>
-      </c>
-      <c r="F5" s="240" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="177" t="n">
-        <v>0.0534</v>
-      </c>
-      <c r="H5" s="241" t="n">
-        <v>0.0267</v>
+      <c r="C5" s="240">
+        <f>IF($B5="","",IF(SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B5)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B5)=0,"",SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B5)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B5)))</f>
+        <v>3.5</v>
+      </c>
+      <c r="D5" s="177">
+        <f>IF(C5="","",E5/C5)</f>
+        <v>585.668571428572</v>
+      </c>
+      <c r="E5" s="241">
+        <f>IF(C5="","",SUMIFS('ИТОГО Торговля'!$E$5:$E$200,'ИТОГО Торговля'!$B$5:$B$200,$B5)+SUMIFS('ИТОГО Лэндинг'!$E$5:$E$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B5))</f>
+        <v>2049.84</v>
+      </c>
+      <c r="F5" s="240">
+        <f>IF($B5="","",IF(SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B5)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B5)=0,"",SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B5)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B5)))</f>
+        <v>9.5</v>
+      </c>
+      <c r="G5" s="177">
+        <f>IF(F5="","",H5/F5)</f>
+        <v>598.515789473684</v>
+      </c>
+      <c r="H5" s="241">
+        <f>IF(F5="","",SUMIFS('ИТОГО Торговля'!$H$5:$H$200,'ИТОГО Торговля'!$B$5:$B$200,$B5)+SUMIFS('ИТОГО Лэндинг'!$H$5:$H$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B5))</f>
+        <v>5685.9</v>
       </c>
       <c r="I5" s="240">
-        <f>IF(AND(AND(ISNUMBER(C5),ISNUMBER(F5),ISNUMBER(E5),ISNUMBER(H5)),C5&gt;0,F5&gt;0,E5&lt;&gt;0),ROUND(MIN(C5,F5)*(H5/F5-E5/C5),8),"")</f>
-        <v>0.00065</v>
+        <f>IF($B5="","",IF(AND(C5="",F5=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$I$5:$I$200,'ИТОГО Торговля'!$B$5:$B$200,$B5)+SUMIFS('ИТОГО Лэндинг'!$I$5:$I$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B5),8)))</f>
+        <v>-6</v>
       </c>
       <c r="J5" s="241">
-        <f>IF(AND(AND(ISNUMBER(C5),ISNUMBER(F5),ISNUMBER(E5),ISNUMBER(H5)),C5&gt;0,F5&gt;0,E5&lt;&gt;0),ROUND((H5/F5)/(E5/C5)*100-100,2),"")</f>
-        <v>2.5</v>
-      </c>
-      <c r="K5" s="240" t="n">
-        <v>0.00063</v>
-      </c>
-      <c r="L5" s="177" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="M5" s="177" t="n">
-        <v>0.0522</v>
+        <f>IF($B5="","",IF(AND(C5="",F5=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$J$5:$J$200,'ИТОГО Торговля'!$B$5:$B$200,$B5)+SUMIFS('ИТОГО Лэндинг'!$J$5:$J$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B5),8)))</f>
+        <v>3636.06</v>
+      </c>
+      <c r="K5" s="240">
+        <f>IF(MIN(N(C5),N(F5))&lt;=0,"",ROUND(MIN(N(C5),N(F5))*(N(G5)-N(D5)),8))</f>
+        <v>44.96526316</v>
+      </c>
+      <c r="L5" s="177">
+        <f>IF(MIN(N(C5),N(F5))&lt;=0,"",IF(N(D5)=0,"",ROUND((N(G5)/N(D5)-1)*100,2)))</f>
+        <v>2.19</v>
+      </c>
+      <c r="M5" s="177">
+        <f>IF(OR(ROUND(N(C5)-N(F5),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C5)&gt;N(F5),(N(E5)-N(H5))/((N(C5)-N(F5))*(1-N(Ввод!$J$19)/100)),(N(H5)-N(E5))/((N(F5)-N(C5))*(1+N(Ввод!$J$19)/100))))</f>
+        <v>604.800399201597</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -31615,82 +31624,100 @@
           <t>BTC/USDT</t>
         </is>
       </c>
-      <c r="C6" s="246" t="n">
+      <c r="C6" s="246">
+        <f>IF($B6="","",IF(SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B6)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B6)=0,"",SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B6)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B6)))</f>
         <v>0.25</v>
       </c>
-      <c r="D6" s="183" t="n">
-        <v>62000</v>
-      </c>
-      <c r="E6" s="247" t="n">
-        <v>15500</v>
-      </c>
-      <c r="F6" s="246" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G6" s="183" t="n">
-        <v>64000</v>
-      </c>
-      <c r="H6" s="247" t="n">
-        <v>16000</v>
+      <c r="D6" s="183">
+        <f>IF(C6="","",E6/C6)</f>
+        <v>62164.08</v>
+      </c>
+      <c r="E6" s="247">
+        <f>IF(C6="","",SUMIFS('ИТОГО Торговля'!$E$5:$E$200,'ИТОГО Торговля'!$B$5:$B$200,$B6)+SUMIFS('ИТОГО Лэндинг'!$E$5:$E$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B6))</f>
+        <v>15541.02</v>
+      </c>
+      <c r="F6" s="246">
+        <f>IF($B6="","",IF(SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B6)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B6)=0,"",SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B6)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B6)))</f>
+        <v>0.05</v>
+      </c>
+      <c r="G6" s="183">
+        <f>IF(F6="","",H6/F6)</f>
+        <v>62874</v>
+      </c>
+      <c r="H6" s="247">
+        <f>IF(F6="","",SUMIFS('ИТОГО Торговля'!$H$5:$H$200,'ИТОГО Торговля'!$B$5:$B$200,$B6)+SUMIFS('ИТОГО Лэндинг'!$H$5:$H$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B6))</f>
+        <v>3143.7</v>
       </c>
       <c r="I6" s="246">
-        <f>IF(AND(AND(ISNUMBER(C6),ISNUMBER(F6),ISNUMBER(E6),ISNUMBER(H6)),C6&gt;0,F6&gt;0,E6&lt;&gt;0),ROUND(MIN(C6,F6)*(H6/F6-E6/C6),8),"")</f>
-        <v>500</v>
+        <f>IF($B6="","",IF(AND(C6="",F6=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$I$5:$I$200,'ИТОГО Торговля'!$B$5:$B$200,$B6)+SUMIFS('ИТОГО Лэндинг'!$I$5:$I$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B6),8)))</f>
+        <v>0.2</v>
       </c>
       <c r="J6" s="247">
-        <f>IF(AND(AND(ISNUMBER(C6),ISNUMBER(F6),ISNUMBER(E6),ISNUMBER(H6)),C6&gt;0,F6&gt;0,E6&lt;&gt;0),ROUND((H6/F6)/(E6/C6)*100-100,2),"")</f>
-        <v>3.23</v>
-      </c>
-      <c r="K6" s="246" t="n">
-        <v>485</v>
-      </c>
-      <c r="L6" s="183" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="M6" s="183" t="n">
-        <v>62155</v>
+        <f>IF($B6="","",IF(AND(C6="",F6=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$J$5:$J$200,'ИТОГО Торговля'!$B$5:$B$200,$B6)+SUMIFS('ИТОГО Лэндинг'!$J$5:$J$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B6),8)))</f>
+        <v>-12397.32</v>
+      </c>
+      <c r="K6" s="246">
+        <f>IF(MIN(N(C6),N(F6))&lt;=0,"",ROUND(MIN(N(C6),N(F6))*(N(G6)-N(D6)),8))</f>
+        <v>35.496</v>
+      </c>
+      <c r="L6" s="183">
+        <f>IF(MIN(N(C6),N(F6))&lt;=0,"",IF(N(D6)=0,"",ROUND((N(G6)/N(D6)-1)*100,2)))</f>
+        <v>1.14</v>
+      </c>
+      <c r="M6" s="183">
+        <f>IF(OR(ROUND(N(C6)-N(F6),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C6)&gt;N(F6),(N(E6)-N(H6))/((N(C6)-N(F6))*(1-N(Ввод!$J$19)/100)),(N(H6)-N(E6))/((N(F6)-N(C6))*(1+N(Ввод!$J$19)/100))))</f>
+        <v>62110.8216432866</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="B7" s="239" t="inlineStr">
         <is>
-          <t>SOL/USDT</t>
+          <t>ETH/BTC</t>
         </is>
       </c>
-      <c r="C7" s="240" t="n">
-        <v>20</v>
-      </c>
-      <c r="D7" s="177" t="n">
-        <v>145</v>
-      </c>
-      <c r="E7" s="241" t="n">
-        <v>2900</v>
-      </c>
-      <c r="F7" s="240" t="n">
-        <v>20</v>
-      </c>
-      <c r="G7" s="177" t="n">
-        <v>139</v>
-      </c>
-      <c r="H7" s="241" t="n">
-        <v>2780</v>
+      <c r="C7" s="240" t="str">
+        <f>IF($B7="","",IF(SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B7)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B7)=0,"",SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B7)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B7)))</f>
+        <v/>
+      </c>
+      <c r="D7" s="177" t="str">
+        <f>IF(C7="","",E7/C7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="241" t="str">
+        <f>IF(C7="","",SUMIFS('ИТОГО Торговля'!$E$5:$E$200,'ИТОГО Торговля'!$B$5:$B$200,$B7)+SUMIFS('ИТОГО Лэндинг'!$E$5:$E$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B7))</f>
+        <v/>
+      </c>
+      <c r="F7" s="240">
+        <f>IF($B7="","",IF(SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B7)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B7)=0,"",SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B7)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B7)))</f>
+        <v>3</v>
+      </c>
+      <c r="G7" s="177">
+        <f>IF(F7="","",H7/F7)</f>
+        <v>0.052395</v>
+      </c>
+      <c r="H7" s="241">
+        <f>IF(F7="","",SUMIFS('ИТОГО Торговля'!$H$5:$H$200,'ИТОГО Торговля'!$B$5:$B$200,$B7)+SUMIFS('ИТОГО Лэндинг'!$H$5:$H$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B7))</f>
+        <v>0.157185</v>
       </c>
       <c r="I7" s="240">
-        <f>IF(AND(AND(ISNUMBER(C7),ISNUMBER(F7),ISNUMBER(E7),ISNUMBER(H7)),C7&gt;0,F7&gt;0,E7&lt;&gt;0),ROUND(MIN(C7,F7)*(H7/F7-E7/C7),8),"")</f>
-        <v>-120</v>
+        <f>IF($B7="","",IF(AND(C7="",F7=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$I$5:$I$200,'ИТОГО Торговля'!$B$5:$B$200,$B7)+SUMIFS('ИТОГО Лэндинг'!$I$5:$I$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B7),8)))</f>
+        <v>-3</v>
       </c>
       <c r="J7" s="241">
-        <f>IF(AND(AND(ISNUMBER(C7),ISNUMBER(F7),ISNUMBER(E7),ISNUMBER(H7)),C7&gt;0,F7&gt;0,E7&lt;&gt;0),ROUND((H7/F7)/(E7/C7)*100-100,2),"")</f>
-        <v>-4.14</v>
-      </c>
-      <c r="K7" s="240" t="n">
-        <v>-125</v>
-      </c>
-      <c r="L7" s="177" t="n">
-        <v>-4.31</v>
-      </c>
-      <c r="M7" s="177" t="n">
-        <v>145.3</v>
+        <f>IF($B7="","",IF(AND(C7="",F7=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$J$5:$J$200,'ИТОГО Торговля'!$B$5:$B$200,$B7)+SUMIFS('ИТОГО Лэндинг'!$J$5:$J$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B7),8)))</f>
+        <v>0.157185</v>
+      </c>
+      <c r="K7" s="240" t="str">
+        <f>IF(MIN(N(C7),N(F7))&lt;=0,"",ROUND(MIN(N(C7),N(F7))*(N(G7)-N(D7)),8))</f>
+        <v/>
+      </c>
+      <c r="L7" s="177" t="str">
+        <f>IF(MIN(N(C7),N(F7))&lt;=0,"",IF(N(D7)=0,"",ROUND((N(G7)/N(D7)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M7" s="177">
+        <f>IF(OR(ROUND(N(C7)-N(F7),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C7)&gt;N(F7),(N(E7)-N(H7))/((N(C7)-N(F7))*(1-N(Ввод!$J$19)/100)),(N(H7)-N(E7))/((N(F7)-N(C7))*(1+N(Ввод!$J$19)/100))))</f>
+        <v>0.0522904191616766</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -31699,208 +31726,241 @@
           <t>ETH/USDT</t>
         </is>
       </c>
-      <c r="C8" s="246" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D8" s="183" t="n">
-        <v>3200</v>
-      </c>
-      <c r="E8" s="247" t="n">
-        <v>3840</v>
-      </c>
-      <c r="F8" s="246" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G8" s="183" t="n">
-        <v>3350</v>
-      </c>
-      <c r="H8" s="247" t="n">
-        <v>4020</v>
+      <c r="C8" s="246">
+        <f>IF($B8="","",IF(SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B8)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B8)=0,"",SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B8)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B8)))</f>
+        <v>7.5</v>
+      </c>
+      <c r="D8" s="183">
+        <f>IF(C8="","",E8/C8)</f>
+        <v>3210.9152</v>
+      </c>
+      <c r="E8" s="247">
+        <f>IF(C8="","",SUMIFS('ИТОГО Торговля'!$E$5:$E$200,'ИТОГО Торговля'!$B$5:$B$200,$B8)+SUMIFS('ИТОГО Лэндинг'!$E$5:$E$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B8))</f>
+        <v>24081.864</v>
+      </c>
+      <c r="F8" s="246">
+        <f>IF($B8="","",IF(SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B8)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B8)=0,"",SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B8)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B8)))</f>
+        <v>4.5</v>
+      </c>
+      <c r="G8" s="183">
+        <f>IF(F8="","",H8/F8)</f>
+        <v>3376.2</v>
+      </c>
+      <c r="H8" s="247">
+        <f>IF(F8="","",SUMIFS('ИТОГО Торговля'!$H$5:$H$200,'ИТОГО Торговля'!$B$5:$B$200,$B8)+SUMIFS('ИТОГО Лэндинг'!$H$5:$H$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B8))</f>
+        <v>15192.9</v>
       </c>
       <c r="I8" s="246">
-        <f>IF(AND(AND(ISNUMBER(C8),ISNUMBER(F8),ISNUMBER(E8),ISNUMBER(H8)),C8&gt;0,F8&gt;0,E8&lt;&gt;0),ROUND(MIN(C8,F8)*(H8/F8-E8/C8),8),"")</f>
-        <v>180</v>
+        <f>IF($B8="","",IF(AND(C8="",F8=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$I$5:$I$200,'ИТОГО Торговля'!$B$5:$B$200,$B8)+SUMIFS('ИТОГО Лэндинг'!$I$5:$I$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B8),8)))</f>
+        <v>3</v>
       </c>
       <c r="J8" s="247">
-        <f>IF(AND(AND(ISNUMBER(C8),ISNUMBER(F8),ISNUMBER(E8),ISNUMBER(H8)),C8&gt;0,F8&gt;0,E8&lt;&gt;0),ROUND((H8/F8)/(E8/C8)*100-100,2),"")</f>
-        <v>4.69</v>
-      </c>
-      <c r="K8" s="246" t="n">
-        <v>175</v>
-      </c>
-      <c r="L8" s="183" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="M8" s="183" t="n">
-        <v>3203.84</v>
+        <f>IF($B8="","",IF(AND(C8="",F8=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$J$5:$J$200,'ИТОГО Торговля'!$B$5:$B$200,$B8)+SUMIFS('ИТОГО Лэндинг'!$J$5:$J$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B8),8)))</f>
+        <v>-8888.964</v>
+      </c>
+      <c r="K8" s="246">
+        <f>IF(MIN(N(C8),N(F8))&lt;=0,"",ROUND(MIN(N(C8),N(F8))*(N(G8)-N(D8)),8))</f>
+        <v>743.7816</v>
+      </c>
+      <c r="L8" s="183">
+        <f>IF(MIN(N(C8),N(F8))&lt;=0,"",IF(N(D8)=0,"",ROUND((N(G8)/N(D8)-1)*100,2)))</f>
+        <v>5.15</v>
+      </c>
+      <c r="M8" s="183">
+        <f>IF(OR(ROUND(N(C8)-N(F8),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C8)&gt;N(F8),(N(E8)-N(H8))/((N(C8)-N(F8))*(1-N(Ввод!$J$19)/100)),(N(H8)-N(E8))/((N(F8)-N(C8))*(1+N(Ввод!$J$19)/100))))</f>
+        <v>2968.92585170341</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="239" t="inlineStr">
         <is>
-          <t>BNB/USDT</t>
-        </is>
-      </c>
-      <c r="C9" s="240" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="177" t="n">
-        <v>590</v>
-      </c>
-      <c r="E9" s="241" t="n">
-        <v>2950</v>
-      </c>
-      <c r="F9" s="240" t="n">
-        <v>5</v>
-      </c>
-      <c r="G9" s="177" t="n">
-        <v>575</v>
-      </c>
-      <c r="H9" s="241" t="n">
-        <v>2875</v>
-      </c>
-      <c r="I9" s="240">
-        <f>IF(AND(AND(ISNUMBER(C9),ISNUMBER(F9),ISNUMBER(E9),ISNUMBER(H9)),C9&gt;0,F9&gt;0,E9&lt;&gt;0),ROUND(MIN(C9,F9)*(H9/F9-E9/C9),8),"")</f>
-        <v>-75</v>
-      </c>
-      <c r="J9" s="241">
-        <f>IF(AND(AND(ISNUMBER(C9),ISNUMBER(F9),ISNUMBER(E9),ISNUMBER(H9)),C9&gt;0,F9&gt;0,E9&lt;&gt;0),ROUND((H9/F9)/(E9/C9)*100-100,2),"")</f>
-        <v>-2.54</v>
-      </c>
-      <c r="K9" s="240" t="n">
-        <v>-80</v>
-      </c>
-      <c r="L9" s="177" t="n">
-        <v>-2.71</v>
-      </c>
-      <c r="M9" s="177" t="n">
-        <v>590.6</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="245" t="inlineStr">
-        <is>
-          <t>BTC/USDT</t>
-        </is>
-      </c>
-      <c r="C10" s="246" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D10" s="183" t="n">
-        <v>62500</v>
-      </c>
-      <c r="E10" s="247" t="n">
-        <v>6250</v>
-      </c>
-      <c r="F10" s="246" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G10" s="183" t="n">
-        <v>63100</v>
-      </c>
-      <c r="H10" s="247" t="n">
-        <v>6310</v>
-      </c>
-      <c r="I10" s="246">
-        <f>IF(AND(AND(ISNUMBER(C10),ISNUMBER(F10),ISNUMBER(E10),ISNUMBER(H10)),C10&gt;0,F10&gt;0,E10&lt;&gt;0),ROUND(MIN(C10,F10)*(H10/F10-E10/C10),8),"")</f>
-        <v>60</v>
-      </c>
-      <c r="J10" s="247">
-        <f>IF(AND(AND(ISNUMBER(C10),ISNUMBER(F10),ISNUMBER(E10),ISNUMBER(H10)),C10&gt;0,F10&gt;0,E10&lt;&gt;0),ROUND((H10/F10)/(E10/C10)*100-100,2),"")</f>
-        <v>0.96</v>
-      </c>
-      <c r="K10" s="246" t="n">
-        <v>55</v>
-      </c>
-      <c r="L10" s="183" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="M10" s="183" t="n">
-        <v>62512.5</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="239" t="inlineStr">
-        <is>
-          <t>ETH/BTC</t>
-        </is>
-      </c>
-      <c r="C11" s="240" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D11" s="177" t="n">
-        <v>0.0518</v>
-      </c>
-      <c r="E11" s="241" t="n">
-        <v>0.04144</v>
-      </c>
-      <c r="F11" s="240" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G11" s="177" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="H11" s="241" t="n">
-        <v>0.0424</v>
-      </c>
-      <c r="I11" s="240">
-        <f>IF(AND(AND(ISNUMBER(C11),ISNUMBER(F11),ISNUMBER(E11),ISNUMBER(H11)),C11&gt;0,F11&gt;0,E11&lt;&gt;0),ROUND(MIN(C11,F11)*(H11/F11-E11/C11),8),"")</f>
-        <v>0.00096</v>
-      </c>
-      <c r="J11" s="241">
-        <f>IF(AND(AND(ISNUMBER(C11),ISNUMBER(F11),ISNUMBER(E11),ISNUMBER(H11)),C11&gt;0,F11&gt;0,E11&lt;&gt;0),ROUND((H11/F11)/(E11/C11)*100-100,2),"")</f>
-        <v>2.32</v>
-      </c>
-      <c r="K11" s="240" t="n">
-        <v>0.00092</v>
-      </c>
-      <c r="L11" s="177" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="M11" s="177" t="n">
-        <v>0.05185</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="245" t="inlineStr">
-        <is>
           <t>SOL/USDT</t>
         </is>
       </c>
-      <c r="C12" s="246" t="n">
-        <v>15</v>
-      </c>
-      <c r="D12" s="183" t="n">
-        <v>142</v>
-      </c>
-      <c r="E12" s="247" t="n">
-        <v>2130</v>
-      </c>
-      <c r="F12" s="246" t="n">
-        <v>15</v>
-      </c>
-      <c r="G12" s="183" t="n">
-        <v>147</v>
-      </c>
-      <c r="H12" s="247" t="n">
-        <v>2205</v>
-      </c>
-      <c r="I12" s="246">
-        <f>IF(AND(AND(ISNUMBER(C12),ISNUMBER(F12),ISNUMBER(E12),ISNUMBER(H12)),C12&gt;0,F12&gt;0,E12&lt;&gt;0),ROUND(MIN(C12,F12)*(H12/F12-E12/C12),8),"")</f>
-        <v>75</v>
-      </c>
-      <c r="J12" s="247">
-        <f>IF(AND(AND(ISNUMBER(C12),ISNUMBER(F12),ISNUMBER(E12),ISNUMBER(H12)),C12&gt;0,F12&gt;0,E12&lt;&gt;0),ROUND((H12/F12)/(E12/C12)*100-100,2),"")</f>
-        <v>3.52</v>
-      </c>
-      <c r="K12" s="246" t="n">
-        <v>70</v>
-      </c>
-      <c r="L12" s="183" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="M12" s="183" t="n">
-        <v>142.28</v>
+      <c r="C9" s="240">
+        <f>IF($B9="","",IF(SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B9)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B9)=0,"",SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B9)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B9)))</f>
+        <v>80</v>
+      </c>
+      <c r="D9" s="177">
+        <f>IF(C9="","",E9/C9)</f>
+        <v>145.88</v>
+      </c>
+      <c r="E9" s="241">
+        <f>IF(C9="","",SUMIFS('ИТОГО Торговля'!$E$5:$E$200,'ИТОГО Торговля'!$B$5:$B$200,$B9)+SUMIFS('ИТОГО Лэндинг'!$E$5:$E$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B9))</f>
+        <v>11670.4</v>
+      </c>
+      <c r="F9" s="240">
+        <f>IF($B9="","",IF(SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B9)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B9)=0,"",SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B9)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B9)))</f>
+        <v>110</v>
+      </c>
+      <c r="G9" s="177">
+        <f>IF(F9="","",H9/F9)</f>
+        <v>150.498545454545</v>
+      </c>
+      <c r="H9" s="241">
+        <f>IF(F9="","",SUMIFS('ИТОГО Торговля'!$H$5:$H$200,'ИТОГО Торговля'!$B$5:$B$200,$B9)+SUMIFS('ИТОГО Лэндинг'!$H$5:$H$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B9))</f>
+        <v>16554.84</v>
+      </c>
+      <c r="I9" s="240">
+        <f>IF($B9="","",IF(AND(C9="",F9=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$I$5:$I$200,'ИТОГО Торговля'!$B$5:$B$200,$B9)+SUMIFS('ИТОГО Лэндинг'!$I$5:$I$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B9),8)))</f>
+        <v>-30</v>
+      </c>
+      <c r="J9" s="241">
+        <f>IF($B9="","",IF(AND(C9="",F9=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$J$5:$J$200,'ИТОГО Торговля'!$B$5:$B$200,$B9)+SUMIFS('ИТОГО Лэндинг'!$J$5:$J$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B9),8)))</f>
+        <v>4884.44</v>
+      </c>
+      <c r="K9" s="240">
+        <f>IF(MIN(N(C9),N(F9))&lt;=0,"",ROUND(MIN(N(C9),N(F9))*(N(G9)-N(D9)),8))</f>
+        <v>369.48363636</v>
+      </c>
+      <c r="L9" s="177">
+        <f>IF(MIN(N(C9),N(F9))&lt;=0,"",IF(N(D9)=0,"",ROUND((N(G9)/N(D9)-1)*100,2)))</f>
+        <v>3.17</v>
+      </c>
+      <c r="M9" s="177">
+        <f>IF(OR(ROUND(N(C9)-N(F9),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C9)&gt;N(F9),(N(E9)-N(H9))/((N(C9)-N(F9))*(1-N(Ввод!$J$19)/100)),(N(H9)-N(E9))/((N(F9)-N(C9))*(1+N(Ввод!$J$19)/100))))</f>
+        <v>162.489687292082</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="245"/>
+      <c r="C10" s="246" t="str">
+        <f>IF($B10="","",IF(SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B10)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B10)=0,"",SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B10)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B10)))</f>
+        <v/>
+      </c>
+      <c r="D10" s="183" t="str">
+        <f>IF(C10="","",E10/C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="247" t="str">
+        <f>IF(C10="","",SUMIFS('ИТОГО Торговля'!$E$5:$E$200,'ИТОГО Торговля'!$B$5:$B$200,$B10)+SUMIFS('ИТОГО Лэндинг'!$E$5:$E$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B10))</f>
+        <v/>
+      </c>
+      <c r="F10" s="246" t="str">
+        <f>IF($B10="","",IF(SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B10)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B10)=0,"",SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B10)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B10)))</f>
+        <v/>
+      </c>
+      <c r="G10" s="183" t="str">
+        <f>IF(F10="","",H10/F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="247" t="str">
+        <f>IF(F10="","",SUMIFS('ИТОГО Торговля'!$H$5:$H$200,'ИТОГО Торговля'!$B$5:$B$200,$B10)+SUMIFS('ИТОГО Лэндинг'!$H$5:$H$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B10))</f>
+        <v/>
+      </c>
+      <c r="I10" s="246" t="str">
+        <f>IF($B10="","",IF(AND(C10="",F10=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$I$5:$I$200,'ИТОГО Торговля'!$B$5:$B$200,$B10)+SUMIFS('ИТОГО Лэндинг'!$I$5:$I$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B10),8)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="247" t="str">
+        <f>IF($B10="","",IF(AND(C10="",F10=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$J$5:$J$200,'ИТОГО Торговля'!$B$5:$B$200,$B10)+SUMIFS('ИТОГО Лэндинг'!$J$5:$J$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B10),8)))</f>
+        <v/>
+      </c>
+      <c r="K10" s="246" t="str">
+        <f>IF(MIN(N(C10),N(F10))&lt;=0,"",ROUND(MIN(N(C10),N(F10))*(N(G10)-N(D10)),8))</f>
+        <v/>
+      </c>
+      <c r="L10" s="183" t="str">
+        <f>IF(MIN(N(C10),N(F10))&lt;=0,"",IF(N(D10)=0,"",ROUND((N(G10)/N(D10)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M10" s="183" t="str">
+        <f>IF(OR(ROUND(N(C10)-N(F10),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C10)&gt;N(F10),(N(E10)-N(H10))/((N(C10)-N(F10))*(1-N(Ввод!$J$19)/100)),(N(H10)-N(E10))/((N(F10)-N(C10))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="239"/>
+      <c r="C11" s="240" t="str">
+        <f>IF($B11="","",IF(SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B11)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B11)=0,"",SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B11)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B11)))</f>
+        <v/>
+      </c>
+      <c r="D11" s="177" t="str">
+        <f>IF(C11="","",E11/C11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="241" t="str">
+        <f>IF(C11="","",SUMIFS('ИТОГО Торговля'!$E$5:$E$200,'ИТОГО Торговля'!$B$5:$B$200,$B11)+SUMIFS('ИТОГО Лэндинг'!$E$5:$E$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B11))</f>
+        <v/>
+      </c>
+      <c r="F11" s="240" t="str">
+        <f>IF($B11="","",IF(SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B11)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B11)=0,"",SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B11)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B11)))</f>
+        <v/>
+      </c>
+      <c r="G11" s="177" t="str">
+        <f>IF(F11="","",H11/F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="241" t="str">
+        <f>IF(F11="","",SUMIFS('ИТОГО Торговля'!$H$5:$H$200,'ИТОГО Торговля'!$B$5:$B$200,$B11)+SUMIFS('ИТОГО Лэндинг'!$H$5:$H$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B11))</f>
+        <v/>
+      </c>
+      <c r="I11" s="240" t="str">
+        <f>IF($B11="","",IF(AND(C11="",F11=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$I$5:$I$200,'ИТОГО Торговля'!$B$5:$B$200,$B11)+SUMIFS('ИТОГО Лэндинг'!$I$5:$I$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B11),8)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="241" t="str">
+        <f>IF($B11="","",IF(AND(C11="",F11=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$J$5:$J$200,'ИТОГО Торговля'!$B$5:$B$200,$B11)+SUMIFS('ИТОГО Лэндинг'!$J$5:$J$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B11),8)))</f>
+        <v/>
+      </c>
+      <c r="K11" s="240" t="str">
+        <f>IF(MIN(N(C11),N(F11))&lt;=0,"",ROUND(MIN(N(C11),N(F11))*(N(G11)-N(D11)),8))</f>
+        <v/>
+      </c>
+      <c r="L11" s="177" t="str">
+        <f>IF(MIN(N(C11),N(F11))&lt;=0,"",IF(N(D11)=0,"",ROUND((N(G11)/N(D11)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M11" s="177" t="str">
+        <f>IF(OR(ROUND(N(C11)-N(F11),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C11)&gt;N(F11),(N(E11)-N(H11))/((N(C11)-N(F11))*(1-N(Ввод!$J$19)/100)),(N(H11)-N(E11))/((N(F11)-N(C11))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="245"/>
+      <c r="C12" s="246" t="str">
+        <f>IF($B12="","",IF(SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B12)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B12)=0,"",SUMIFS('ИТОГО Торговля'!$C$5:$C$200,'ИТОГО Торговля'!$B$5:$B$200,$B12)+SUMIFS('ИТОГО Лэндинг'!$C$5:$C$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B12)))</f>
+        <v/>
+      </c>
+      <c r="D12" s="183" t="str">
+        <f>IF(C12="","",E12/C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="247" t="str">
+        <f>IF(C12="","",SUMIFS('ИТОГО Торговля'!$E$5:$E$200,'ИТОГО Торговля'!$B$5:$B$200,$B12)+SUMIFS('ИТОГО Лэндинг'!$E$5:$E$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B12))</f>
+        <v/>
+      </c>
+      <c r="F12" s="246" t="str">
+        <f>IF($B12="","",IF(SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B12)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B12)=0,"",SUMIFS('ИТОГО Торговля'!$F$5:$F$200,'ИТОГО Торговля'!$B$5:$B$200,$B12)+SUMIFS('ИТОГО Лэндинг'!$F$5:$F$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B12)))</f>
+        <v/>
+      </c>
+      <c r="G12" s="183" t="str">
+        <f>IF(F12="","",H12/F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="247" t="str">
+        <f>IF(F12="","",SUMIFS('ИТОГО Торговля'!$H$5:$H$200,'ИТОГО Торговля'!$B$5:$B$200,$B12)+SUMIFS('ИТОГО Лэндинг'!$H$5:$H$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B12))</f>
+        <v/>
+      </c>
+      <c r="I12" s="246" t="str">
+        <f>IF($B12="","",IF(AND(C12="",F12=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$I$5:$I$200,'ИТОГО Торговля'!$B$5:$B$200,$B12)+SUMIFS('ИТОГО Лэндинг'!$I$5:$I$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B12),8)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="247" t="str">
+        <f>IF($B12="","",IF(AND(C12="",F12=""),"",ROUND(SUMIFS('ИТОГО Торговля'!$J$5:$J$200,'ИТОГО Торговля'!$B$5:$B$200,$B12)+SUMIFS('ИТОГО Лэндинг'!$J$5:$J$200,'ИТОГО Лэндинг'!$B$5:$B$200,$B12),8)))</f>
+        <v/>
+      </c>
+      <c r="K12" s="246" t="str">
+        <f>IF(MIN(N(C12),N(F12))&lt;=0,"",ROUND(MIN(N(C12),N(F12))*(N(G12)-N(D12)),8))</f>
+        <v/>
+      </c>
+      <c r="L12" s="183" t="str">
+        <f>IF(MIN(N(C12),N(F12))&lt;=0,"",IF(N(D12)=0,"",ROUND((N(G12)/N(D12)-1)*100,2)))</f>
+        <v/>
+      </c>
+      <c r="M12" s="183" t="str">
+        <f>IF(OR(ROUND(N(C12)-N(F12),8)=0,1-N(Ввод!$J$19)/100&lt;=0),"",IF(N(C12)&gt;N(F12),(N(E12)-N(H12))/((N(C12)-N(F12))*(1-N(Ввод!$J$19)/100)),(N(H12)-N(E12))/((N(F12)-N(C12))*(1+N(Ввод!$J$19)/100))))</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -1973,7 +1973,7 @@
       </c>
       <c r="J6" s="191" t="inlineStr">
         <is>
-          <t>Операция</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="K6" s="207" t="n"/>
@@ -2369,7 +2369,7 @@
     <mergeCell ref="B1:J2"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <dataValidations count="11">
+  <dataValidations count="12">
     <dataValidation sqref="H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Добавить,Закрыть"</formula1>
     </dataValidation>
@@ -2380,6 +2380,9 @@
       <formula1>=Список_Протокол</formula1>
     </dataValidation>
     <dataValidation sqref="H6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Действие" error="Выберите значение из списка." type="list">
+      <formula1>=Список_Действие_Торговля</formula1>
+    </dataValidation>
+    <dataValidation sqref="J6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Действие" error="Выберите значение из списка." type="list">
       <formula1>=Список_Действие_Торговля</formula1>
     </dataValidation>
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Актив" error="Актив 1 и Актив 2 не могут совпадать, символ «/» в тикере не допускается." type="custom">

--- a/CryptoJournal_Input_Prototype_v7.xlsx
+++ b/CryptoJournal_Input_Prototype_v7.xlsx
@@ -2029,8 +2029,8 @@
         </is>
       </c>
       <c r="J8" s="211">
-        <f>IF(AND(ISNUMBER(J7),ISNUMBER(J9),J7&lt;&gt;0,1-N(J19)/100&lt;&gt;0),J9/(J7*(1-N(J19)/100)),"")</f>
-        <v>1.00200400801603</v>
+        <f>IF(AND(ISNUMBER(J7),ISNUMBER(J9),J7&lt;&gt;0),IF(J6="Buy",J9/(J7*(1+N(J19)/100)),IF(AND(J6="Sell",1-N(J19)/100&lt;&gt;0),J9/(J7*(1-N(J19)/100)),"")),"")</f>
+        <v>0.998003992015968</v>
       </c>
       <c r="K8" s="207" t="n"/>
       <c r="L8" s="207" t="n"/>
